--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>7.56</v>
+        <v>6.94</v>
       </c>
       <c r="F14" t="n">
-        <v>17.89</v>
+        <v>17.93</v>
       </c>
       <c r="G14" t="n">
-        <v>157.5</v>
+        <v>158.7</v>
       </c>
       <c r="H14" t="n">
-        <v>84.2</v>
+        <v>86.5</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-154.62</v>
+        <v>-203.98</v>
       </c>
       <c r="K14" t="n">
-        <v>65.73999999999999</v>
+        <v>77.05</v>
       </c>
       <c r="L14" t="n">
-        <v>168.01</v>
+        <v>218.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:59:02</t>
+          <t>06:00:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.24</v>
+        <v>6.98</v>
       </c>
       <c r="F15" t="n">
-        <v>18.2</v>
+        <v>18.94</v>
       </c>
       <c r="G15" t="n">
-        <v>143.4</v>
+        <v>155</v>
       </c>
       <c r="H15" t="n">
-        <v>93.7</v>
+        <v>85.8</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>139.88</v>
+        <v>-100.76</v>
       </c>
       <c r="K15" t="n">
-        <v>-90.78</v>
+        <v>198.55</v>
       </c>
       <c r="L15" t="n">
-        <v>166.75</v>
+        <v>222.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:00:38</t>
+          <t>06:02:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.33</v>
+        <v>6.18</v>
       </c>
       <c r="F16" t="n">
-        <v>18.23</v>
+        <v>17.18</v>
       </c>
       <c r="G16" t="n">
-        <v>148.7</v>
+        <v>163.1</v>
       </c>
       <c r="H16" t="n">
-        <v>89</v>
+        <v>86.3</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-193.64</v>
+        <v>-113.51</v>
       </c>
       <c r="K16" t="n">
-        <v>-33.89</v>
+        <v>-114.4</v>
       </c>
       <c r="L16" t="n">
-        <v>196.59</v>
+        <v>161.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:06:00</t>
+          <t>06:07:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>6.18</v>
+        <v>7.34</v>
       </c>
       <c r="F17" t="n">
-        <v>18.69</v>
+        <v>18.02</v>
       </c>
       <c r="G17" t="n">
-        <v>146.4</v>
+        <v>155.1</v>
       </c>
       <c r="H17" t="n">
-        <v>93.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.67</v>
+        <v>-235.59</v>
       </c>
       <c r="K17" t="n">
-        <v>271.43</v>
+        <v>341.39</v>
       </c>
       <c r="L17" t="n">
-        <v>277.28</v>
+        <v>414.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:07:27</t>
+          <t>06:09:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>6.38</v>
+        <v>6.42</v>
       </c>
       <c r="F18" t="n">
-        <v>17.93</v>
+        <v>18.87</v>
       </c>
       <c r="G18" t="n">
-        <v>158.6</v>
+        <v>146.5</v>
       </c>
       <c r="H18" t="n">
-        <v>90.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-49.49</v>
+        <v>-109.46</v>
       </c>
       <c r="K18" t="n">
-        <v>140.13</v>
+        <v>282.1</v>
       </c>
       <c r="L18" t="n">
-        <v>148.61</v>
+        <v>302.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:08:49</t>
+          <t>06:10:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>7.13</v>
+        <v>5.96</v>
       </c>
       <c r="F19" t="n">
-        <v>18.32</v>
+        <v>19.04</v>
       </c>
       <c r="G19" t="n">
-        <v>168</v>
+        <v>153.9</v>
       </c>
       <c r="H19" t="n">
-        <v>84.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>89.79000000000001</v>
+        <v>-535.49</v>
       </c>
       <c r="K19" t="n">
-        <v>-51.94</v>
+        <v>59.45</v>
       </c>
       <c r="L19" t="n">
-        <v>103.73</v>
+        <v>538.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:14:42</t>
+          <t>06:14:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>7.04</v>
+        <v>6.43</v>
       </c>
       <c r="F20" t="n">
-        <v>17.85</v>
+        <v>18.19</v>
       </c>
       <c r="G20" t="n">
-        <v>143.6</v>
+        <v>153.8</v>
       </c>
       <c r="H20" t="n">
-        <v>86.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>25.89</v>
+        <v>245.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-233.73</v>
+        <v>-246.22</v>
       </c>
       <c r="L20" t="n">
-        <v>235.15</v>
+        <v>347.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:16:01</t>
+          <t>06:16:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>6.94</v>
+        <v>5.87</v>
       </c>
       <c r="F21" t="n">
-        <v>18.11</v>
+        <v>18.25</v>
       </c>
       <c r="G21" t="n">
-        <v>150.3</v>
+        <v>139.8</v>
       </c>
       <c r="H21" t="n">
-        <v>92.5</v>
+        <v>90.5</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>185.28</v>
+        <v>-116.45</v>
       </c>
       <c r="K21" t="n">
-        <v>260.26</v>
+        <v>311.69</v>
       </c>
       <c r="L21" t="n">
-        <v>319.47</v>
+        <v>332.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:17:27</t>
+          <t>06:18:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6.32</v>
+        <v>6.72</v>
       </c>
       <c r="F22" t="n">
-        <v>17.63</v>
+        <v>17.72</v>
       </c>
       <c r="G22" t="n">
-        <v>153.2</v>
+        <v>166.5</v>
       </c>
       <c r="H22" t="n">
-        <v>92.7</v>
+        <v>83</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>356.86</v>
+        <v>369.07</v>
       </c>
       <c r="K22" t="n">
-        <v>108.42</v>
+        <v>144.99</v>
       </c>
       <c r="L22" t="n">
-        <v>372.97</v>
+        <v>396.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:22:00</t>
+          <t>06:22:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>7.27</v>
+        <v>5.98</v>
       </c>
       <c r="F23" t="n">
-        <v>18.21</v>
+        <v>17.38</v>
       </c>
       <c r="G23" t="n">
-        <v>151.9</v>
+        <v>149.8</v>
       </c>
       <c r="H23" t="n">
-        <v>86.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>139.37</v>
+        <v>15.63</v>
       </c>
       <c r="K23" t="n">
-        <v>157.42</v>
+        <v>-352.49</v>
       </c>
       <c r="L23" t="n">
-        <v>210.25</v>
+        <v>352.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:22:33</t>
+          <t>06:23:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.13</v>
+        <v>7.07</v>
       </c>
       <c r="F24" t="n">
-        <v>18.01</v>
+        <v>18.41</v>
       </c>
       <c r="G24" t="n">
-        <v>128.8</v>
+        <v>155.1</v>
       </c>
       <c r="H24" t="n">
-        <v>89.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>522.8</v>
+        <v>-574.9</v>
       </c>
       <c r="K24" t="n">
-        <v>-263.36</v>
+        <v>-76</v>
       </c>
       <c r="L24" t="n">
-        <v>585.38</v>
+        <v>579.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:25:10</t>
+          <t>06:25:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>6.49</v>
+        <v>5.64</v>
       </c>
       <c r="F25" t="n">
-        <v>18.74</v>
+        <v>18.02</v>
       </c>
       <c r="G25" t="n">
-        <v>152.2</v>
+        <v>148.9</v>
       </c>
       <c r="H25" t="n">
-        <v>89.8</v>
+        <v>93.5</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>152.45</v>
+        <v>229.83</v>
       </c>
       <c r="K25" t="n">
-        <v>-222.24</v>
+        <v>80.27</v>
       </c>
       <c r="L25" t="n">
-        <v>269.5</v>
+        <v>243.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:29:32</t>
+          <t>06:29:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.29</v>
+        <v>6.31</v>
       </c>
       <c r="F26" t="n">
-        <v>18.27</v>
+        <v>18.38</v>
       </c>
       <c r="G26" t="n">
-        <v>164.7</v>
+        <v>159.5</v>
       </c>
       <c r="H26" t="n">
-        <v>84.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-424.75</v>
+        <v>-33.72</v>
       </c>
       <c r="K26" t="n">
-        <v>343.58</v>
+        <v>340.72</v>
       </c>
       <c r="L26" t="n">
-        <v>546.3099999999999</v>
+        <v>342.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:30:47</t>
+          <t>06:31:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>7.83</v>
+        <v>5.63</v>
       </c>
       <c r="F27" t="n">
-        <v>19.02</v>
+        <v>17.32</v>
       </c>
       <c r="G27" t="n">
-        <v>144.1</v>
+        <v>158.8</v>
       </c>
       <c r="H27" t="n">
-        <v>88.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-655.8200000000001</v>
+        <v>-25.45</v>
       </c>
       <c r="K27" t="n">
-        <v>-242.38</v>
+        <v>-428.15</v>
       </c>
       <c r="L27" t="n">
-        <v>699.1799999999999</v>
+        <v>428.91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:32:16</t>
+          <t>06:32:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>6.92</v>
+        <v>5.77</v>
       </c>
       <c r="F28" t="n">
-        <v>18.29</v>
+        <v>17.92</v>
       </c>
       <c r="G28" t="n">
-        <v>143.2</v>
+        <v>155.6</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-415.58</v>
+        <v>-175.26</v>
       </c>
       <c r="K28" t="n">
-        <v>42.5</v>
+        <v>-323.14</v>
       </c>
       <c r="L28" t="n">
-        <v>417.74</v>
+        <v>367.61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:43:29</t>
+          <t>06:41:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.92</v>
+        <v>6.97</v>
       </c>
       <c r="F29" t="n">
-        <v>18.23</v>
+        <v>17.77</v>
       </c>
       <c r="G29" t="n">
-        <v>159.3</v>
+        <v>162</v>
       </c>
       <c r="H29" t="n">
-        <v>95.8</v>
+        <v>90.8</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>44.67</v>
+        <v>-287.91</v>
       </c>
       <c r="K29" t="n">
-        <v>-98.38</v>
+        <v>50.58</v>
       </c>
       <c r="L29" t="n">
-        <v>108.05</v>
+        <v>292.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:44:31</t>
+          <t>06:42:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.09</v>
+        <v>6.66</v>
       </c>
       <c r="F30" t="n">
-        <v>17.61</v>
+        <v>18.18</v>
       </c>
       <c r="G30" t="n">
-        <v>149.9</v>
+        <v>141.7</v>
       </c>
       <c r="H30" t="n">
-        <v>83.5</v>
+        <v>86</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>58.65</v>
+        <v>-169.85</v>
       </c>
       <c r="K30" t="n">
-        <v>109.03</v>
+        <v>391.11</v>
       </c>
       <c r="L30" t="n">
-        <v>123.8</v>
+        <v>426.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:46:45</t>
+          <t>06:44:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.33</v>
+        <v>6.58</v>
       </c>
       <c r="F31" t="n">
-        <v>18.68</v>
+        <v>17.52</v>
       </c>
       <c r="G31" t="n">
-        <v>145.5</v>
+        <v>151.4</v>
       </c>
       <c r="H31" t="n">
-        <v>87.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-343.45</v>
+        <v>-28.79</v>
       </c>
       <c r="K31" t="n">
-        <v>246.8</v>
+        <v>181.07</v>
       </c>
       <c r="L31" t="n">
-        <v>422.93</v>
+        <v>183.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:51:21</t>
+          <t>06:48:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.91</v>
+        <v>6.23</v>
       </c>
       <c r="F32" t="n">
-        <v>18.09</v>
+        <v>18.32</v>
       </c>
       <c r="G32" t="n">
-        <v>152.2</v>
+        <v>161.7</v>
       </c>
       <c r="H32" t="n">
-        <v>91.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-373.98</v>
+        <v>353.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-117.01</v>
+        <v>276.85</v>
       </c>
       <c r="L32" t="n">
-        <v>391.86</v>
+        <v>448.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:53:03</t>
+          <t>06:49:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>7.88</v>
+        <v>7.12</v>
       </c>
       <c r="F33" t="n">
-        <v>17.91</v>
+        <v>18.27</v>
       </c>
       <c r="G33" t="n">
-        <v>154.5</v>
+        <v>157.6</v>
       </c>
       <c r="H33" t="n">
-        <v>86.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>206.43</v>
+        <v>-42.89</v>
       </c>
       <c r="K33" t="n">
-        <v>194.53</v>
+        <v>-434.83</v>
       </c>
       <c r="L33" t="n">
-        <v>283.65</v>
+        <v>436.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:55:06</t>
+          <t>06:51:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>7.32</v>
+        <v>6.65</v>
       </c>
       <c r="F34" t="n">
-        <v>18.33</v>
+        <v>18.96</v>
       </c>
       <c r="G34" t="n">
-        <v>160.2</v>
+        <v>154.8</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>385.03</v>
+        <v>-115.04</v>
       </c>
       <c r="K34" t="n">
-        <v>349.1</v>
+        <v>220.56</v>
       </c>
       <c r="L34" t="n">
-        <v>519.73</v>
+        <v>248.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:59:34</t>
+          <t>06:56:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="F35" t="n">
-        <v>18.3</v>
+        <v>17.79</v>
       </c>
       <c r="G35" t="n">
-        <v>139.9</v>
+        <v>151.5</v>
       </c>
       <c r="H35" t="n">
-        <v>85.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>157.03</v>
+        <v>-353.15</v>
       </c>
       <c r="K35" t="n">
-        <v>-260.88</v>
+        <v>103.87</v>
       </c>
       <c r="L35" t="n">
-        <v>304.49</v>
+        <v>368.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:01:23</t>
+          <t>06:57:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.69</v>
+        <v>6.74</v>
       </c>
       <c r="F36" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="G36" t="n">
-        <v>157.7</v>
+        <v>145.7</v>
       </c>
       <c r="H36" t="n">
-        <v>82.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>171.66</v>
+        <v>219.12</v>
       </c>
       <c r="K36" t="n">
-        <v>-184.69</v>
+        <v>198.58</v>
       </c>
       <c r="L36" t="n">
-        <v>252.15</v>
+        <v>295.71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:03:57</t>
+          <t>06:58:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.7</v>
+        <v>8.17</v>
       </c>
       <c r="F37" t="n">
-        <v>17.59</v>
+        <v>18.35</v>
       </c>
       <c r="G37" t="n">
-        <v>167.6</v>
+        <v>153.5</v>
       </c>
       <c r="H37" t="n">
-        <v>88.3</v>
+        <v>87.8</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>58.07</v>
+        <v>551.08</v>
       </c>
       <c r="K37" t="n">
-        <v>97.64</v>
+        <v>-373.44</v>
       </c>
       <c r="L37" t="n">
-        <v>113.6</v>
+        <v>665.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:09:24</t>
+          <t>07:03:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.26</v>
+        <v>7.34</v>
       </c>
       <c r="F38" t="n">
-        <v>18.39</v>
+        <v>19.17</v>
       </c>
       <c r="G38" t="n">
-        <v>166</v>
+        <v>149.3</v>
       </c>
       <c r="H38" t="n">
-        <v>93.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>42.44</v>
+        <v>267.69</v>
       </c>
       <c r="K38" t="n">
-        <v>554.99</v>
+        <v>-607.11</v>
       </c>
       <c r="L38" t="n">
-        <v>556.61</v>
+        <v>663.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:11:09</t>
+          <t>07:03:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>7.38</v>
+        <v>7.81</v>
       </c>
       <c r="F39" t="n">
-        <v>18.6</v>
+        <v>17.99</v>
       </c>
       <c r="G39" t="n">
-        <v>145.3</v>
+        <v>153.9</v>
       </c>
       <c r="H39" t="n">
-        <v>87</v>
+        <v>92.2</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>77.70999999999999</v>
+        <v>359.75</v>
       </c>
       <c r="K39" t="n">
-        <v>-82.18000000000001</v>
+        <v>-6.35</v>
       </c>
       <c r="L39" t="n">
-        <v>113.1</v>
+        <v>359.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:12:36</t>
+          <t>07:05:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>7.62</v>
+        <v>6.76</v>
       </c>
       <c r="F40" t="n">
-        <v>18.4</v>
+        <v>17.94</v>
       </c>
       <c r="G40" t="n">
-        <v>143.5</v>
+        <v>152.3</v>
       </c>
       <c r="H40" t="n">
-        <v>86.2</v>
+        <v>91</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>272.32</v>
+        <v>-564.14</v>
       </c>
       <c r="K40" t="n">
-        <v>492.91</v>
+        <v>124.76</v>
       </c>
       <c r="L40" t="n">
-        <v>563.13</v>
+        <v>577.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:15:37</t>
+          <t>07:10:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.73</v>
+        <v>6.63</v>
       </c>
       <c r="F41" t="n">
-        <v>17.86</v>
+        <v>18.33</v>
       </c>
       <c r="G41" t="n">
-        <v>146.6</v>
+        <v>144</v>
       </c>
       <c r="H41" t="n">
-        <v>84</v>
+        <v>87.2</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-298.17</v>
+        <v>-198.71</v>
       </c>
       <c r="K41" t="n">
-        <v>254.53</v>
+        <v>-1411.09</v>
       </c>
       <c r="L41" t="n">
-        <v>392.04</v>
+        <v>1425.01</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:16:22</t>
+          <t>07:12:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>7.18</v>
+        <v>6.97</v>
       </c>
       <c r="F42" t="n">
-        <v>18.88</v>
+        <v>17.68</v>
       </c>
       <c r="G42" t="n">
-        <v>154.2</v>
+        <v>160.5</v>
       </c>
       <c r="H42" t="n">
-        <v>91.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>338.92</v>
+        <v>-433.16</v>
       </c>
       <c r="K42" t="n">
-        <v>140.13</v>
+        <v>958.02</v>
       </c>
       <c r="L42" t="n">
-        <v>366.74</v>
+        <v>1051.39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:18:04</t>
+          <t>07:14:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>7.53</v>
+        <v>7.28</v>
       </c>
       <c r="F43" t="n">
-        <v>18.17</v>
+        <v>18.13</v>
       </c>
       <c r="G43" t="n">
-        <v>135.7</v>
+        <v>149.7</v>
       </c>
       <c r="H43" t="n">
-        <v>90.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>182.95</v>
+        <v>-495.46</v>
       </c>
       <c r="K43" t="n">
-        <v>14.86</v>
+        <v>-99.13</v>
       </c>
       <c r="L43" t="n">
-        <v>183.55</v>
+        <v>505.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:30:31</t>
+          <t>07:22:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6.63</v>
+        <v>7.46</v>
       </c>
       <c r="F44" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="G44" t="n">
-        <v>145.2</v>
+        <v>149.5</v>
       </c>
       <c r="H44" t="n">
-        <v>94.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-94.31</v>
+        <v>226.03</v>
       </c>
       <c r="K44" t="n">
-        <v>-24.89</v>
+        <v>-306.73</v>
       </c>
       <c r="L44" t="n">
-        <v>97.54000000000001</v>
+        <v>381.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:31:27</t>
+          <t>07:24:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>6.67</v>
+        <v>7.1</v>
       </c>
       <c r="F45" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="G45" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="I45" t="n">
         <v>19</v>
       </c>
-      <c r="G45" t="n">
-        <v>154.1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="I45" t="n">
-        <v>22</v>
-      </c>
       <c r="J45" t="n">
-        <v>294.67</v>
+        <v>-180.06</v>
       </c>
       <c r="K45" t="n">
-        <v>117.66</v>
+        <v>372.38</v>
       </c>
       <c r="L45" t="n">
-        <v>317.29</v>
+        <v>413.63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:32:56</t>
+          <t>07:25:57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>7.15</v>
+        <v>7.45</v>
       </c>
       <c r="F46" t="n">
-        <v>18.56</v>
+        <v>18.2</v>
       </c>
       <c r="G46" t="n">
-        <v>152.4</v>
+        <v>139.8</v>
       </c>
       <c r="H46" t="n">
-        <v>87.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>160.75</v>
+        <v>-269.12</v>
       </c>
       <c r="K46" t="n">
-        <v>198.97</v>
+        <v>79.2</v>
       </c>
       <c r="L46" t="n">
-        <v>255.79</v>
+        <v>280.53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:38:05</t>
+          <t>07:31:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.62</v>
+        <v>6.32</v>
       </c>
       <c r="F47" t="n">
-        <v>17.7</v>
+        <v>17.81</v>
       </c>
       <c r="G47" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="H47" t="n">
-        <v>96.2</v>
+        <v>91.2</v>
       </c>
       <c r="I47" t="n">
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>343.09</v>
+        <v>20.08</v>
       </c>
       <c r="K47" t="n">
-        <v>-316.67</v>
+        <v>-744.13</v>
       </c>
       <c r="L47" t="n">
-        <v>466.9</v>
+        <v>744.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:40:16</t>
+          <t>07:32:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.08</v>
+        <v>7.69</v>
       </c>
       <c r="F48" t="n">
-        <v>18.37</v>
+        <v>17.93</v>
       </c>
       <c r="G48" t="n">
-        <v>156.8</v>
+        <v>159.8</v>
       </c>
       <c r="H48" t="n">
-        <v>91.2</v>
+        <v>86.8</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-322.23</v>
+        <v>129.72</v>
       </c>
       <c r="K48" t="n">
-        <v>231.39</v>
+        <v>561.37</v>
       </c>
       <c r="L48" t="n">
-        <v>396.7</v>
+        <v>576.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:42:46</t>
+          <t>07:34:44</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.86</v>
+        <v>7.93</v>
       </c>
       <c r="F49" t="n">
-        <v>18.66</v>
+        <v>18.46</v>
       </c>
       <c r="G49" t="n">
-        <v>153.7</v>
+        <v>141.7</v>
       </c>
       <c r="H49" t="n">
-        <v>90.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>109.31</v>
+        <v>162.42</v>
       </c>
       <c r="K49" t="n">
-        <v>154.82</v>
+        <v>-130.32</v>
       </c>
       <c r="L49" t="n">
-        <v>189.52</v>
+        <v>208.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:47:22</t>
+          <t>07:40:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7.82</v>
+        <v>7.32</v>
       </c>
       <c r="F50" t="n">
-        <v>17.54</v>
+        <v>18.46</v>
       </c>
       <c r="G50" t="n">
-        <v>162.7</v>
+        <v>153.2</v>
       </c>
       <c r="H50" t="n">
-        <v>93.8</v>
+        <v>77.8</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-324.3</v>
+        <v>-361.52</v>
       </c>
       <c r="K50" t="n">
-        <v>258.25</v>
+        <v>126.15</v>
       </c>
       <c r="L50" t="n">
-        <v>414.57</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:49:38</t>
+          <t>07:43:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.38</v>
+        <v>6.98</v>
       </c>
       <c r="F51" t="n">
-        <v>17.93</v>
+        <v>18.38</v>
       </c>
       <c r="G51" t="n">
-        <v>146.8</v>
+        <v>154.3</v>
       </c>
       <c r="H51" t="n">
-        <v>93</v>
+        <v>84.7</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-392.61</v>
+        <v>166.79</v>
       </c>
       <c r="K51" t="n">
-        <v>114.92</v>
+        <v>-401.74</v>
       </c>
       <c r="L51" t="n">
-        <v>409.09</v>
+        <v>434.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:51:32</t>
+          <t>07:44:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.46</v>
+        <v>5.63</v>
       </c>
       <c r="F52" t="n">
-        <v>17.96</v>
+        <v>18.52</v>
       </c>
       <c r="G52" t="n">
-        <v>146.4</v>
+        <v>149</v>
       </c>
       <c r="H52" t="n">
-        <v>86.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>3.17</v>
+        <v>416.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-309.92</v>
+        <v>-126.79</v>
       </c>
       <c r="L52" t="n">
-        <v>309.94</v>
+        <v>435.22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:55:17</t>
+          <t>07:50:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7.54</v>
+        <v>7.36</v>
       </c>
       <c r="F53" t="n">
-        <v>18.19</v>
+        <v>18.54</v>
       </c>
       <c r="G53" t="n">
-        <v>139</v>
+        <v>148.1</v>
       </c>
       <c r="H53" t="n">
-        <v>87.3</v>
+        <v>83.3</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-309.99</v>
+        <v>231.35</v>
       </c>
       <c r="K53" t="n">
-        <v>629.61</v>
+        <v>-313.87</v>
       </c>
       <c r="L53" t="n">
-        <v>701.79</v>
+        <v>389.92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:56:27</t>
+          <t>07:53:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.53</v>
+        <v>7.55</v>
       </c>
       <c r="F54" t="n">
-        <v>18.71</v>
+        <v>18.67</v>
       </c>
       <c r="G54" t="n">
-        <v>137</v>
+        <v>154.4</v>
       </c>
       <c r="H54" t="n">
-        <v>92.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-36.25</v>
+        <v>546.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-336.42</v>
+        <v>-116.52</v>
       </c>
       <c r="L54" t="n">
-        <v>338.37</v>
+        <v>558.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:57:50</t>
+          <t>07:55:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="F55" t="n">
-        <v>18.35</v>
+        <v>18.72</v>
       </c>
       <c r="G55" t="n">
-        <v>163.6</v>
+        <v>143.3</v>
       </c>
       <c r="H55" t="n">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I55" t="n">
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>164.59</v>
+        <v>-234.6</v>
       </c>
       <c r="K55" t="n">
-        <v>-148.71</v>
+        <v>-85.34999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>221.82</v>
+        <v>249.65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:02:29</t>
+          <t>07:58:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>7.32</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>18.55</v>
+        <v>18.86</v>
       </c>
       <c r="G56" t="n">
-        <v>156.9</v>
+        <v>147.4</v>
       </c>
       <c r="H56" t="n">
-        <v>86.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>21.4</v>
+        <v>-698.46</v>
       </c>
       <c r="K56" t="n">
-        <v>559.99</v>
+        <v>2028.23</v>
       </c>
       <c r="L56" t="n">
-        <v>560.4</v>
+        <v>2145.13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:03:51</t>
+          <t>08:00:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>7.64</v>
+        <v>7.5</v>
       </c>
       <c r="F57" t="n">
-        <v>17.91</v>
+        <v>18.94</v>
       </c>
       <c r="G57" t="n">
-        <v>143.9</v>
+        <v>158.6</v>
       </c>
       <c r="H57" t="n">
-        <v>87.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-262.12</v>
+        <v>-388.53</v>
       </c>
       <c r="K57" t="n">
-        <v>305.71</v>
+        <v>480.13</v>
       </c>
       <c r="L57" t="n">
-        <v>402.7</v>
+        <v>617.64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:05:06</t>
+          <t>08:02:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>7.39</v>
+        <v>6.76</v>
       </c>
       <c r="F58" t="n">
-        <v>17.89</v>
+        <v>17.84</v>
       </c>
       <c r="G58" t="n">
-        <v>157.6</v>
+        <v>139.3</v>
       </c>
       <c r="H58" t="n">
-        <v>92.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-341.92</v>
+        <v>350.63</v>
       </c>
       <c r="K58" t="n">
-        <v>5.16</v>
+        <v>-1022.54</v>
       </c>
       <c r="L58" t="n">
-        <v>341.96</v>
+        <v>1080.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:17:34</t>
+          <t>08:11:42</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.71</v>
+        <v>5.39</v>
       </c>
       <c r="F59" t="n">
-        <v>18.36</v>
+        <v>17.95</v>
       </c>
       <c r="G59" t="n">
-        <v>155.2</v>
+        <v>164</v>
       </c>
       <c r="H59" t="n">
-        <v>90.8</v>
+        <v>87.7</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-91.90000000000001</v>
+        <v>-4.53</v>
       </c>
       <c r="K59" t="n">
-        <v>-82.92</v>
+        <v>-45.52</v>
       </c>
       <c r="L59" t="n">
-        <v>123.78</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:19:11</t>
+          <t>08:12:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>7.31</v>
+        <v>6.74</v>
       </c>
       <c r="F60" t="n">
-        <v>18.47</v>
+        <v>18.11</v>
       </c>
       <c r="G60" t="n">
-        <v>143.9</v>
+        <v>153.2</v>
       </c>
       <c r="H60" t="n">
-        <v>93.3</v>
+        <v>87</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-38.92</v>
+        <v>251.28</v>
       </c>
       <c r="K60" t="n">
-        <v>-267.35</v>
+        <v>94.73</v>
       </c>
       <c r="L60" t="n">
-        <v>270.16</v>
+        <v>268.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:20:53</t>
+          <t>08:14:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>8.23</v>
+        <v>6.98</v>
       </c>
       <c r="F61" t="n">
-        <v>18.18</v>
+        <v>17.95</v>
       </c>
       <c r="G61" t="n">
-        <v>156.7</v>
+        <v>152.4</v>
       </c>
       <c r="H61" t="n">
-        <v>87.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-202.39</v>
+        <v>-381.36</v>
       </c>
       <c r="K61" t="n">
-        <v>-524.64</v>
+        <v>-96.43000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>562.3200000000001</v>
+        <v>393.37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:25:01</t>
+          <t>08:17:35</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>7.63</v>
+        <v>7.59</v>
       </c>
       <c r="F62" t="n">
-        <v>18.44</v>
+        <v>18.72</v>
       </c>
       <c r="G62" t="n">
-        <v>154.8</v>
+        <v>158.9</v>
       </c>
       <c r="H62" t="n">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>434.51</v>
+        <v>593.49</v>
       </c>
       <c r="K62" t="n">
-        <v>271.04</v>
+        <v>-275.01</v>
       </c>
       <c r="L62" t="n">
-        <v>512.12</v>
+        <v>654.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:26:12</t>
+          <t>08:18:48</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>7.51</v>
+        <v>5.77</v>
       </c>
       <c r="F63" t="n">
-        <v>17.95</v>
+        <v>18.73</v>
       </c>
       <c r="G63" t="n">
-        <v>156.3</v>
+        <v>154</v>
       </c>
       <c r="H63" t="n">
-        <v>89.5</v>
+        <v>90.7</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>113.11</v>
+        <v>201.71</v>
       </c>
       <c r="K63" t="n">
-        <v>-128.09</v>
+        <v>-243.84</v>
       </c>
       <c r="L63" t="n">
-        <v>170.88</v>
+        <v>316.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:27:38</t>
+          <t>08:20:54</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.54</v>
+        <v>6.64</v>
       </c>
       <c r="F64" t="n">
-        <v>18.38</v>
+        <v>17.95</v>
       </c>
       <c r="G64" t="n">
-        <v>171.7</v>
+        <v>146.8</v>
       </c>
       <c r="H64" t="n">
-        <v>91.7</v>
+        <v>90.5</v>
       </c>
       <c r="I64" t="n">
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>286.76</v>
+        <v>-179.14</v>
       </c>
       <c r="K64" t="n">
-        <v>-262</v>
+        <v>-364.52</v>
       </c>
       <c r="L64" t="n">
-        <v>388.42</v>
+        <v>406.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:32:48</t>
+          <t>08:25:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>7.28</v>
+        <v>6.43</v>
       </c>
       <c r="F65" t="n">
-        <v>18.45</v>
+        <v>18.31</v>
       </c>
       <c r="G65" t="n">
-        <v>139.3</v>
+        <v>154.1</v>
       </c>
       <c r="H65" t="n">
-        <v>88.7</v>
+        <v>94.5</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-145.01</v>
+        <v>-27.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-252.85</v>
+        <v>113.97</v>
       </c>
       <c r="L65" t="n">
-        <v>291.49</v>
+        <v>117.14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:34:33</t>
+          <t>08:27:40</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>7.96</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>17.78</v>
+        <v>18</v>
       </c>
       <c r="G66" t="n">
-        <v>163.8</v>
+        <v>158.1</v>
       </c>
       <c r="H66" t="n">
-        <v>92.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>243.34</v>
+        <v>161.14</v>
       </c>
       <c r="K66" t="n">
-        <v>-67.73999999999999</v>
+        <v>252.12</v>
       </c>
       <c r="L66" t="n">
-        <v>252.59</v>
+        <v>299.22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:35:46</t>
+          <t>08:29:57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.79</v>
+        <v>7.67</v>
       </c>
       <c r="F67" t="n">
-        <v>18.38</v>
+        <v>18.37</v>
       </c>
       <c r="G67" t="n">
-        <v>154.9</v>
+        <v>156.2</v>
       </c>
       <c r="H67" t="n">
-        <v>93.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>75.8</v>
+        <v>480.41</v>
       </c>
       <c r="K67" t="n">
-        <v>-100.56</v>
+        <v>-427.74</v>
       </c>
       <c r="L67" t="n">
-        <v>125.93</v>
+        <v>643.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:41:31</t>
+          <t>08:32:57</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>8.380000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="F68" t="n">
-        <v>18.16</v>
+        <v>18.31</v>
       </c>
       <c r="G68" t="n">
-        <v>154.8</v>
+        <v>148.9</v>
       </c>
       <c r="H68" t="n">
-        <v>92.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>80.44</v>
+        <v>-1692.38</v>
       </c>
       <c r="K68" t="n">
-        <v>170.01</v>
+        <v>-724.78</v>
       </c>
       <c r="L68" t="n">
-        <v>188.08</v>
+        <v>1841.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:43:30</t>
+          <t>08:34:49</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>7.95</v>
+        <v>7.33</v>
       </c>
       <c r="F69" t="n">
-        <v>18.04</v>
+        <v>17.78</v>
       </c>
       <c r="G69" t="n">
-        <v>158</v>
+        <v>149.2</v>
       </c>
       <c r="H69" t="n">
-        <v>95.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>166.91</v>
+        <v>-135.84</v>
       </c>
       <c r="K69" t="n">
-        <v>898.47</v>
+        <v>-253.61</v>
       </c>
       <c r="L69" t="n">
-        <v>913.85</v>
+        <v>287.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:45:38</t>
+          <t>08:37:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>7.53</v>
+        <v>7.21</v>
       </c>
       <c r="F70" t="n">
-        <v>18.69</v>
+        <v>18.2</v>
       </c>
       <c r="G70" t="n">
-        <v>147.9</v>
+        <v>148.7</v>
       </c>
       <c r="H70" t="n">
-        <v>83.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>597.03</v>
+        <v>603.11</v>
       </c>
       <c r="K70" t="n">
-        <v>-690.17</v>
+        <v>351.22</v>
       </c>
       <c r="L70" t="n">
-        <v>912.5700000000001</v>
+        <v>697.92</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:49:02</t>
+          <t>08:42:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>8.33</v>
+        <v>7.88</v>
       </c>
       <c r="F71" t="n">
-        <v>18.38</v>
+        <v>18.3</v>
       </c>
       <c r="G71" t="n">
-        <v>133</v>
+        <v>150.3</v>
       </c>
       <c r="H71" t="n">
-        <v>90.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-157.6</v>
+        <v>-795.52</v>
       </c>
       <c r="K71" t="n">
-        <v>-747.46</v>
+        <v>-911.59</v>
       </c>
       <c r="L71" t="n">
-        <v>763.89</v>
+        <v>1209.89</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:51:10</t>
+          <t>08:44:33</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.86</v>
+        <v>6.4</v>
       </c>
       <c r="F72" t="n">
-        <v>17.59</v>
+        <v>17.63</v>
       </c>
       <c r="G72" t="n">
-        <v>135.9</v>
+        <v>155.8</v>
       </c>
       <c r="H72" t="n">
-        <v>94.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>129.4</v>
+        <v>-377.52</v>
       </c>
       <c r="K72" t="n">
-        <v>-581.24</v>
+        <v>-44.6</v>
       </c>
       <c r="L72" t="n">
-        <v>595.47</v>
+        <v>380.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:52:11</t>
+          <t>08:46:53</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7.91</v>
+        <v>7.93</v>
       </c>
       <c r="F73" t="n">
-        <v>18.07</v>
+        <v>18.32</v>
       </c>
       <c r="G73" t="n">
-        <v>136.2</v>
+        <v>174.7</v>
       </c>
       <c r="H73" t="n">
-        <v>89.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>105.53</v>
+        <v>940.77</v>
       </c>
       <c r="K73" t="n">
-        <v>-102.65</v>
+        <v>91.17</v>
       </c>
       <c r="L73" t="n">
-        <v>147.22</v>
+        <v>945.1799999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:01:50</t>
+          <t>08:57:52</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7.68</v>
+        <v>6.91</v>
       </c>
       <c r="F74" t="n">
-        <v>18.13</v>
+        <v>18.28</v>
       </c>
       <c r="G74" t="n">
-        <v>154.3</v>
+        <v>164.6</v>
       </c>
       <c r="H74" t="n">
-        <v>89.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>81.34999999999999</v>
+        <v>439.83</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.32</v>
+        <v>-92.54000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>81.34999999999999</v>
+        <v>449.46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:04:05</t>
+          <t>08:59:31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>7.34</v>
+        <v>7.88</v>
       </c>
       <c r="F75" t="n">
-        <v>18.29</v>
+        <v>18.17</v>
       </c>
       <c r="G75" t="n">
-        <v>154.9</v>
+        <v>141.4</v>
       </c>
       <c r="H75" t="n">
-        <v>83.5</v>
+        <v>86.7</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-76.31</v>
+        <v>-87.70999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-147.32</v>
+        <v>332.14</v>
       </c>
       <c r="L75" t="n">
-        <v>165.91</v>
+        <v>343.53</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:05:07</t>
+          <t>09:00:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.95</v>
+        <v>7.01</v>
       </c>
       <c r="F76" t="n">
-        <v>18.44</v>
+        <v>17.67</v>
       </c>
       <c r="G76" t="n">
-        <v>162.8</v>
+        <v>139.3</v>
       </c>
       <c r="H76" t="n">
-        <v>96.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.56</v>
+        <v>481.29</v>
       </c>
       <c r="K76" t="n">
-        <v>251.65</v>
+        <v>128.99</v>
       </c>
       <c r="L76" t="n">
-        <v>253.62</v>
+        <v>498.28</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:10:03</t>
+          <t>09:04:22</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.94</v>
+        <v>6.52</v>
       </c>
       <c r="F77" t="n">
-        <v>17.46</v>
+        <v>17.85</v>
       </c>
       <c r="G77" t="n">
-        <v>146.9</v>
+        <v>160.9</v>
       </c>
       <c r="H77" t="n">
-        <v>88.5</v>
+        <v>89.7</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>19.74</v>
+        <v>258.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-240.93</v>
+        <v>-155.01</v>
       </c>
       <c r="L77" t="n">
-        <v>241.74</v>
+        <v>301.35</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:12:00</t>
+          <t>09:06:42</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>7.69</v>
+        <v>7.29</v>
       </c>
       <c r="F78" t="n">
-        <v>17.88</v>
+        <v>18.19</v>
       </c>
       <c r="G78" t="n">
-        <v>153.1</v>
+        <v>156.1</v>
       </c>
       <c r="H78" t="n">
-        <v>91.8</v>
+        <v>91.7</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>564.15</v>
+        <v>-126.93</v>
       </c>
       <c r="K78" t="n">
-        <v>-348.54</v>
+        <v>-420.67</v>
       </c>
       <c r="L78" t="n">
-        <v>663.14</v>
+        <v>439.41</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:13:15</t>
+          <t>09:07:42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>7.43</v>
+        <v>8.69</v>
       </c>
       <c r="F79" t="n">
-        <v>18.26</v>
+        <v>18.05</v>
       </c>
       <c r="G79" t="n">
-        <v>155.6</v>
+        <v>152.3</v>
       </c>
       <c r="H79" t="n">
-        <v>94.2</v>
+        <v>89.8</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>36.78</v>
+        <v>9.9</v>
       </c>
       <c r="K79" t="n">
-        <v>84.22</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>91.90000000000001</v>
+        <v>80.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:17:55</t>
+          <t>09:11:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.6</v>
+        <v>6.19</v>
       </c>
       <c r="F80" t="n">
-        <v>17.34</v>
+        <v>17.65</v>
       </c>
       <c r="G80" t="n">
-        <v>141.1</v>
+        <v>156.4</v>
       </c>
       <c r="H80" t="n">
-        <v>94.7</v>
+        <v>89.5</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-77.23</v>
+        <v>-213.82</v>
       </c>
       <c r="K80" t="n">
-        <v>-542.59</v>
+        <v>465.22</v>
       </c>
       <c r="L80" t="n">
-        <v>548.0599999999999</v>
+        <v>512.01</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:19:35</t>
+          <t>09:12:06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>7.86</v>
+        <v>7.22</v>
       </c>
       <c r="F81" t="n">
-        <v>18.65</v>
+        <v>18.71</v>
       </c>
       <c r="G81" t="n">
-        <v>157.9</v>
+        <v>149.8</v>
       </c>
       <c r="H81" t="n">
-        <v>94.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>281.26</v>
+        <v>-485.58</v>
       </c>
       <c r="K81" t="n">
-        <v>-559.8</v>
+        <v>-831.9299999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>626.49</v>
+        <v>963.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:22:19</t>
+          <t>09:13:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.74</v>
+        <v>6.94</v>
       </c>
       <c r="F82" t="n">
-        <v>18.33</v>
+        <v>17.39</v>
       </c>
       <c r="G82" t="n">
-        <v>154.9</v>
+        <v>145.9</v>
       </c>
       <c r="H82" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I82" t="n">
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>83.31999999999999</v>
+        <v>479.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-250.42</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>263.92</v>
+        <v>489.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:25:37</t>
+          <t>09:17:28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>7.52</v>
+        <v>7.7</v>
       </c>
       <c r="F83" t="n">
-        <v>17.96</v>
+        <v>18.55</v>
       </c>
       <c r="G83" t="n">
-        <v>156.3</v>
+        <v>151.5</v>
       </c>
       <c r="H83" t="n">
-        <v>99.7</v>
+        <v>85.5</v>
       </c>
       <c r="I83" t="n">
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-181.37</v>
+        <v>453.76</v>
       </c>
       <c r="K83" t="n">
-        <v>597.21</v>
+        <v>-579.24</v>
       </c>
       <c r="L83" t="n">
-        <v>624.15</v>
+        <v>735.8099999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:27:35</t>
+          <t>09:19:18</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.58</v>
+        <v>7.61</v>
       </c>
       <c r="F84" t="n">
-        <v>18.18</v>
+        <v>17.5</v>
       </c>
       <c r="G84" t="n">
-        <v>156.5</v>
+        <v>168.1</v>
       </c>
       <c r="H84" t="n">
-        <v>94.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="I84" t="n">
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>89.75</v>
+        <v>748.5599999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>65.91</v>
+        <v>-1013.56</v>
       </c>
       <c r="L84" t="n">
-        <v>111.35</v>
+        <v>1260.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:28:50</t>
+          <t>09:21:42</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>8.41</v>
+        <v>7.24</v>
       </c>
       <c r="F85" t="n">
-        <v>17.99</v>
+        <v>18.47</v>
       </c>
       <c r="G85" t="n">
-        <v>142.3</v>
+        <v>156.6</v>
       </c>
       <c r="H85" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-301.31</v>
+        <v>-502.02</v>
       </c>
       <c r="K85" t="n">
-        <v>-259.83</v>
+        <v>-93.05</v>
       </c>
       <c r="L85" t="n">
-        <v>397.87</v>
+        <v>510.57</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:32:35</t>
+          <t>09:27:21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>8.460000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="F86" t="n">
-        <v>18.65</v>
+        <v>17.72</v>
       </c>
       <c r="G86" t="n">
-        <v>148.3</v>
+        <v>152.6</v>
       </c>
       <c r="H86" t="n">
-        <v>90.2</v>
+        <v>98.7</v>
       </c>
       <c r="I86" t="n">
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>93.29000000000001</v>
+        <v>-790.03</v>
       </c>
       <c r="K86" t="n">
-        <v>-272.18</v>
+        <v>-907.71</v>
       </c>
       <c r="L86" t="n">
-        <v>287.73</v>
+        <v>1203.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:34:19</t>
+          <t>09:29:24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>7.91</v>
+        <v>7.04</v>
       </c>
       <c r="F87" t="n">
-        <v>18.08</v>
+        <v>17.76</v>
       </c>
       <c r="G87" t="n">
-        <v>160.7</v>
+        <v>156</v>
       </c>
       <c r="H87" t="n">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-245.42</v>
+        <v>256.38</v>
       </c>
       <c r="K87" t="n">
-        <v>-414.21</v>
+        <v>-587.78</v>
       </c>
       <c r="L87" t="n">
-        <v>481.46</v>
+        <v>641.27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:35:52</t>
+          <t>09:30:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>8.779999999999999</v>
+        <v>7.49</v>
       </c>
       <c r="F88" t="n">
-        <v>18.51</v>
+        <v>18.84</v>
       </c>
       <c r="G88" t="n">
-        <v>158.9</v>
+        <v>153.6</v>
       </c>
       <c r="H88" t="n">
-        <v>92.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>185.48</v>
+        <v>962.98</v>
       </c>
       <c r="K88" t="n">
-        <v>130.47</v>
+        <v>250.31</v>
       </c>
       <c r="L88" t="n">
-        <v>226.77</v>
+        <v>994.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-203.98</v>
+        <v>-337.43</v>
       </c>
       <c r="K14" t="n">
-        <v>77.05</v>
+        <v>127.46</v>
       </c>
       <c r="L14" t="n">
-        <v>218.05</v>
+        <v>360.7</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-100.76</v>
+        <v>-174.69</v>
       </c>
       <c r="K15" t="n">
-        <v>198.55</v>
+        <v>344.22</v>
       </c>
       <c r="L15" t="n">
-        <v>222.66</v>
+        <v>386.01</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-113.51</v>
+        <v>-205.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-114.4</v>
+        <v>-207.41</v>
       </c>
       <c r="L16" t="n">
-        <v>161.15</v>
+        <v>292.19</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-235.59</v>
+        <v>-326.45</v>
       </c>
       <c r="K17" t="n">
-        <v>341.39</v>
+        <v>473.07</v>
       </c>
       <c r="L17" t="n">
-        <v>414.79</v>
+        <v>574.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-109.46</v>
+        <v>-166.47</v>
       </c>
       <c r="K18" t="n">
-        <v>282.1</v>
+        <v>429.03</v>
       </c>
       <c r="L18" t="n">
-        <v>302.59</v>
+        <v>460.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-535.49</v>
+        <v>-627.96</v>
       </c>
       <c r="K19" t="n">
-        <v>59.45</v>
+        <v>69.72</v>
       </c>
       <c r="L19" t="n">
-        <v>538.78</v>
+        <v>631.8200000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>245.8</v>
+        <v>413.35</v>
       </c>
       <c r="K20" t="n">
-        <v>-246.22</v>
+        <v>-414.06</v>
       </c>
       <c r="L20" t="n">
-        <v>347.91</v>
+        <v>585.0599999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-116.45</v>
+        <v>-189.76</v>
       </c>
       <c r="K21" t="n">
-        <v>311.69</v>
+        <v>507.9</v>
       </c>
       <c r="L21" t="n">
-        <v>332.73</v>
+        <v>542.1900000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>369.07</v>
+        <v>571.0599999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>144.99</v>
+        <v>224.34</v>
       </c>
       <c r="L22" t="n">
-        <v>396.53</v>
+        <v>613.55</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>15.63</v>
+        <v>31.94</v>
       </c>
       <c r="K23" t="n">
-        <v>-352.49</v>
+        <v>-720.3200000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>352.84</v>
+        <v>721.02</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-574.9</v>
+        <v>-1021.56</v>
       </c>
       <c r="K24" t="n">
-        <v>-76</v>
+        <v>-135.04</v>
       </c>
       <c r="L24" t="n">
-        <v>579.9</v>
+        <v>1030.45</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>229.83</v>
+        <v>498.52</v>
       </c>
       <c r="K25" t="n">
-        <v>80.27</v>
+        <v>174.12</v>
       </c>
       <c r="L25" t="n">
-        <v>243.44</v>
+        <v>528.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-33.72</v>
+        <v>-76.89</v>
       </c>
       <c r="K26" t="n">
-        <v>340.72</v>
+        <v>777.02</v>
       </c>
       <c r="L26" t="n">
-        <v>342.38</v>
+        <v>780.8099999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-25.45</v>
+        <v>-52.56</v>
       </c>
       <c r="K27" t="n">
-        <v>-428.15</v>
+        <v>-884.16</v>
       </c>
       <c r="L27" t="n">
-        <v>428.91</v>
+        <v>885.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-175.26</v>
+        <v>-385.42</v>
       </c>
       <c r="K28" t="n">
-        <v>-323.14</v>
+        <v>-710.62</v>
       </c>
       <c r="L28" t="n">
-        <v>367.61</v>
+        <v>808.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-287.91</v>
+        <v>-395.02</v>
       </c>
       <c r="K29" t="n">
-        <v>50.58</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>292.32</v>
+        <v>401.07</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-169.85</v>
+        <v>-228.55</v>
       </c>
       <c r="K30" t="n">
-        <v>391.11</v>
+        <v>526.25</v>
       </c>
       <c r="L30" t="n">
-        <v>426.4</v>
+        <v>573.74</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.79</v>
+        <v>-46.34</v>
       </c>
       <c r="K31" t="n">
-        <v>181.07</v>
+        <v>291.48</v>
       </c>
       <c r="L31" t="n">
-        <v>183.34</v>
+        <v>295.14</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>353.18</v>
+        <v>433.64</v>
       </c>
       <c r="K32" t="n">
-        <v>276.85</v>
+        <v>339.93</v>
       </c>
       <c r="L32" t="n">
-        <v>448.76</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.89</v>
+        <v>-53.35</v>
       </c>
       <c r="K33" t="n">
-        <v>-434.83</v>
+        <v>-540.9400000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>436.94</v>
+        <v>543.5700000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-115.04</v>
+        <v>-180.6</v>
       </c>
       <c r="K34" t="n">
-        <v>220.56</v>
+        <v>346.25</v>
       </c>
       <c r="L34" t="n">
-        <v>248.76</v>
+        <v>390.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-353.15</v>
+        <v>-547.23</v>
       </c>
       <c r="K35" t="n">
-        <v>103.87</v>
+        <v>160.96</v>
       </c>
       <c r="L35" t="n">
-        <v>368.11</v>
+        <v>570.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>219.12</v>
+        <v>425.06</v>
       </c>
       <c r="K36" t="n">
-        <v>198.58</v>
+        <v>385.21</v>
       </c>
       <c r="L36" t="n">
-        <v>295.71</v>
+        <v>573.64</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>551.08</v>
+        <v>840.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-373.44</v>
+        <v>-569.24</v>
       </c>
       <c r="L37" t="n">
-        <v>665.7</v>
+        <v>1014.72</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>267.69</v>
+        <v>479.53</v>
       </c>
       <c r="K38" t="n">
-        <v>-607.11</v>
+        <v>-1087.57</v>
       </c>
       <c r="L38" t="n">
-        <v>663.5</v>
+        <v>1188.6</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>359.75</v>
+        <v>815.1900000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.35</v>
+        <v>-14.38</v>
       </c>
       <c r="L39" t="n">
-        <v>359.81</v>
+        <v>815.3200000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-564.14</v>
+        <v>-1044.12</v>
       </c>
       <c r="K40" t="n">
-        <v>124.76</v>
+        <v>230.91</v>
       </c>
       <c r="L40" t="n">
-        <v>577.77</v>
+        <v>1069.35</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-198.71</v>
+        <v>-267.83</v>
       </c>
       <c r="K41" t="n">
-        <v>-1411.09</v>
+        <v>-1901.91</v>
       </c>
       <c r="L41" t="n">
-        <v>1425.01</v>
+        <v>1920.68</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-433.16</v>
+        <v>-705.33</v>
       </c>
       <c r="K42" t="n">
-        <v>958.02</v>
+        <v>1559.96</v>
       </c>
       <c r="L42" t="n">
-        <v>1051.39</v>
+        <v>1712.01</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-495.46</v>
+        <v>-1047.12</v>
       </c>
       <c r="K43" t="n">
-        <v>-99.13</v>
+        <v>-209.5</v>
       </c>
       <c r="L43" t="n">
-        <v>505.28</v>
+        <v>1067.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>226.03</v>
+        <v>310.44</v>
       </c>
       <c r="K44" t="n">
-        <v>-306.73</v>
+        <v>-421.29</v>
       </c>
       <c r="L44" t="n">
-        <v>381.02</v>
+        <v>523.3099999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-180.06</v>
+        <v>-241.08</v>
       </c>
       <c r="K45" t="n">
-        <v>372.38</v>
+        <v>498.58</v>
       </c>
       <c r="L45" t="n">
-        <v>413.63</v>
+        <v>553.8099999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-269.12</v>
+        <v>-436.46</v>
       </c>
       <c r="K46" t="n">
-        <v>79.2</v>
+        <v>128.45</v>
       </c>
       <c r="L46" t="n">
-        <v>280.53</v>
+        <v>454.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>20.08</v>
+        <v>23.54</v>
       </c>
       <c r="K47" t="n">
-        <v>-744.13</v>
+        <v>-872.29</v>
       </c>
       <c r="L47" t="n">
-        <v>744.41</v>
+        <v>872.6</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>129.72</v>
+        <v>175.93</v>
       </c>
       <c r="K48" t="n">
-        <v>561.37</v>
+        <v>761.33</v>
       </c>
       <c r="L48" t="n">
-        <v>576.16</v>
+        <v>781.39</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>162.42</v>
+        <v>345.09</v>
       </c>
       <c r="K49" t="n">
-        <v>-130.32</v>
+        <v>-276.88</v>
       </c>
       <c r="L49" t="n">
-        <v>208.24</v>
+        <v>442.44</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-361.52</v>
+        <v>-637.88</v>
       </c>
       <c r="K50" t="n">
-        <v>126.15</v>
+        <v>222.58</v>
       </c>
       <c r="L50" t="n">
-        <v>382.89</v>
+        <v>675.6</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>166.79</v>
+        <v>250.22</v>
       </c>
       <c r="K51" t="n">
-        <v>-401.74</v>
+        <v>-602.7</v>
       </c>
       <c r="L51" t="n">
-        <v>434.99</v>
+        <v>652.5700000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>416.34</v>
+        <v>544.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-126.79</v>
+        <v>-165.67</v>
       </c>
       <c r="L52" t="n">
-        <v>435.22</v>
+        <v>568.67</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>231.35</v>
+        <v>452.8</v>
       </c>
       <c r="K53" t="n">
-        <v>-313.87</v>
+        <v>-614.3200000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>389.92</v>
+        <v>763.16</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>546.63</v>
+        <v>1013.59</v>
       </c>
       <c r="K54" t="n">
-        <v>-116.52</v>
+        <v>-216.06</v>
       </c>
       <c r="L54" t="n">
-        <v>558.91</v>
+        <v>1036.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-234.6</v>
+        <v>-674.38</v>
       </c>
       <c r="K55" t="n">
-        <v>-85.34999999999999</v>
+        <v>-245.34</v>
       </c>
       <c r="L55" t="n">
-        <v>249.65</v>
+        <v>717.62</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-698.46</v>
+        <v>-963.1</v>
       </c>
       <c r="K56" t="n">
-        <v>2028.23</v>
+        <v>2796.69</v>
       </c>
       <c r="L56" t="n">
-        <v>2145.13</v>
+        <v>2957.87</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-388.53</v>
+        <v>-836.3200000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>480.13</v>
+        <v>1033.48</v>
       </c>
       <c r="L57" t="n">
-        <v>617.64</v>
+        <v>1329.48</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>350.63</v>
+        <v>599.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-1022.54</v>
+        <v>-1749.38</v>
       </c>
       <c r="L58" t="n">
-        <v>1080.99</v>
+        <v>1849.37</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.53</v>
+        <v>-16.4</v>
       </c>
       <c r="K59" t="n">
-        <v>-45.52</v>
+        <v>-164.95</v>
       </c>
       <c r="L59" t="n">
-        <v>45.74</v>
+        <v>165.77</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>251.28</v>
+        <v>367.71</v>
       </c>
       <c r="K60" t="n">
-        <v>94.73</v>
+        <v>138.63</v>
       </c>
       <c r="L60" t="n">
-        <v>268.54</v>
+        <v>392.98</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-381.36</v>
+        <v>-485.88</v>
       </c>
       <c r="K61" t="n">
-        <v>-96.43000000000001</v>
+        <v>-122.86</v>
       </c>
       <c r="L61" t="n">
-        <v>393.37</v>
+        <v>501.18</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>593.49</v>
+        <v>787.9299999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-275.01</v>
+        <v>-365.11</v>
       </c>
       <c r="L62" t="n">
-        <v>654.11</v>
+        <v>868.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>201.71</v>
+        <v>272.1</v>
       </c>
       <c r="K63" t="n">
-        <v>-243.84</v>
+        <v>-328.92</v>
       </c>
       <c r="L63" t="n">
-        <v>316.46</v>
+        <v>426.88</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-179.14</v>
+        <v>-239.09</v>
       </c>
       <c r="K64" t="n">
-        <v>-364.52</v>
+        <v>-486.49</v>
       </c>
       <c r="L64" t="n">
-        <v>406.16</v>
+        <v>542.0599999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-27.05</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>113.97</v>
+        <v>315.55</v>
       </c>
       <c r="L65" t="n">
-        <v>117.14</v>
+        <v>324.32</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>161.14</v>
+        <v>302.24</v>
       </c>
       <c r="K66" t="n">
-        <v>252.12</v>
+        <v>472.88</v>
       </c>
       <c r="L66" t="n">
-        <v>299.22</v>
+        <v>561.22</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>480.41</v>
+        <v>712.0599999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-427.74</v>
+        <v>-633.98</v>
       </c>
       <c r="L67" t="n">
-        <v>643.24</v>
+        <v>953.4</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-1692.38</v>
+        <v>-2200.09</v>
       </c>
       <c r="K68" t="n">
-        <v>-724.78</v>
+        <v>-942.22</v>
       </c>
       <c r="L68" t="n">
-        <v>1841.04</v>
+        <v>2393.36</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-135.84</v>
+        <v>-328.38</v>
       </c>
       <c r="K69" t="n">
-        <v>-253.61</v>
+        <v>-613.0700000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>287.7</v>
+        <v>695.47</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>603.11</v>
+        <v>1042.93</v>
       </c>
       <c r="K70" t="n">
-        <v>351.22</v>
+        <v>607.35</v>
       </c>
       <c r="L70" t="n">
-        <v>697.92</v>
+        <v>1206.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-795.52</v>
+        <v>-1238.27</v>
       </c>
       <c r="K71" t="n">
-        <v>-911.59</v>
+        <v>-1418.93</v>
       </c>
       <c r="L71" t="n">
-        <v>1209.89</v>
+        <v>1883.26</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-377.52</v>
+        <v>-888.58</v>
       </c>
       <c r="K72" t="n">
-        <v>-44.6</v>
+        <v>-104.98</v>
       </c>
       <c r="L72" t="n">
-        <v>380.14</v>
+        <v>894.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>940.77</v>
+        <v>1627.12</v>
       </c>
       <c r="K73" t="n">
-        <v>91.17</v>
+        <v>157.68</v>
       </c>
       <c r="L73" t="n">
-        <v>945.1799999999999</v>
+        <v>1634.74</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>439.83</v>
+        <v>537.61</v>
       </c>
       <c r="K74" t="n">
-        <v>-92.54000000000001</v>
+        <v>-113.11</v>
       </c>
       <c r="L74" t="n">
-        <v>449.46</v>
+        <v>549.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-87.70999999999999</v>
+        <v>-123.76</v>
       </c>
       <c r="K75" t="n">
-        <v>332.14</v>
+        <v>468.67</v>
       </c>
       <c r="L75" t="n">
-        <v>343.53</v>
+        <v>484.74</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>481.29</v>
+        <v>576.21</v>
       </c>
       <c r="K76" t="n">
-        <v>128.99</v>
+        <v>154.43</v>
       </c>
       <c r="L76" t="n">
-        <v>498.28</v>
+        <v>596.54</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>258.43</v>
+        <v>400.81</v>
       </c>
       <c r="K77" t="n">
-        <v>-155.01</v>
+        <v>-240.41</v>
       </c>
       <c r="L77" t="n">
-        <v>301.35</v>
+        <v>467.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-126.93</v>
+        <v>-173.14</v>
       </c>
       <c r="K78" t="n">
-        <v>-420.67</v>
+        <v>-573.8099999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>439.41</v>
+        <v>599.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>9.9</v>
+        <v>35.33</v>
       </c>
       <c r="K79" t="n">
-        <v>79.70999999999999</v>
+        <v>284.35</v>
       </c>
       <c r="L79" t="n">
-        <v>80.33</v>
+        <v>286.53</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-213.82</v>
+        <v>-309.11</v>
       </c>
       <c r="K80" t="n">
-        <v>465.22</v>
+        <v>672.55</v>
       </c>
       <c r="L80" t="n">
-        <v>512.01</v>
+        <v>740.1799999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-485.58</v>
+        <v>-660.1900000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-831.9299999999999</v>
+        <v>-1131.07</v>
       </c>
       <c r="L81" t="n">
-        <v>963.27</v>
+        <v>1309.65</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>479.85</v>
+        <v>705.34</v>
       </c>
       <c r="K82" t="n">
-        <v>97.04000000000001</v>
+        <v>142.64</v>
       </c>
       <c r="L82" t="n">
-        <v>489.56</v>
+        <v>719.61</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>453.76</v>
+        <v>759.33</v>
       </c>
       <c r="K83" t="n">
-        <v>-579.24</v>
+        <v>-969.3</v>
       </c>
       <c r="L83" t="n">
-        <v>735.8099999999999</v>
+        <v>1231.31</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>748.5599999999999</v>
+        <v>1111.22</v>
       </c>
       <c r="K84" t="n">
-        <v>-1013.56</v>
+        <v>-1504.6</v>
       </c>
       <c r="L84" t="n">
-        <v>1260.02</v>
+        <v>1870.47</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-502.02</v>
+        <v>-1015.94</v>
       </c>
       <c r="K85" t="n">
-        <v>-93.05</v>
+        <v>-188.31</v>
       </c>
       <c r="L85" t="n">
-        <v>510.57</v>
+        <v>1033.24</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-790.03</v>
+        <v>-1145.82</v>
       </c>
       <c r="K86" t="n">
-        <v>-907.71</v>
+        <v>-1316.5</v>
       </c>
       <c r="L86" t="n">
-        <v>1203.37</v>
+        <v>1745.3</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>256.38</v>
+        <v>458.33</v>
       </c>
       <c r="K87" t="n">
-        <v>-587.78</v>
+        <v>-1050.75</v>
       </c>
       <c r="L87" t="n">
-        <v>641.27</v>
+        <v>1146.36</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>962.98</v>
+        <v>1653.17</v>
       </c>
       <c r="K88" t="n">
-        <v>250.31</v>
+        <v>429.71</v>
       </c>
       <c r="L88" t="n">
-        <v>994.98</v>
+        <v>1708.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-337.43</v>
+        <v>-204.82</v>
       </c>
       <c r="K14" t="n">
-        <v>127.46</v>
+        <v>77.37</v>
       </c>
       <c r="L14" t="n">
-        <v>360.7</v>
+        <v>218.95</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-174.69</v>
+        <v>-100.86</v>
       </c>
       <c r="K15" t="n">
-        <v>344.22</v>
+        <v>198.76</v>
       </c>
       <c r="L15" t="n">
-        <v>386.01</v>
+        <v>222.88</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-205.8</v>
+        <v>-123.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-207.41</v>
+        <v>-124.26</v>
       </c>
       <c r="L16" t="n">
-        <v>292.19</v>
+        <v>175.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-326.45</v>
+        <v>-194.79</v>
       </c>
       <c r="K17" t="n">
-        <v>473.07</v>
+        <v>282.28</v>
       </c>
       <c r="L17" t="n">
-        <v>574.78</v>
+        <v>342.96</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-166.47</v>
+        <v>-95.58</v>
       </c>
       <c r="K18" t="n">
-        <v>429.03</v>
+        <v>246.32</v>
       </c>
       <c r="L18" t="n">
-        <v>460.2</v>
+        <v>264.21</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-627.96</v>
+        <v>-383.04</v>
       </c>
       <c r="K19" t="n">
-        <v>69.72</v>
+        <v>42.52</v>
       </c>
       <c r="L19" t="n">
-        <v>631.8200000000001</v>
+        <v>385.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>413.35</v>
+        <v>211.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-414.06</v>
+        <v>-212.23</v>
       </c>
       <c r="L20" t="n">
-        <v>585.0599999999999</v>
+        <v>299.88</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-189.76</v>
+        <v>-98.27</v>
       </c>
       <c r="K21" t="n">
-        <v>507.9</v>
+        <v>263.03</v>
       </c>
       <c r="L21" t="n">
-        <v>542.1900000000001</v>
+        <v>280.78</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>571.0599999999999</v>
+        <v>307.83</v>
       </c>
       <c r="K22" t="n">
-        <v>224.34</v>
+        <v>120.93</v>
       </c>
       <c r="L22" t="n">
-        <v>613.55</v>
+        <v>330.74</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>31.94</v>
+        <v>14.29</v>
       </c>
       <c r="K23" t="n">
-        <v>-720.3200000000001</v>
+        <v>-322.23</v>
       </c>
       <c r="L23" t="n">
-        <v>721.02</v>
+        <v>322.54</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-1021.56</v>
+        <v>-460.4</v>
       </c>
       <c r="K24" t="n">
-        <v>-135.04</v>
+        <v>-60.86</v>
       </c>
       <c r="L24" t="n">
-        <v>1030.45</v>
+        <v>464.4</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>498.52</v>
+        <v>243.36</v>
       </c>
       <c r="K25" t="n">
-        <v>174.12</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
-        <v>528.05</v>
+        <v>257.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-76.89</v>
+        <v>-34.66</v>
       </c>
       <c r="K26" t="n">
-        <v>777.02</v>
+        <v>350.26</v>
       </c>
       <c r="L26" t="n">
-        <v>780.8099999999999</v>
+        <v>351.98</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-52.56</v>
+        <v>-22.05</v>
       </c>
       <c r="K27" t="n">
-        <v>-884.16</v>
+        <v>-370.97</v>
       </c>
       <c r="L27" t="n">
-        <v>885.72</v>
+        <v>371.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-385.42</v>
+        <v>-165.6</v>
       </c>
       <c r="K28" t="n">
-        <v>-710.62</v>
+        <v>-305.33</v>
       </c>
       <c r="L28" t="n">
-        <v>808.41</v>
+        <v>347.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-395.02</v>
+        <v>-260.96</v>
       </c>
       <c r="K29" t="n">
-        <v>69.40000000000001</v>
+        <v>45.85</v>
       </c>
       <c r="L29" t="n">
-        <v>401.07</v>
+        <v>264.95</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-228.55</v>
+        <v>-132.59</v>
       </c>
       <c r="K30" t="n">
-        <v>526.25</v>
+        <v>305.3</v>
       </c>
       <c r="L30" t="n">
-        <v>573.74</v>
+        <v>332.84</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-46.34</v>
+        <v>-30.79</v>
       </c>
       <c r="K31" t="n">
-        <v>291.48</v>
+        <v>193.68</v>
       </c>
       <c r="L31" t="n">
-        <v>295.14</v>
+        <v>196.12</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>433.64</v>
+        <v>270.72</v>
       </c>
       <c r="K32" t="n">
-        <v>339.93</v>
+        <v>212.21</v>
       </c>
       <c r="L32" t="n">
-        <v>551</v>
+        <v>343.98</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-53.35</v>
+        <v>-34.94</v>
       </c>
       <c r="K33" t="n">
-        <v>-540.9400000000001</v>
+        <v>-354.26</v>
       </c>
       <c r="L33" t="n">
-        <v>543.5700000000001</v>
+        <v>355.98</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-180.6</v>
+        <v>-111.95</v>
       </c>
       <c r="K34" t="n">
-        <v>346.25</v>
+        <v>214.63</v>
       </c>
       <c r="L34" t="n">
-        <v>390.52</v>
+        <v>242.08</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-547.23</v>
+        <v>-290.91</v>
       </c>
       <c r="K35" t="n">
-        <v>160.96</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>570.42</v>
+        <v>303.23</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>425.06</v>
+        <v>211.36</v>
       </c>
       <c r="K36" t="n">
-        <v>385.21</v>
+        <v>191.54</v>
       </c>
       <c r="L36" t="n">
-        <v>573.64</v>
+        <v>285.24</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>840.02</v>
+        <v>417.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-569.24</v>
+        <v>-282.59</v>
       </c>
       <c r="L37" t="n">
-        <v>1014.72</v>
+        <v>503.75</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>479.53</v>
+        <v>209.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-1087.57</v>
+        <v>-476.12</v>
       </c>
       <c r="L38" t="n">
-        <v>1188.6</v>
+        <v>520.35</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>815.1900000000001</v>
+        <v>384.53</v>
       </c>
       <c r="K39" t="n">
-        <v>-14.38</v>
+        <v>-6.78</v>
       </c>
       <c r="L39" t="n">
-        <v>815.3200000000001</v>
+        <v>384.59</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-1044.12</v>
+        <v>-449.91</v>
       </c>
       <c r="K40" t="n">
-        <v>230.91</v>
+        <v>99.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1069.35</v>
+        <v>460.78</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-267.83</v>
+        <v>-123.98</v>
       </c>
       <c r="K41" t="n">
-        <v>-1901.91</v>
+        <v>-880.38</v>
       </c>
       <c r="L41" t="n">
-        <v>1920.68</v>
+        <v>889.0599999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-705.33</v>
+        <v>-296.81</v>
       </c>
       <c r="K42" t="n">
-        <v>1559.96</v>
+        <v>656.46</v>
       </c>
       <c r="L42" t="n">
-        <v>1712.01</v>
+        <v>720.4400000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-1047.12</v>
+        <v>-465.1</v>
       </c>
       <c r="K43" t="n">
-        <v>-209.5</v>
+        <v>-93.05</v>
       </c>
       <c r="L43" t="n">
-        <v>1067.87</v>
+        <v>474.32</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>310.44</v>
+        <v>192.24</v>
       </c>
       <c r="K44" t="n">
-        <v>-421.29</v>
+        <v>-260.88</v>
       </c>
       <c r="L44" t="n">
-        <v>523.3099999999999</v>
+        <v>324.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-241.08</v>
+        <v>-146.01</v>
       </c>
       <c r="K45" t="n">
-        <v>498.58</v>
+        <v>301.97</v>
       </c>
       <c r="L45" t="n">
-        <v>553.8099999999999</v>
+        <v>335.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-436.46</v>
+        <v>-256.58</v>
       </c>
       <c r="K46" t="n">
-        <v>128.45</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>454.97</v>
+        <v>267.46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>23.54</v>
+        <v>13.54</v>
       </c>
       <c r="K47" t="n">
-        <v>-872.29</v>
+        <v>-501.67</v>
       </c>
       <c r="L47" t="n">
-        <v>872.6</v>
+        <v>501.85</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>175.93</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>761.33</v>
+        <v>429.35</v>
       </c>
       <c r="L48" t="n">
-        <v>781.39</v>
+        <v>440.66</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>345.09</v>
+        <v>191.61</v>
       </c>
       <c r="K49" t="n">
-        <v>-276.88</v>
+        <v>-153.73</v>
       </c>
       <c r="L49" t="n">
-        <v>442.44</v>
+        <v>245.66</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-637.88</v>
+        <v>-322.66</v>
       </c>
       <c r="K50" t="n">
-        <v>222.58</v>
+        <v>112.59</v>
       </c>
       <c r="L50" t="n">
-        <v>675.6</v>
+        <v>341.74</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>250.22</v>
+        <v>138.45</v>
       </c>
       <c r="K51" t="n">
-        <v>-602.7</v>
+        <v>-333.48</v>
       </c>
       <c r="L51" t="n">
-        <v>652.5700000000001</v>
+        <v>361.08</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>544.01</v>
+        <v>318.26</v>
       </c>
       <c r="K52" t="n">
-        <v>-165.67</v>
+        <v>-96.92</v>
       </c>
       <c r="L52" t="n">
-        <v>568.67</v>
+        <v>332.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>452.8</v>
+        <v>228.48</v>
       </c>
       <c r="K53" t="n">
-        <v>-614.3200000000001</v>
+        <v>-309.98</v>
       </c>
       <c r="L53" t="n">
-        <v>763.16</v>
+        <v>385.08</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>1013.59</v>
+        <v>466.23</v>
       </c>
       <c r="K54" t="n">
-        <v>-216.06</v>
+        <v>-99.38</v>
       </c>
       <c r="L54" t="n">
-        <v>1036.36</v>
+        <v>476.71</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-674.38</v>
+        <v>-296.23</v>
       </c>
       <c r="K55" t="n">
-        <v>-245.34</v>
+        <v>-107.77</v>
       </c>
       <c r="L55" t="n">
-        <v>717.62</v>
+        <v>315.23</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-963.1</v>
+        <v>-422.52</v>
       </c>
       <c r="K56" t="n">
-        <v>2796.69</v>
+        <v>1226.93</v>
       </c>
       <c r="L56" t="n">
-        <v>2957.87</v>
+        <v>1297.64</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-836.3200000000001</v>
+        <v>-340.21</v>
       </c>
       <c r="K57" t="n">
-        <v>1033.48</v>
+        <v>420.42</v>
       </c>
       <c r="L57" t="n">
-        <v>1329.48</v>
+        <v>540.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>599.86</v>
+        <v>234.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-1749.38</v>
+        <v>-684.28</v>
       </c>
       <c r="L58" t="n">
-        <v>1849.37</v>
+        <v>723.39</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-16.4</v>
+        <v>-9.99</v>
       </c>
       <c r="K59" t="n">
-        <v>-164.95</v>
+        <v>-100.5</v>
       </c>
       <c r="L59" t="n">
-        <v>165.77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>367.71</v>
+        <v>229.93</v>
       </c>
       <c r="K60" t="n">
-        <v>138.63</v>
+        <v>86.69</v>
       </c>
       <c r="L60" t="n">
-        <v>392.98</v>
+        <v>245.73</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-485.88</v>
+        <v>-311.46</v>
       </c>
       <c r="K61" t="n">
-        <v>-122.86</v>
+        <v>-78.75</v>
       </c>
       <c r="L61" t="n">
-        <v>501.18</v>
+        <v>321.26</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>787.9299999999999</v>
+        <v>434.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-365.11</v>
+        <v>-201.24</v>
       </c>
       <c r="L62" t="n">
-        <v>868.41</v>
+        <v>478.66</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>272.1</v>
+        <v>166.61</v>
       </c>
       <c r="K63" t="n">
-        <v>-328.92</v>
+        <v>-201.41</v>
       </c>
       <c r="L63" t="n">
-        <v>426.88</v>
+        <v>261.39</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-239.09</v>
+        <v>-144.09</v>
       </c>
       <c r="K64" t="n">
-        <v>-486.49</v>
+        <v>-293.2</v>
       </c>
       <c r="L64" t="n">
-        <v>542.0599999999999</v>
+        <v>326.69</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-74.90000000000001</v>
+        <v>-41.8</v>
       </c>
       <c r="K65" t="n">
-        <v>315.55</v>
+        <v>176.1</v>
       </c>
       <c r="L65" t="n">
-        <v>324.32</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>302.24</v>
+        <v>167.32</v>
       </c>
       <c r="K66" t="n">
-        <v>472.88</v>
+        <v>261.8</v>
       </c>
       <c r="L66" t="n">
-        <v>561.22</v>
+        <v>310.7</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>712.0599999999999</v>
+        <v>358.6</v>
       </c>
       <c r="K67" t="n">
-        <v>-633.98</v>
+        <v>-319.28</v>
       </c>
       <c r="L67" t="n">
-        <v>953.4</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-2200.09</v>
+        <v>-992.38</v>
       </c>
       <c r="K68" t="n">
-        <v>-942.22</v>
+        <v>-425</v>
       </c>
       <c r="L68" t="n">
-        <v>2393.36</v>
+        <v>1079.55</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-328.38</v>
+        <v>-155.82</v>
       </c>
       <c r="K69" t="n">
-        <v>-613.0700000000001</v>
+        <v>-290.91</v>
       </c>
       <c r="L69" t="n">
-        <v>695.47</v>
+        <v>330.01</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>1042.93</v>
+        <v>457.37</v>
       </c>
       <c r="K70" t="n">
-        <v>607.35</v>
+        <v>266.35</v>
       </c>
       <c r="L70" t="n">
-        <v>1206.89</v>
+        <v>529.27</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-1238.27</v>
+        <v>-548.36</v>
       </c>
       <c r="K71" t="n">
-        <v>-1418.93</v>
+        <v>-628.37</v>
       </c>
       <c r="L71" t="n">
-        <v>1883.26</v>
+        <v>834</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-888.58</v>
+        <v>-377.28</v>
       </c>
       <c r="K72" t="n">
-        <v>-104.98</v>
+        <v>-44.57</v>
       </c>
       <c r="L72" t="n">
-        <v>894.76</v>
+        <v>379.91</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>1627.12</v>
+        <v>703.45</v>
       </c>
       <c r="K73" t="n">
-        <v>157.68</v>
+        <v>68.17</v>
       </c>
       <c r="L73" t="n">
-        <v>1634.74</v>
+        <v>706.74</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>537.61</v>
+        <v>344.96</v>
       </c>
       <c r="K74" t="n">
-        <v>-113.11</v>
+        <v>-72.58</v>
       </c>
       <c r="L74" t="n">
-        <v>549.38</v>
+        <v>352.51</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-123.76</v>
+        <v>-78.84</v>
       </c>
       <c r="K75" t="n">
-        <v>468.67</v>
+        <v>298.54</v>
       </c>
       <c r="L75" t="n">
-        <v>484.74</v>
+        <v>308.78</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>576.21</v>
+        <v>369.2</v>
       </c>
       <c r="K76" t="n">
-        <v>154.43</v>
+        <v>98.95</v>
       </c>
       <c r="L76" t="n">
-        <v>596.54</v>
+        <v>382.23</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>400.81</v>
+        <v>229.73</v>
       </c>
       <c r="K77" t="n">
-        <v>-240.41</v>
+        <v>-137.8</v>
       </c>
       <c r="L77" t="n">
-        <v>467.38</v>
+        <v>267.89</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-173.14</v>
+        <v>-103.38</v>
       </c>
       <c r="K78" t="n">
-        <v>-573.8099999999999</v>
+        <v>-342.61</v>
       </c>
       <c r="L78" t="n">
-        <v>599.36</v>
+        <v>357.86</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>35.33</v>
+        <v>22.54</v>
       </c>
       <c r="K79" t="n">
-        <v>284.35</v>
+        <v>181.4</v>
       </c>
       <c r="L79" t="n">
-        <v>286.53</v>
+        <v>182.8</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-309.11</v>
+        <v>-159.1</v>
       </c>
       <c r="K80" t="n">
-        <v>672.55</v>
+        <v>346.17</v>
       </c>
       <c r="L80" t="n">
-        <v>740.1799999999999</v>
+        <v>380.99</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-660.1900000000001</v>
+        <v>-318.25</v>
       </c>
       <c r="K81" t="n">
-        <v>-1131.07</v>
+        <v>-545.25</v>
       </c>
       <c r="L81" t="n">
-        <v>1309.65</v>
+        <v>631.33</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>705.34</v>
+        <v>378.96</v>
       </c>
       <c r="K82" t="n">
-        <v>142.64</v>
+        <v>76.64</v>
       </c>
       <c r="L82" t="n">
-        <v>719.61</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>759.33</v>
+        <v>348.64</v>
       </c>
       <c r="K83" t="n">
-        <v>-969.3</v>
+        <v>-445.04</v>
       </c>
       <c r="L83" t="n">
-        <v>1231.31</v>
+        <v>565.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>1111.22</v>
+        <v>484.82</v>
       </c>
       <c r="K84" t="n">
-        <v>-1504.6</v>
+        <v>-656.45</v>
       </c>
       <c r="L84" t="n">
-        <v>1870.47</v>
+        <v>816.0700000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-1015.94</v>
+        <v>-434.76</v>
       </c>
       <c r="K85" t="n">
-        <v>-188.31</v>
+        <v>-80.59</v>
       </c>
       <c r="L85" t="n">
-        <v>1033.24</v>
+        <v>442.17</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-1145.82</v>
+        <v>-526.63</v>
       </c>
       <c r="K86" t="n">
-        <v>-1316.5</v>
+        <v>-605.0700000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>1745.3</v>
+        <v>802.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>458.33</v>
+        <v>210.86</v>
       </c>
       <c r="K87" t="n">
-        <v>-1050.75</v>
+        <v>-483.41</v>
       </c>
       <c r="L87" t="n">
-        <v>1146.36</v>
+        <v>527.39</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>1653.17</v>
+        <v>690.84</v>
       </c>
       <c r="K88" t="n">
-        <v>429.71</v>
+        <v>179.57</v>
       </c>
       <c r="L88" t="n">
-        <v>1708.1</v>
+        <v>713.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-204.82</v>
+        <v>-227.87</v>
       </c>
       <c r="K14" t="n">
-        <v>77.37</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>218.95</v>
+        <v>243.58</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-100.86</v>
+        <v>-113.06</v>
       </c>
       <c r="K15" t="n">
-        <v>198.76</v>
+        <v>222.78</v>
       </c>
       <c r="L15" t="n">
-        <v>222.88</v>
+        <v>249.83</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-123.29</v>
+        <v>-137.01</v>
       </c>
       <c r="K16" t="n">
-        <v>-124.26</v>
+        <v>-138.09</v>
       </c>
       <c r="L16" t="n">
-        <v>175.05</v>
+        <v>194.53</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-194.79</v>
+        <v>-217.01</v>
       </c>
       <c r="K17" t="n">
-        <v>282.28</v>
+        <v>314.47</v>
       </c>
       <c r="L17" t="n">
-        <v>342.96</v>
+        <v>382.08</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-95.58</v>
+        <v>-106.8</v>
       </c>
       <c r="K18" t="n">
-        <v>246.32</v>
+        <v>275.26</v>
       </c>
       <c r="L18" t="n">
-        <v>264.21</v>
+        <v>295.25</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-383.04</v>
+        <v>-423.75</v>
       </c>
       <c r="K19" t="n">
-        <v>42.52</v>
+        <v>47.04</v>
       </c>
       <c r="L19" t="n">
-        <v>385.39</v>
+        <v>426.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>211.87</v>
+        <v>243.2</v>
       </c>
       <c r="K20" t="n">
-        <v>-212.23</v>
+        <v>-243.62</v>
       </c>
       <c r="L20" t="n">
-        <v>299.88</v>
+        <v>344.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-98.27</v>
+        <v>-112.64</v>
       </c>
       <c r="K21" t="n">
-        <v>263.03</v>
+        <v>301.49</v>
       </c>
       <c r="L21" t="n">
-        <v>280.78</v>
+        <v>321.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>307.83</v>
+        <v>346.33</v>
       </c>
       <c r="K22" t="n">
-        <v>120.93</v>
+        <v>136.06</v>
       </c>
       <c r="L22" t="n">
-        <v>330.74</v>
+        <v>372.09</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>14.29</v>
+        <v>16.83</v>
       </c>
       <c r="K23" t="n">
-        <v>-322.23</v>
+        <v>-379.62</v>
       </c>
       <c r="L23" t="n">
-        <v>322.54</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-460.4</v>
+        <v>-531.25</v>
       </c>
       <c r="K24" t="n">
-        <v>-60.86</v>
+        <v>-70.22</v>
       </c>
       <c r="L24" t="n">
-        <v>464.4</v>
+        <v>535.87</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>243.36</v>
+        <v>284.76</v>
       </c>
       <c r="K25" t="n">
-        <v>85</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>257.78</v>
+        <v>301.63</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-34.66</v>
+        <v>-40.37</v>
       </c>
       <c r="K26" t="n">
-        <v>350.26</v>
+        <v>407.99</v>
       </c>
       <c r="L26" t="n">
-        <v>351.98</v>
+        <v>409.98</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-22.05</v>
+        <v>-26.75</v>
       </c>
       <c r="K27" t="n">
-        <v>-370.97</v>
+        <v>-450</v>
       </c>
       <c r="L27" t="n">
-        <v>371.62</v>
+        <v>450.79</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-165.6</v>
+        <v>-198.22</v>
       </c>
       <c r="K28" t="n">
-        <v>-305.33</v>
+        <v>-365.47</v>
       </c>
       <c r="L28" t="n">
-        <v>347.35</v>
+        <v>415.77</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-260.96</v>
+        <v>-288.15</v>
       </c>
       <c r="K29" t="n">
-        <v>45.85</v>
+        <v>50.63</v>
       </c>
       <c r="L29" t="n">
-        <v>264.95</v>
+        <v>292.57</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-132.59</v>
+        <v>-148.37</v>
       </c>
       <c r="K30" t="n">
-        <v>305.3</v>
+        <v>341.63</v>
       </c>
       <c r="L30" t="n">
-        <v>332.84</v>
+        <v>372.46</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-30.79</v>
+        <v>-33.94</v>
       </c>
       <c r="K31" t="n">
-        <v>193.68</v>
+        <v>213.44</v>
       </c>
       <c r="L31" t="n">
-        <v>196.12</v>
+        <v>216.12</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>270.72</v>
+        <v>297.32</v>
       </c>
       <c r="K32" t="n">
-        <v>212.21</v>
+        <v>233.06</v>
       </c>
       <c r="L32" t="n">
-        <v>343.98</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-34.94</v>
+        <v>-38.18</v>
       </c>
       <c r="K33" t="n">
-        <v>-354.26</v>
+        <v>-387.07</v>
       </c>
       <c r="L33" t="n">
-        <v>355.98</v>
+        <v>388.95</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-111.95</v>
+        <v>-124.16</v>
       </c>
       <c r="K34" t="n">
-        <v>214.63</v>
+        <v>238.05</v>
       </c>
       <c r="L34" t="n">
-        <v>242.08</v>
+        <v>268.49</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-290.91</v>
+        <v>-328.09</v>
       </c>
       <c r="K35" t="n">
-        <v>85.56999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="L35" t="n">
-        <v>303.23</v>
+        <v>341.98</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>211.36</v>
+        <v>243.14</v>
       </c>
       <c r="K36" t="n">
-        <v>191.54</v>
+        <v>220.35</v>
       </c>
       <c r="L36" t="n">
-        <v>285.24</v>
+        <v>328.14</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>417.02</v>
+        <v>480.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-282.59</v>
+        <v>-325.42</v>
       </c>
       <c r="L37" t="n">
-        <v>503.75</v>
+        <v>580.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>209.93</v>
+        <v>245.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-476.12</v>
+        <v>-557.77</v>
       </c>
       <c r="L38" t="n">
-        <v>520.35</v>
+        <v>609.58</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>384.53</v>
+        <v>445.26</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.78</v>
+        <v>-7.86</v>
       </c>
       <c r="L39" t="n">
-        <v>384.59</v>
+        <v>445.33</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-449.91</v>
+        <v>-530.9400000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>99.5</v>
+        <v>117.42</v>
       </c>
       <c r="L40" t="n">
-        <v>460.78</v>
+        <v>543.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-123.98</v>
+        <v>-144.46</v>
       </c>
       <c r="K41" t="n">
-        <v>-880.38</v>
+        <v>-1025.81</v>
       </c>
       <c r="L41" t="n">
-        <v>889.0599999999999</v>
+        <v>1035.94</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-296.81</v>
+        <v>-348.32</v>
       </c>
       <c r="K42" t="n">
-        <v>656.46</v>
+        <v>770.38</v>
       </c>
       <c r="L42" t="n">
-        <v>720.4400000000001</v>
+        <v>845.47</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-465.1</v>
+        <v>-545.78</v>
       </c>
       <c r="K43" t="n">
-        <v>-93.05</v>
+        <v>-109.19</v>
       </c>
       <c r="L43" t="n">
-        <v>474.32</v>
+        <v>556.6</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>192.24</v>
+        <v>214.39</v>
       </c>
       <c r="K44" t="n">
-        <v>-260.88</v>
+        <v>-290.95</v>
       </c>
       <c r="L44" t="n">
-        <v>324.06</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-146.01</v>
+        <v>-164.27</v>
       </c>
       <c r="K45" t="n">
-        <v>301.97</v>
+        <v>339.72</v>
       </c>
       <c r="L45" t="n">
-        <v>335.42</v>
+        <v>377.35</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-256.58</v>
+        <v>-291.53</v>
       </c>
       <c r="K46" t="n">
-        <v>75.51000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="L46" t="n">
-        <v>267.46</v>
+        <v>303.89</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>13.54</v>
+        <v>15.16</v>
       </c>
       <c r="K47" t="n">
-        <v>-501.67</v>
+        <v>-561.8200000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>501.85</v>
+        <v>562.02</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>99.20999999999999</v>
+        <v>111.22</v>
       </c>
       <c r="K48" t="n">
-        <v>429.35</v>
+        <v>481.33</v>
       </c>
       <c r="L48" t="n">
-        <v>440.66</v>
+        <v>494.01</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>191.61</v>
+        <v>217.73</v>
       </c>
       <c r="K49" t="n">
-        <v>-153.73</v>
+        <v>-174.69</v>
       </c>
       <c r="L49" t="n">
-        <v>245.66</v>
+        <v>279.15</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-322.66</v>
+        <v>-363.66</v>
       </c>
       <c r="K50" t="n">
-        <v>112.59</v>
+        <v>126.89</v>
       </c>
       <c r="L50" t="n">
-        <v>341.74</v>
+        <v>385.16</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>138.45</v>
+        <v>155.4</v>
       </c>
       <c r="K51" t="n">
-        <v>-333.48</v>
+        <v>-374.31</v>
       </c>
       <c r="L51" t="n">
-        <v>361.08</v>
+        <v>405.28</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>318.26</v>
+        <v>359.48</v>
       </c>
       <c r="K52" t="n">
-        <v>-96.92</v>
+        <v>-109.48</v>
       </c>
       <c r="L52" t="n">
-        <v>332.69</v>
+        <v>375.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>228.48</v>
+        <v>259.41</v>
       </c>
       <c r="K53" t="n">
-        <v>-309.98</v>
+        <v>-351.95</v>
       </c>
       <c r="L53" t="n">
-        <v>385.08</v>
+        <v>437.22</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>466.23</v>
+        <v>540.21</v>
       </c>
       <c r="K54" t="n">
-        <v>-99.38</v>
+        <v>-115.15</v>
       </c>
       <c r="L54" t="n">
-        <v>476.71</v>
+        <v>552.35</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-296.23</v>
+        <v>-347.7</v>
       </c>
       <c r="K55" t="n">
-        <v>-107.77</v>
+        <v>-126.5</v>
       </c>
       <c r="L55" t="n">
-        <v>315.23</v>
+        <v>370</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-422.52</v>
+        <v>-494.01</v>
       </c>
       <c r="K56" t="n">
-        <v>1226.93</v>
+        <v>1434.52</v>
       </c>
       <c r="L56" t="n">
-        <v>1297.64</v>
+        <v>1517.2</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-340.21</v>
+        <v>-402.9</v>
       </c>
       <c r="K57" t="n">
-        <v>420.42</v>
+        <v>497.89</v>
       </c>
       <c r="L57" t="n">
-        <v>540.83</v>
+        <v>640.49</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>234.64</v>
+        <v>278.88</v>
       </c>
       <c r="K58" t="n">
-        <v>-684.28</v>
+        <v>-813.3</v>
       </c>
       <c r="L58" t="n">
-        <v>723.39</v>
+        <v>859.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.99</v>
+        <v>-11.05</v>
       </c>
       <c r="K59" t="n">
-        <v>-100.5</v>
+        <v>-111.13</v>
       </c>
       <c r="L59" t="n">
-        <v>101</v>
+        <v>111.68</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>229.93</v>
+        <v>254.57</v>
       </c>
       <c r="K60" t="n">
-        <v>86.69</v>
+        <v>95.97</v>
       </c>
       <c r="L60" t="n">
-        <v>245.73</v>
+        <v>272.06</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-311.46</v>
+        <v>-343.61</v>
       </c>
       <c r="K61" t="n">
-        <v>-78.75</v>
+        <v>-86.88</v>
       </c>
       <c r="L61" t="n">
-        <v>321.26</v>
+        <v>354.43</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>434.3</v>
+        <v>497.16</v>
       </c>
       <c r="K62" t="n">
-        <v>-201.24</v>
+        <v>-230.37</v>
       </c>
       <c r="L62" t="n">
-        <v>478.66</v>
+        <v>547.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>166.61</v>
+        <v>184.23</v>
       </c>
       <c r="K63" t="n">
-        <v>-201.41</v>
+        <v>-222.7</v>
       </c>
       <c r="L63" t="n">
-        <v>261.39</v>
+        <v>289.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-144.09</v>
+        <v>-160.16</v>
       </c>
       <c r="K64" t="n">
-        <v>-293.2</v>
+        <v>-325.89</v>
       </c>
       <c r="L64" t="n">
-        <v>326.69</v>
+        <v>363.12</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-41.8</v>
+        <v>-47.53</v>
       </c>
       <c r="K65" t="n">
-        <v>176.1</v>
+        <v>200.23</v>
       </c>
       <c r="L65" t="n">
-        <v>181</v>
+        <v>205.79</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>167.32</v>
+        <v>190.02</v>
       </c>
       <c r="K66" t="n">
-        <v>261.8</v>
+        <v>297.31</v>
       </c>
       <c r="L66" t="n">
-        <v>310.7</v>
+        <v>352.85</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>358.6</v>
+        <v>409.09</v>
       </c>
       <c r="K67" t="n">
-        <v>-319.28</v>
+        <v>-364.23</v>
       </c>
       <c r="L67" t="n">
-        <v>480.14</v>
+        <v>547.74</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-992.38</v>
+        <v>-1164.42</v>
       </c>
       <c r="K68" t="n">
-        <v>-425</v>
+        <v>-498.68</v>
       </c>
       <c r="L68" t="n">
-        <v>1079.55</v>
+        <v>1266.71</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-155.82</v>
+        <v>-181.28</v>
       </c>
       <c r="K69" t="n">
-        <v>-290.91</v>
+        <v>-338.44</v>
       </c>
       <c r="L69" t="n">
-        <v>330.01</v>
+        <v>383.93</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>457.37</v>
+        <v>529.6900000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>266.35</v>
+        <v>308.46</v>
       </c>
       <c r="L70" t="n">
-        <v>529.27</v>
+        <v>612.96</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-548.36</v>
+        <v>-638.85</v>
       </c>
       <c r="K71" t="n">
-        <v>-628.37</v>
+        <v>-732.0700000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>834</v>
+        <v>971.63</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-377.28</v>
+        <v>-448.84</v>
       </c>
       <c r="K72" t="n">
-        <v>-44.57</v>
+        <v>-53.03</v>
       </c>
       <c r="L72" t="n">
-        <v>379.91</v>
+        <v>451.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>703.45</v>
+        <v>824.15</v>
       </c>
       <c r="K73" t="n">
-        <v>68.17</v>
+        <v>79.87</v>
       </c>
       <c r="L73" t="n">
-        <v>706.74</v>
+        <v>828.01</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>344.96</v>
+        <v>379.15</v>
       </c>
       <c r="K74" t="n">
-        <v>-72.58</v>
+        <v>-79.78</v>
       </c>
       <c r="L74" t="n">
-        <v>352.51</v>
+        <v>387.46</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-78.84</v>
+        <v>-87.38</v>
       </c>
       <c r="K75" t="n">
-        <v>298.54</v>
+        <v>330.91</v>
       </c>
       <c r="L75" t="n">
-        <v>308.78</v>
+        <v>342.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>369.2</v>
+        <v>409.44</v>
       </c>
       <c r="K76" t="n">
-        <v>98.95</v>
+        <v>109.73</v>
       </c>
       <c r="L76" t="n">
-        <v>382.23</v>
+        <v>423.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>229.73</v>
+        <v>257.07</v>
       </c>
       <c r="K77" t="n">
-        <v>-137.8</v>
+        <v>-154.2</v>
       </c>
       <c r="L77" t="n">
-        <v>267.89</v>
+        <v>299.77</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-103.38</v>
+        <v>-115.46</v>
       </c>
       <c r="K78" t="n">
-        <v>-342.61</v>
+        <v>-382.65</v>
       </c>
       <c r="L78" t="n">
-        <v>357.86</v>
+        <v>399.69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>22.54</v>
+        <v>25.35</v>
       </c>
       <c r="K79" t="n">
-        <v>181.4</v>
+        <v>204.06</v>
       </c>
       <c r="L79" t="n">
-        <v>182.8</v>
+        <v>205.63</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-159.1</v>
+        <v>-182.13</v>
       </c>
       <c r="K80" t="n">
-        <v>346.17</v>
+        <v>396.27</v>
       </c>
       <c r="L80" t="n">
-        <v>380.99</v>
+        <v>436.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-318.25</v>
+        <v>-366.73</v>
       </c>
       <c r="K81" t="n">
-        <v>-545.25</v>
+        <v>-628.3</v>
       </c>
       <c r="L81" t="n">
-        <v>631.33</v>
+        <v>727.5</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>378.96</v>
+        <v>426.69</v>
       </c>
       <c r="K82" t="n">
-        <v>76.64</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>386.63</v>
+        <v>435.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>348.64</v>
+        <v>402.07</v>
       </c>
       <c r="K83" t="n">
-        <v>-445.04</v>
+        <v>-513.24</v>
       </c>
       <c r="L83" t="n">
-        <v>565.34</v>
+        <v>651.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>484.82</v>
+        <v>566.86</v>
       </c>
       <c r="K84" t="n">
-        <v>-656.45</v>
+        <v>-767.53</v>
       </c>
       <c r="L84" t="n">
-        <v>816.0700000000001</v>
+        <v>954.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-434.76</v>
+        <v>-507.24</v>
       </c>
       <c r="K85" t="n">
-        <v>-80.59</v>
+        <v>-94.02</v>
       </c>
       <c r="L85" t="n">
-        <v>442.17</v>
+        <v>515.88</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-526.63</v>
+        <v>-620.76</v>
       </c>
       <c r="K86" t="n">
-        <v>-605.0700000000001</v>
+        <v>-713.23</v>
       </c>
       <c r="L86" t="n">
-        <v>802.15</v>
+        <v>945.54</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>210.86</v>
+        <v>246.63</v>
       </c>
       <c r="K87" t="n">
-        <v>-483.41</v>
+        <v>-565.42</v>
       </c>
       <c r="L87" t="n">
-        <v>527.39</v>
+        <v>616.87</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>690.84</v>
+        <v>812.86</v>
       </c>
       <c r="K88" t="n">
-        <v>179.57</v>
+        <v>211.29</v>
       </c>
       <c r="L88" t="n">
-        <v>713.8</v>
+        <v>839.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-227.87</v>
+        <v>-93.92</v>
       </c>
       <c r="K14" t="n">
-        <v>86.06999999999999</v>
+        <v>35.48</v>
       </c>
       <c r="L14" t="n">
-        <v>243.58</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-113.06</v>
+        <v>-46.62</v>
       </c>
       <c r="K15" t="n">
-        <v>222.78</v>
+        <v>91.87</v>
       </c>
       <c r="L15" t="n">
-        <v>249.83</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-137.01</v>
+        <v>-55.94</v>
       </c>
       <c r="K16" t="n">
-        <v>-138.09</v>
+        <v>-56.38</v>
       </c>
       <c r="L16" t="n">
-        <v>194.53</v>
+        <v>79.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-217.01</v>
+        <v>-97.11</v>
       </c>
       <c r="K17" t="n">
-        <v>314.47</v>
+        <v>140.73</v>
       </c>
       <c r="L17" t="n">
-        <v>382.08</v>
+        <v>170.98</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-106.8</v>
+        <v>-46.87</v>
       </c>
       <c r="K18" t="n">
-        <v>275.26</v>
+        <v>120.8</v>
       </c>
       <c r="L18" t="n">
-        <v>295.25</v>
+        <v>129.57</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-423.75</v>
+        <v>-183.7</v>
       </c>
       <c r="K19" t="n">
-        <v>47.04</v>
+        <v>20.39</v>
       </c>
       <c r="L19" t="n">
-        <v>426.36</v>
+        <v>184.83</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>243.2</v>
+        <v>116.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-243.62</v>
+        <v>-116.73</v>
       </c>
       <c r="L20" t="n">
-        <v>344.23</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-112.64</v>
+        <v>-53.91</v>
       </c>
       <c r="K21" t="n">
-        <v>301.49</v>
+        <v>144.31</v>
       </c>
       <c r="L21" t="n">
-        <v>321.84</v>
+        <v>154.05</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>346.33</v>
+        <v>166.03</v>
       </c>
       <c r="K22" t="n">
-        <v>136.06</v>
+        <v>65.23</v>
       </c>
       <c r="L22" t="n">
-        <v>372.09</v>
+        <v>178.38</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>16.83</v>
+        <v>7.82</v>
       </c>
       <c r="K23" t="n">
-        <v>-379.62</v>
+        <v>-176.32</v>
       </c>
       <c r="L23" t="n">
-        <v>379.99</v>
+        <v>176.49</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-531.25</v>
+        <v>-256.66</v>
       </c>
       <c r="K24" t="n">
-        <v>-70.22</v>
+        <v>-33.93</v>
       </c>
       <c r="L24" t="n">
-        <v>535.87</v>
+        <v>258.9</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>284.76</v>
+        <v>130.25</v>
       </c>
       <c r="K25" t="n">
-        <v>99.45999999999999</v>
+        <v>45.49</v>
       </c>
       <c r="L25" t="n">
-        <v>301.63</v>
+        <v>137.96</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-40.37</v>
+        <v>-22.26</v>
       </c>
       <c r="K26" t="n">
-        <v>407.99</v>
+        <v>224.99</v>
       </c>
       <c r="L26" t="n">
-        <v>409.98</v>
+        <v>226.09</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-26.75</v>
+        <v>-14.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-450</v>
+        <v>-244.13</v>
       </c>
       <c r="L27" t="n">
-        <v>450.79</v>
+        <v>244.56</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-198.22</v>
+        <v>-107.93</v>
       </c>
       <c r="K28" t="n">
-        <v>-365.47</v>
+        <v>-199</v>
       </c>
       <c r="L28" t="n">
-        <v>415.77</v>
+        <v>226.39</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-288.15</v>
+        <v>-118.81</v>
       </c>
       <c r="K29" t="n">
-        <v>50.63</v>
+        <v>20.87</v>
       </c>
       <c r="L29" t="n">
-        <v>292.57</v>
+        <v>120.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-148.37</v>
+        <v>-60.96</v>
       </c>
       <c r="K30" t="n">
-        <v>341.63</v>
+        <v>140.36</v>
       </c>
       <c r="L30" t="n">
-        <v>372.46</v>
+        <v>153.02</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-33.94</v>
+        <v>-13.93</v>
       </c>
       <c r="K31" t="n">
-        <v>213.44</v>
+        <v>87.61</v>
       </c>
       <c r="L31" t="n">
-        <v>216.12</v>
+        <v>88.70999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>297.32</v>
+        <v>129.85</v>
       </c>
       <c r="K32" t="n">
-        <v>233.06</v>
+        <v>101.79</v>
       </c>
       <c r="L32" t="n">
-        <v>377.78</v>
+        <v>164.99</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-38.18</v>
+        <v>-17.01</v>
       </c>
       <c r="K33" t="n">
-        <v>-387.07</v>
+        <v>-172.49</v>
       </c>
       <c r="L33" t="n">
-        <v>388.95</v>
+        <v>173.33</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-124.16</v>
+        <v>-54.79</v>
       </c>
       <c r="K34" t="n">
-        <v>238.05</v>
+        <v>105.04</v>
       </c>
       <c r="L34" t="n">
-        <v>268.49</v>
+        <v>118.47</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-328.09</v>
+        <v>-157.05</v>
       </c>
       <c r="K35" t="n">
-        <v>96.5</v>
+        <v>46.19</v>
       </c>
       <c r="L35" t="n">
-        <v>341.98</v>
+        <v>163.7</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>243.14</v>
+        <v>116.57</v>
       </c>
       <c r="K36" t="n">
-        <v>220.35</v>
+        <v>105.64</v>
       </c>
       <c r="L36" t="n">
-        <v>328.14</v>
+        <v>157.32</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>480.22</v>
+        <v>230.68</v>
       </c>
       <c r="K37" t="n">
-        <v>-325.42</v>
+        <v>-156.32</v>
       </c>
       <c r="L37" t="n">
-        <v>580.09</v>
+        <v>278.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>245.93</v>
+        <v>119.77</v>
       </c>
       <c r="K38" t="n">
-        <v>-557.77</v>
+        <v>-271.64</v>
       </c>
       <c r="L38" t="n">
-        <v>609.58</v>
+        <v>296.88</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>445.26</v>
+        <v>219.61</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.86</v>
+        <v>-3.87</v>
       </c>
       <c r="L39" t="n">
-        <v>445.33</v>
+        <v>219.64</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-530.9400000000001</v>
+        <v>-253.97</v>
       </c>
       <c r="K40" t="n">
-        <v>117.42</v>
+        <v>56.17</v>
       </c>
       <c r="L40" t="n">
-        <v>543.76</v>
+        <v>260.11</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-144.46</v>
+        <v>-80.19</v>
       </c>
       <c r="K41" t="n">
-        <v>-1025.81</v>
+        <v>-569.4299999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>1035.94</v>
+        <v>575.05</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-348.32</v>
+        <v>-194.59</v>
       </c>
       <c r="K42" t="n">
-        <v>770.38</v>
+        <v>430.37</v>
       </c>
       <c r="L42" t="n">
-        <v>845.47</v>
+        <v>472.32</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-545.78</v>
+        <v>-306.53</v>
       </c>
       <c r="K43" t="n">
-        <v>-109.19</v>
+        <v>-61.33</v>
       </c>
       <c r="L43" t="n">
-        <v>556.6</v>
+        <v>312.6</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>214.39</v>
+        <v>88.84</v>
       </c>
       <c r="K44" t="n">
-        <v>-290.95</v>
+        <v>-120.56</v>
       </c>
       <c r="L44" t="n">
-        <v>361.41</v>
+        <v>149.75</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-164.27</v>
+        <v>-67.81999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>339.72</v>
+        <v>140.27</v>
       </c>
       <c r="L45" t="n">
-        <v>377.35</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-291.53</v>
+        <v>-120.79</v>
       </c>
       <c r="K46" t="n">
-        <v>85.8</v>
+        <v>35.55</v>
       </c>
       <c r="L46" t="n">
-        <v>303.89</v>
+        <v>125.91</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>15.16</v>
+        <v>6.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-561.8200000000001</v>
+        <v>-245.94</v>
       </c>
       <c r="L47" t="n">
-        <v>562.02</v>
+        <v>246.03</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>111.22</v>
+        <v>50.08</v>
       </c>
       <c r="K48" t="n">
-        <v>481.33</v>
+        <v>216.71</v>
       </c>
       <c r="L48" t="n">
-        <v>494.01</v>
+        <v>222.42</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>217.73</v>
+        <v>98.41</v>
       </c>
       <c r="K49" t="n">
-        <v>-174.69</v>
+        <v>-78.95999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>279.15</v>
+        <v>126.17</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-363.66</v>
+        <v>-174.5</v>
       </c>
       <c r="K50" t="n">
-        <v>126.89</v>
+        <v>60.89</v>
       </c>
       <c r="L50" t="n">
-        <v>385.16</v>
+        <v>184.82</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>155.4</v>
+        <v>74.53</v>
       </c>
       <c r="K51" t="n">
-        <v>-374.31</v>
+        <v>-179.52</v>
       </c>
       <c r="L51" t="n">
-        <v>405.28</v>
+        <v>194.38</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>359.48</v>
+        <v>171.97</v>
       </c>
       <c r="K52" t="n">
-        <v>-109.48</v>
+        <v>-52.37</v>
       </c>
       <c r="L52" t="n">
-        <v>375.79</v>
+        <v>179.77</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>259.41</v>
+        <v>126.41</v>
       </c>
       <c r="K53" t="n">
-        <v>-351.95</v>
+        <v>-171.5</v>
       </c>
       <c r="L53" t="n">
-        <v>437.22</v>
+        <v>213.05</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>540.21</v>
+        <v>264.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-115.15</v>
+        <v>-56.41</v>
       </c>
       <c r="L54" t="n">
-        <v>552.35</v>
+        <v>270.58</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-347.7</v>
+        <v>-168.09</v>
       </c>
       <c r="K55" t="n">
-        <v>-126.5</v>
+        <v>-61.15</v>
       </c>
       <c r="L55" t="n">
-        <v>370</v>
+        <v>178.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-494.01</v>
+        <v>-281.6</v>
       </c>
       <c r="K56" t="n">
-        <v>1434.52</v>
+        <v>817.71</v>
       </c>
       <c r="L56" t="n">
-        <v>1517.2</v>
+        <v>864.84</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-402.9</v>
+        <v>-227.08</v>
       </c>
       <c r="K57" t="n">
-        <v>497.89</v>
+        <v>280.62</v>
       </c>
       <c r="L57" t="n">
-        <v>640.49</v>
+        <v>360.99</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>278.88</v>
+        <v>155.19</v>
       </c>
       <c r="K58" t="n">
-        <v>-813.3</v>
+        <v>-452.6</v>
       </c>
       <c r="L58" t="n">
-        <v>859.78</v>
+        <v>478.47</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-11.05</v>
+        <v>-1.02</v>
       </c>
       <c r="K59" t="n">
-        <v>-111.13</v>
+        <v>-10.22</v>
       </c>
       <c r="L59" t="n">
-        <v>111.68</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>254.57</v>
+        <v>104.69</v>
       </c>
       <c r="K60" t="n">
-        <v>95.97</v>
+        <v>39.47</v>
       </c>
       <c r="L60" t="n">
-        <v>272.06</v>
+        <v>111.88</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-343.61</v>
+        <v>-141.69</v>
       </c>
       <c r="K61" t="n">
-        <v>-86.88</v>
+        <v>-35.83</v>
       </c>
       <c r="L61" t="n">
-        <v>354.43</v>
+        <v>146.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>497.16</v>
+        <v>223.47</v>
       </c>
       <c r="K62" t="n">
-        <v>-230.37</v>
+        <v>-103.55</v>
       </c>
       <c r="L62" t="n">
-        <v>547.95</v>
+        <v>246.29</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>184.23</v>
+        <v>79.41</v>
       </c>
       <c r="K63" t="n">
-        <v>-222.7</v>
+        <v>-96</v>
       </c>
       <c r="L63" t="n">
-        <v>289.02</v>
+        <v>124.58</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-160.16</v>
+        <v>-70.65000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>-325.89</v>
+        <v>-143.76</v>
       </c>
       <c r="L64" t="n">
-        <v>363.12</v>
+        <v>160.18</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-47.53</v>
+        <v>-19.81</v>
       </c>
       <c r="K65" t="n">
-        <v>200.23</v>
+        <v>83.44</v>
       </c>
       <c r="L65" t="n">
-        <v>205.79</v>
+        <v>85.76000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>190.02</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>297.31</v>
+        <v>142.83</v>
       </c>
       <c r="L66" t="n">
-        <v>352.85</v>
+        <v>169.51</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>409.09</v>
+        <v>196.39</v>
       </c>
       <c r="K67" t="n">
-        <v>-364.23</v>
+        <v>-174.86</v>
       </c>
       <c r="L67" t="n">
-        <v>547.74</v>
+        <v>262.96</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-1164.42</v>
+        <v>-561.53</v>
       </c>
       <c r="K68" t="n">
-        <v>-498.68</v>
+        <v>-240.48</v>
       </c>
       <c r="L68" t="n">
-        <v>1266.71</v>
+        <v>610.86</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-181.28</v>
+        <v>-88.26000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-338.44</v>
+        <v>-164.78</v>
       </c>
       <c r="L69" t="n">
-        <v>383.93</v>
+        <v>186.92</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>529.6900000000001</v>
+        <v>257</v>
       </c>
       <c r="K70" t="n">
-        <v>308.46</v>
+        <v>149.66</v>
       </c>
       <c r="L70" t="n">
-        <v>612.96</v>
+        <v>297.4</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-638.85</v>
+        <v>-362.11</v>
       </c>
       <c r="K71" t="n">
-        <v>-732.0700000000001</v>
+        <v>-414.94</v>
       </c>
       <c r="L71" t="n">
-        <v>971.63</v>
+        <v>550.72</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-448.84</v>
+        <v>-247.99</v>
       </c>
       <c r="K72" t="n">
-        <v>-53.03</v>
+        <v>-29.3</v>
       </c>
       <c r="L72" t="n">
-        <v>451.96</v>
+        <v>249.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>824.15</v>
+        <v>467.46</v>
       </c>
       <c r="K73" t="n">
-        <v>79.87</v>
+        <v>45.3</v>
       </c>
       <c r="L73" t="n">
-        <v>828.01</v>
+        <v>469.65</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>379.15</v>
+        <v>156.23</v>
       </c>
       <c r="K74" t="n">
-        <v>-79.78</v>
+        <v>-32.87</v>
       </c>
       <c r="L74" t="n">
-        <v>387.46</v>
+        <v>159.65</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-87.38</v>
+        <v>-36.34</v>
       </c>
       <c r="K75" t="n">
-        <v>330.91</v>
+        <v>137.62</v>
       </c>
       <c r="L75" t="n">
-        <v>342.25</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>409.44</v>
+        <v>168.89</v>
       </c>
       <c r="K76" t="n">
-        <v>109.73</v>
+        <v>45.26</v>
       </c>
       <c r="L76" t="n">
-        <v>423.88</v>
+        <v>174.85</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>257.07</v>
+        <v>113.09</v>
       </c>
       <c r="K77" t="n">
-        <v>-154.2</v>
+        <v>-67.83</v>
       </c>
       <c r="L77" t="n">
-        <v>299.77</v>
+        <v>131.87</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-115.46</v>
+        <v>-51.62</v>
       </c>
       <c r="K78" t="n">
-        <v>-382.65</v>
+        <v>-171.08</v>
       </c>
       <c r="L78" t="n">
-        <v>399.69</v>
+        <v>178.7</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>25.35</v>
+        <v>2.63</v>
       </c>
       <c r="K79" t="n">
-        <v>204.06</v>
+        <v>21.21</v>
       </c>
       <c r="L79" t="n">
-        <v>205.63</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-182.13</v>
+        <v>-87.23</v>
       </c>
       <c r="K80" t="n">
-        <v>396.27</v>
+        <v>189.8</v>
       </c>
       <c r="L80" t="n">
-        <v>436.12</v>
+        <v>208.88</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-366.73</v>
+        <v>-175.95</v>
       </c>
       <c r="K81" t="n">
-        <v>-628.3</v>
+        <v>-301.44</v>
       </c>
       <c r="L81" t="n">
-        <v>727.5</v>
+        <v>349.04</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>426.69</v>
+        <v>204.63</v>
       </c>
       <c r="K82" t="n">
-        <v>86.29000000000001</v>
+        <v>41.38</v>
       </c>
       <c r="L82" t="n">
-        <v>435.33</v>
+        <v>208.77</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>402.07</v>
+        <v>197.74</v>
       </c>
       <c r="K83" t="n">
-        <v>-513.24</v>
+        <v>-252.42</v>
       </c>
       <c r="L83" t="n">
-        <v>651.98</v>
+        <v>320.65</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>566.86</v>
+        <v>278.13</v>
       </c>
       <c r="K84" t="n">
-        <v>-767.53</v>
+        <v>-376.59</v>
       </c>
       <c r="L84" t="n">
-        <v>954.16</v>
+        <v>468.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-507.24</v>
+        <v>-246.32</v>
       </c>
       <c r="K85" t="n">
-        <v>-94.02</v>
+        <v>-45.66</v>
       </c>
       <c r="L85" t="n">
-        <v>515.88</v>
+        <v>250.52</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-620.76</v>
+        <v>-347.64</v>
       </c>
       <c r="K86" t="n">
-        <v>-713.23</v>
+        <v>-399.43</v>
       </c>
       <c r="L86" t="n">
-        <v>945.54</v>
+        <v>529.52</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>246.63</v>
+        <v>137.95</v>
       </c>
       <c r="K87" t="n">
-        <v>-565.42</v>
+        <v>-316.26</v>
       </c>
       <c r="L87" t="n">
-        <v>616.87</v>
+        <v>345.04</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>812.86</v>
+        <v>458.07</v>
       </c>
       <c r="K88" t="n">
-        <v>211.29</v>
+        <v>119.07</v>
       </c>
       <c r="L88" t="n">
-        <v>839.87</v>
+        <v>473.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-93.92</v>
+        <v>-72.73999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>35.48</v>
+        <v>27.48</v>
       </c>
       <c r="L14" t="n">
-        <v>100.4</v>
+        <v>77.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.62</v>
+        <v>-36.14</v>
       </c>
       <c r="K15" t="n">
-        <v>91.87</v>
+        <v>71.22</v>
       </c>
       <c r="L15" t="n">
-        <v>103.02</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.94</v>
+        <v>-45.42</v>
       </c>
       <c r="K16" t="n">
-        <v>-56.38</v>
+        <v>-45.77</v>
       </c>
       <c r="L16" t="n">
-        <v>79.42</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-97.11</v>
+        <v>-77.39</v>
       </c>
       <c r="K17" t="n">
-        <v>140.73</v>
+        <v>112.14</v>
       </c>
       <c r="L17" t="n">
-        <v>170.98</v>
+        <v>136.25</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-46.87</v>
+        <v>-38.96</v>
       </c>
       <c r="K18" t="n">
-        <v>120.8</v>
+        <v>100.4</v>
       </c>
       <c r="L18" t="n">
-        <v>129.57</v>
+        <v>107.69</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-183.7</v>
+        <v>-147.2</v>
       </c>
       <c r="K19" t="n">
-        <v>20.39</v>
+        <v>16.34</v>
       </c>
       <c r="L19" t="n">
-        <v>184.83</v>
+        <v>148.11</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>116.53</v>
+        <v>114.89</v>
       </c>
       <c r="K20" t="n">
-        <v>-116.73</v>
+        <v>-115.08</v>
       </c>
       <c r="L20" t="n">
-        <v>164.94</v>
+        <v>162.61</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-53.91</v>
+        <v>-53.22</v>
       </c>
       <c r="K21" t="n">
-        <v>144.31</v>
+        <v>142.44</v>
       </c>
       <c r="L21" t="n">
-        <v>154.05</v>
+        <v>152.06</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>166.03</v>
+        <v>161.55</v>
       </c>
       <c r="K22" t="n">
-        <v>65.23</v>
+        <v>63.47</v>
       </c>
       <c r="L22" t="n">
-        <v>178.38</v>
+        <v>173.57</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>7.82</v>
+        <v>8.84</v>
       </c>
       <c r="K23" t="n">
-        <v>-176.32</v>
+        <v>-199.26</v>
       </c>
       <c r="L23" t="n">
-        <v>176.49</v>
+        <v>199.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-256.66</v>
+        <v>-284.92</v>
       </c>
       <c r="K24" t="n">
-        <v>-33.93</v>
+        <v>-37.66</v>
       </c>
       <c r="L24" t="n">
-        <v>258.9</v>
+        <v>287.4</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>130.25</v>
+        <v>149.53</v>
       </c>
       <c r="K25" t="n">
-        <v>45.49</v>
+        <v>52.23</v>
       </c>
       <c r="L25" t="n">
-        <v>137.96</v>
+        <v>158.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-22.26</v>
+        <v>-28.31</v>
       </c>
       <c r="K26" t="n">
-        <v>224.99</v>
+        <v>286.08</v>
       </c>
       <c r="L26" t="n">
-        <v>226.09</v>
+        <v>287.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-14.51</v>
+        <v>-17.68</v>
       </c>
       <c r="K27" t="n">
-        <v>-244.13</v>
+        <v>-297.44</v>
       </c>
       <c r="L27" t="n">
-        <v>244.56</v>
+        <v>297.97</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-107.93</v>
+        <v>-133.84</v>
       </c>
       <c r="K28" t="n">
-        <v>-199</v>
+        <v>-246.76</v>
       </c>
       <c r="L28" t="n">
-        <v>226.39</v>
+        <v>280.72</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-118.81</v>
+        <v>-89.81</v>
       </c>
       <c r="K29" t="n">
-        <v>20.87</v>
+        <v>15.78</v>
       </c>
       <c r="L29" t="n">
-        <v>120.63</v>
+        <v>91.19</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-60.96</v>
+        <v>-45.48</v>
       </c>
       <c r="K30" t="n">
-        <v>140.36</v>
+        <v>104.73</v>
       </c>
       <c r="L30" t="n">
-        <v>153.02</v>
+        <v>114.18</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.93</v>
+        <v>-11.05</v>
       </c>
       <c r="K31" t="n">
-        <v>87.61</v>
+        <v>69.48</v>
       </c>
       <c r="L31" t="n">
-        <v>88.70999999999999</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>129.85</v>
+        <v>105.12</v>
       </c>
       <c r="K32" t="n">
-        <v>101.79</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>164.99</v>
+        <v>133.57</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-17.01</v>
+        <v>-13.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-172.49</v>
+        <v>-137.35</v>
       </c>
       <c r="L33" t="n">
-        <v>173.33</v>
+        <v>138.02</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-54.79</v>
+        <v>-46.13</v>
       </c>
       <c r="K34" t="n">
-        <v>105.04</v>
+        <v>88.44</v>
       </c>
       <c r="L34" t="n">
-        <v>118.47</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-157.05</v>
+        <v>-154.42</v>
       </c>
       <c r="K35" t="n">
-        <v>46.19</v>
+        <v>45.42</v>
       </c>
       <c r="L35" t="n">
-        <v>163.7</v>
+        <v>160.96</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>116.57</v>
+        <v>117.6</v>
       </c>
       <c r="K36" t="n">
-        <v>105.64</v>
+        <v>106.58</v>
       </c>
       <c r="L36" t="n">
-        <v>157.32</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>230.68</v>
+        <v>219.62</v>
       </c>
       <c r="K37" t="n">
-        <v>-156.32</v>
+        <v>-148.82</v>
       </c>
       <c r="L37" t="n">
-        <v>278.66</v>
+        <v>265.29</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>119.77</v>
+        <v>133.26</v>
       </c>
       <c r="K38" t="n">
-        <v>-271.64</v>
+        <v>-302.23</v>
       </c>
       <c r="L38" t="n">
-        <v>296.88</v>
+        <v>330.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>219.61</v>
+        <v>257.85</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.87</v>
+        <v>-4.55</v>
       </c>
       <c r="L39" t="n">
-        <v>219.64</v>
+        <v>257.89</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-253.97</v>
+        <v>-282.93</v>
       </c>
       <c r="K40" t="n">
-        <v>56.17</v>
+        <v>62.57</v>
       </c>
       <c r="L40" t="n">
-        <v>260.11</v>
+        <v>289.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-80.19</v>
+        <v>-92.66</v>
       </c>
       <c r="K41" t="n">
-        <v>-569.4299999999999</v>
+        <v>-658.01</v>
       </c>
       <c r="L41" t="n">
-        <v>575.05</v>
+        <v>664.5</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-194.59</v>
+        <v>-233.55</v>
       </c>
       <c r="K42" t="n">
-        <v>430.37</v>
+        <v>516.54</v>
       </c>
       <c r="L42" t="n">
-        <v>472.32</v>
+        <v>566.88</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-306.53</v>
+        <v>-392.94</v>
       </c>
       <c r="K43" t="n">
-        <v>-61.33</v>
+        <v>-78.62</v>
       </c>
       <c r="L43" t="n">
-        <v>312.6</v>
+        <v>400.73</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>88.84</v>
+        <v>65.37</v>
       </c>
       <c r="K44" t="n">
-        <v>-120.56</v>
+        <v>-88.72</v>
       </c>
       <c r="L44" t="n">
-        <v>149.75</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-67.81999999999999</v>
+        <v>-50.06</v>
       </c>
       <c r="K45" t="n">
-        <v>140.27</v>
+        <v>103.52</v>
       </c>
       <c r="L45" t="n">
-        <v>155.8</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-120.79</v>
+        <v>-91.45999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>35.55</v>
+        <v>26.92</v>
       </c>
       <c r="L46" t="n">
-        <v>125.91</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>6.64</v>
+        <v>5.21</v>
       </c>
       <c r="K47" t="n">
-        <v>-245.94</v>
+        <v>-193.09</v>
       </c>
       <c r="L47" t="n">
-        <v>246.03</v>
+        <v>193.16</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>50.08</v>
+        <v>39.15</v>
       </c>
       <c r="K48" t="n">
-        <v>216.71</v>
+        <v>169.43</v>
       </c>
       <c r="L48" t="n">
-        <v>222.42</v>
+        <v>173.9</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>98.41</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-78.95999999999999</v>
+        <v>-66.98</v>
       </c>
       <c r="L49" t="n">
-        <v>126.17</v>
+        <v>107.04</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-174.5</v>
+        <v>-172.59</v>
       </c>
       <c r="K50" t="n">
-        <v>60.89</v>
+        <v>60.22</v>
       </c>
       <c r="L50" t="n">
-        <v>184.82</v>
+        <v>182.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>74.53</v>
+        <v>72.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-179.52</v>
+        <v>-174.44</v>
       </c>
       <c r="L51" t="n">
-        <v>194.38</v>
+        <v>188.87</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>171.97</v>
+        <v>165.88</v>
       </c>
       <c r="K52" t="n">
-        <v>-52.37</v>
+        <v>-50.52</v>
       </c>
       <c r="L52" t="n">
-        <v>179.77</v>
+        <v>173.4</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>126.41</v>
+        <v>145.77</v>
       </c>
       <c r="K53" t="n">
-        <v>-171.5</v>
+        <v>-197.77</v>
       </c>
       <c r="L53" t="n">
-        <v>213.05</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>264.63</v>
+        <v>298.97</v>
       </c>
       <c r="K54" t="n">
-        <v>-56.41</v>
+        <v>-63.73</v>
       </c>
       <c r="L54" t="n">
-        <v>270.58</v>
+        <v>305.68</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-168.09</v>
+        <v>-201.65</v>
       </c>
       <c r="K55" t="n">
-        <v>-61.15</v>
+        <v>-73.36</v>
       </c>
       <c r="L55" t="n">
-        <v>178.87</v>
+        <v>214.58</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-281.6</v>
+        <v>-289.2</v>
       </c>
       <c r="K56" t="n">
-        <v>817.71</v>
+        <v>839.8099999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>864.84</v>
+        <v>888.21</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-227.08</v>
+        <v>-282.17</v>
       </c>
       <c r="K57" t="n">
-        <v>280.62</v>
+        <v>348.69</v>
       </c>
       <c r="L57" t="n">
-        <v>360.99</v>
+        <v>448.55</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>155.19</v>
+        <v>185.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-452.6</v>
+        <v>-541.39</v>
       </c>
       <c r="L58" t="n">
-        <v>478.47</v>
+        <v>572.34</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.02</v>
+        <v>-0.84</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.22</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>10.27</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>104.69</v>
+        <v>80.17</v>
       </c>
       <c r="K60" t="n">
-        <v>39.47</v>
+        <v>30.23</v>
       </c>
       <c r="L60" t="n">
-        <v>111.88</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-141.69</v>
+        <v>-104.52</v>
       </c>
       <c r="K61" t="n">
-        <v>-35.83</v>
+        <v>-26.43</v>
       </c>
       <c r="L61" t="n">
-        <v>146.15</v>
+        <v>107.81</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>223.47</v>
+        <v>173.02</v>
       </c>
       <c r="K62" t="n">
-        <v>-103.55</v>
+        <v>-80.17</v>
       </c>
       <c r="L62" t="n">
-        <v>246.29</v>
+        <v>190.69</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>79.41</v>
+        <v>66.62</v>
       </c>
       <c r="K63" t="n">
-        <v>-96</v>
+        <v>-80.54000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>124.58</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-70.65000000000001</v>
+        <v>-57.12</v>
       </c>
       <c r="K64" t="n">
-        <v>-143.76</v>
+        <v>-116.23</v>
       </c>
       <c r="L64" t="n">
-        <v>160.18</v>
+        <v>129.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-19.81</v>
+        <v>-18.72</v>
       </c>
       <c r="K65" t="n">
-        <v>83.44</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>85.76000000000001</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>91.29000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="K66" t="n">
-        <v>142.83</v>
+        <v>143.69</v>
       </c>
       <c r="L66" t="n">
-        <v>169.51</v>
+        <v>170.53</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>196.39</v>
+        <v>185.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-174.86</v>
+        <v>-165.53</v>
       </c>
       <c r="L67" t="n">
-        <v>262.96</v>
+        <v>248.93</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-561.53</v>
+        <v>-486.34</v>
       </c>
       <c r="K68" t="n">
-        <v>-240.48</v>
+        <v>-208.28</v>
       </c>
       <c r="L68" t="n">
-        <v>610.86</v>
+        <v>529.0700000000001</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-88.26000000000001</v>
+        <v>-104.27</v>
       </c>
       <c r="K69" t="n">
-        <v>-164.78</v>
+        <v>-194.66</v>
       </c>
       <c r="L69" t="n">
-        <v>186.92</v>
+        <v>220.83</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>257</v>
+        <v>283.17</v>
       </c>
       <c r="K70" t="n">
-        <v>149.66</v>
+        <v>164.9</v>
       </c>
       <c r="L70" t="n">
-        <v>297.4</v>
+        <v>327.68</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-362.11</v>
+        <v>-403.37</v>
       </c>
       <c r="K71" t="n">
-        <v>-414.94</v>
+        <v>-462.22</v>
       </c>
       <c r="L71" t="n">
-        <v>550.72</v>
+        <v>613.48</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-247.99</v>
+        <v>-315.89</v>
       </c>
       <c r="K72" t="n">
-        <v>-29.3</v>
+        <v>-37.32</v>
       </c>
       <c r="L72" t="n">
-        <v>249.71</v>
+        <v>318.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>467.46</v>
+        <v>528.5700000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>45.3</v>
+        <v>51.22</v>
       </c>
       <c r="L73" t="n">
-        <v>469.65</v>
+        <v>531.05</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>156.23</v>
+        <v>114.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-32.87</v>
+        <v>-24.08</v>
       </c>
       <c r="L74" t="n">
-        <v>159.65</v>
+        <v>116.97</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-36.34</v>
+        <v>-26.65</v>
       </c>
       <c r="K75" t="n">
-        <v>137.62</v>
+        <v>100.92</v>
       </c>
       <c r="L75" t="n">
-        <v>142.34</v>
+        <v>104.37</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>168.89</v>
+        <v>122.56</v>
       </c>
       <c r="K76" t="n">
-        <v>45.26</v>
+        <v>32.85</v>
       </c>
       <c r="L76" t="n">
-        <v>174.85</v>
+        <v>126.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>113.09</v>
+        <v>94.28</v>
       </c>
       <c r="K77" t="n">
-        <v>-67.83</v>
+        <v>-56.55</v>
       </c>
       <c r="L77" t="n">
-        <v>131.87</v>
+        <v>109.94</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-51.62</v>
+        <v>-41.15</v>
       </c>
       <c r="K78" t="n">
-        <v>-171.08</v>
+        <v>-136.37</v>
       </c>
       <c r="L78" t="n">
-        <v>178.7</v>
+        <v>142.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="K79" t="n">
-        <v>21.21</v>
+        <v>16.41</v>
       </c>
       <c r="L79" t="n">
-        <v>21.37</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-87.23</v>
+        <v>-83.66</v>
       </c>
       <c r="K80" t="n">
-        <v>189.8</v>
+        <v>182.02</v>
       </c>
       <c r="L80" t="n">
-        <v>208.88</v>
+        <v>200.32</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-175.95</v>
+        <v>-162.37</v>
       </c>
       <c r="K81" t="n">
-        <v>-301.44</v>
+        <v>-278.18</v>
       </c>
       <c r="L81" t="n">
-        <v>349.04</v>
+        <v>322.09</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>204.63</v>
+        <v>196.82</v>
       </c>
       <c r="K82" t="n">
-        <v>41.38</v>
+        <v>39.8</v>
       </c>
       <c r="L82" t="n">
-        <v>208.77</v>
+        <v>200.8</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>197.74</v>
+        <v>218.47</v>
       </c>
       <c r="K83" t="n">
-        <v>-252.42</v>
+        <v>-278.89</v>
       </c>
       <c r="L83" t="n">
-        <v>320.65</v>
+        <v>354.27</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>278.13</v>
+        <v>295.73</v>
       </c>
       <c r="K84" t="n">
-        <v>-376.59</v>
+        <v>-400.41</v>
       </c>
       <c r="L84" t="n">
-        <v>468.16</v>
+        <v>497.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-246.32</v>
+        <v>-279.53</v>
       </c>
       <c r="K85" t="n">
-        <v>-45.66</v>
+        <v>-51.81</v>
       </c>
       <c r="L85" t="n">
-        <v>250.52</v>
+        <v>284.29</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-347.64</v>
+        <v>-412.14</v>
       </c>
       <c r="K86" t="n">
-        <v>-399.43</v>
+        <v>-473.53</v>
       </c>
       <c r="L86" t="n">
-        <v>529.52</v>
+        <v>627.76</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>137.95</v>
+        <v>171.39</v>
       </c>
       <c r="K87" t="n">
-        <v>-316.26</v>
+        <v>-392.92</v>
       </c>
       <c r="L87" t="n">
-        <v>345.04</v>
+        <v>428.68</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>458.07</v>
+        <v>545.66</v>
       </c>
       <c r="K88" t="n">
-        <v>119.07</v>
+        <v>141.84</v>
       </c>
       <c r="L88" t="n">
-        <v>473.29</v>
+        <v>563.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.73999999999999</v>
+        <v>-72.61</v>
       </c>
       <c r="K14" t="n">
-        <v>27.48</v>
+        <v>27.43</v>
       </c>
       <c r="L14" t="n">
-        <v>77.76000000000001</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-36.14</v>
+        <v>-36.16</v>
       </c>
       <c r="K15" t="n">
-        <v>71.22</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>79.87</v>
+        <v>79.91</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.42</v>
+        <v>-46.39</v>
       </c>
       <c r="K16" t="n">
-        <v>-45.77</v>
+        <v>-46.75</v>
       </c>
       <c r="L16" t="n">
-        <v>64.48</v>
+        <v>65.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-77.39</v>
+        <v>-74.61</v>
       </c>
       <c r="K17" t="n">
-        <v>112.14</v>
+        <v>108.11</v>
       </c>
       <c r="L17" t="n">
-        <v>136.25</v>
+        <v>131.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-38.96</v>
+        <v>-38.51</v>
       </c>
       <c r="K18" t="n">
-        <v>100.4</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>107.69</v>
+        <v>106.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-147.2</v>
+        <v>-137.24</v>
       </c>
       <c r="K19" t="n">
-        <v>16.34</v>
+        <v>15.24</v>
       </c>
       <c r="L19" t="n">
-        <v>148.11</v>
+        <v>138.08</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>114.89</v>
+        <v>116.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-115.08</v>
+        <v>-117.07</v>
       </c>
       <c r="L20" t="n">
-        <v>162.61</v>
+        <v>165.43</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-53.22</v>
+        <v>-54.02</v>
       </c>
       <c r="K21" t="n">
-        <v>142.44</v>
+        <v>144.6</v>
       </c>
       <c r="L21" t="n">
-        <v>152.06</v>
+        <v>154.36</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>161.55</v>
+        <v>162.22</v>
       </c>
       <c r="K22" t="n">
-        <v>63.47</v>
+        <v>63.73</v>
       </c>
       <c r="L22" t="n">
-        <v>173.57</v>
+        <v>174.29</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>8.84</v>
+        <v>9.33</v>
       </c>
       <c r="K23" t="n">
-        <v>-199.26</v>
+        <v>-210.39</v>
       </c>
       <c r="L23" t="n">
-        <v>199.46</v>
+        <v>210.6</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-284.92</v>
+        <v>-291.45</v>
       </c>
       <c r="K24" t="n">
-        <v>-37.66</v>
+        <v>-38.53</v>
       </c>
       <c r="L24" t="n">
-        <v>287.4</v>
+        <v>293.99</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>149.53</v>
+        <v>161.21</v>
       </c>
       <c r="K25" t="n">
-        <v>52.23</v>
+        <v>56.31</v>
       </c>
       <c r="L25" t="n">
-        <v>158.39</v>
+        <v>170.76</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-28.31</v>
+        <v>-30.74</v>
       </c>
       <c r="K26" t="n">
-        <v>286.08</v>
+        <v>310.59</v>
       </c>
       <c r="L26" t="n">
-        <v>287.48</v>
+        <v>312.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-17.68</v>
+        <v>-18.74</v>
       </c>
       <c r="K27" t="n">
-        <v>-297.44</v>
+        <v>-315.24</v>
       </c>
       <c r="L27" t="n">
-        <v>297.97</v>
+        <v>315.8</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-133.84</v>
+        <v>-143.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-246.76</v>
+        <v>-265.14</v>
       </c>
       <c r="L28" t="n">
-        <v>280.72</v>
+        <v>301.63</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-89.81</v>
+        <v>-87.37</v>
       </c>
       <c r="K29" t="n">
-        <v>15.78</v>
+        <v>15.35</v>
       </c>
       <c r="L29" t="n">
-        <v>91.19</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-45.48</v>
+        <v>-43.1</v>
       </c>
       <c r="K30" t="n">
-        <v>104.73</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>114.18</v>
+        <v>108.19</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.05</v>
+        <v>-11.17</v>
       </c>
       <c r="K31" t="n">
-        <v>69.48</v>
+        <v>70.28</v>
       </c>
       <c r="L31" t="n">
-        <v>70.34999999999999</v>
+        <v>71.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>105.12</v>
+        <v>100.19</v>
       </c>
       <c r="K32" t="n">
-        <v>82.40000000000001</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>133.57</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-13.55</v>
+        <v>-12.98</v>
       </c>
       <c r="K33" t="n">
-        <v>-137.35</v>
+        <v>-131.62</v>
       </c>
       <c r="L33" t="n">
-        <v>138.02</v>
+        <v>132.26</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-46.13</v>
+        <v>-46.54</v>
       </c>
       <c r="K34" t="n">
-        <v>88.44</v>
+        <v>89.22</v>
       </c>
       <c r="L34" t="n">
-        <v>99.75</v>
+        <v>100.63</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-154.42</v>
+        <v>-156.12</v>
       </c>
       <c r="K35" t="n">
-        <v>45.42</v>
+        <v>45.92</v>
       </c>
       <c r="L35" t="n">
-        <v>160.96</v>
+        <v>162.74</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>117.6</v>
+        <v>122.82</v>
       </c>
       <c r="K36" t="n">
-        <v>106.58</v>
+        <v>111.31</v>
       </c>
       <c r="L36" t="n">
-        <v>158.71</v>
+        <v>165.76</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>219.62</v>
+        <v>216.52</v>
       </c>
       <c r="K37" t="n">
-        <v>-148.82</v>
+        <v>-146.73</v>
       </c>
       <c r="L37" t="n">
-        <v>265.29</v>
+        <v>261.55</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>133.26</v>
+        <v>136.31</v>
       </c>
       <c r="K38" t="n">
-        <v>-302.23</v>
+        <v>-309.16</v>
       </c>
       <c r="L38" t="n">
-        <v>330.31</v>
+        <v>337.87</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>257.85</v>
+        <v>278.19</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.55</v>
+        <v>-4.91</v>
       </c>
       <c r="L39" t="n">
-        <v>257.89</v>
+        <v>278.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-282.93</v>
+        <v>-291.46</v>
       </c>
       <c r="K40" t="n">
-        <v>62.57</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>289.76</v>
+        <v>298.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-92.66</v>
+        <v>-89.56999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-658.01</v>
+        <v>-636.0700000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>664.5</v>
+        <v>642.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-233.55</v>
+        <v>-234.29</v>
       </c>
       <c r="K42" t="n">
-        <v>516.54</v>
+        <v>518.1799999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>566.88</v>
+        <v>568.6799999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-392.94</v>
+        <v>-416.25</v>
       </c>
       <c r="K43" t="n">
-        <v>-78.62</v>
+        <v>-83.28</v>
       </c>
       <c r="L43" t="n">
-        <v>400.73</v>
+        <v>424.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>65.37</v>
+        <v>62.63</v>
       </c>
       <c r="K44" t="n">
-        <v>-88.72</v>
+        <v>-85</v>
       </c>
       <c r="L44" t="n">
-        <v>110.2</v>
+        <v>105.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-50.06</v>
+        <v>-47.57</v>
       </c>
       <c r="K45" t="n">
-        <v>103.52</v>
+        <v>98.39</v>
       </c>
       <c r="L45" t="n">
-        <v>114.99</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-91.45999999999999</v>
+        <v>-90.45</v>
       </c>
       <c r="K46" t="n">
-        <v>26.92</v>
+        <v>26.62</v>
       </c>
       <c r="L46" t="n">
-        <v>95.34</v>
+        <v>94.29000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>5.21</v>
+        <v>4.8</v>
       </c>
       <c r="K47" t="n">
-        <v>-193.09</v>
+        <v>-177.72</v>
       </c>
       <c r="L47" t="n">
-        <v>193.16</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>39.15</v>
+        <v>37.18</v>
       </c>
       <c r="K48" t="n">
-        <v>169.43</v>
+        <v>160.91</v>
       </c>
       <c r="L48" t="n">
-        <v>173.9</v>
+        <v>165.15</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>83.48999999999999</v>
+        <v>87.09</v>
       </c>
       <c r="K49" t="n">
-        <v>-66.98</v>
+        <v>-69.87</v>
       </c>
       <c r="L49" t="n">
-        <v>107.04</v>
+        <v>111.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-172.59</v>
+        <v>-176.98</v>
       </c>
       <c r="K50" t="n">
-        <v>60.22</v>
+        <v>61.75</v>
       </c>
       <c r="L50" t="n">
-        <v>182.8</v>
+        <v>187.44</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>72.42</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-174.44</v>
+        <v>-175.13</v>
       </c>
       <c r="L51" t="n">
-        <v>188.87</v>
+        <v>189.62</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>165.88</v>
+        <v>163.76</v>
       </c>
       <c r="K52" t="n">
-        <v>-50.52</v>
+        <v>-49.87</v>
       </c>
       <c r="L52" t="n">
-        <v>173.4</v>
+        <v>171.18</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>145.77</v>
+        <v>154.92</v>
       </c>
       <c r="K53" t="n">
-        <v>-197.77</v>
+        <v>-210.18</v>
       </c>
       <c r="L53" t="n">
-        <v>245.68</v>
+        <v>261.11</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>298.97</v>
+        <v>310.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-63.73</v>
+        <v>-66.17</v>
       </c>
       <c r="L54" t="n">
-        <v>305.68</v>
+        <v>317.41</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-201.65</v>
+        <v>-223.37</v>
       </c>
       <c r="K55" t="n">
-        <v>-73.36</v>
+        <v>-81.27</v>
       </c>
       <c r="L55" t="n">
-        <v>214.58</v>
+        <v>237.7</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-289.2</v>
+        <v>-272.53</v>
       </c>
       <c r="K56" t="n">
-        <v>839.8099999999999</v>
+        <v>791.38</v>
       </c>
       <c r="L56" t="n">
-        <v>888.21</v>
+        <v>836.99</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-282.17</v>
+        <v>-294.57</v>
       </c>
       <c r="K57" t="n">
-        <v>348.69</v>
+        <v>364.01</v>
       </c>
       <c r="L57" t="n">
-        <v>448.55</v>
+        <v>468.27</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>185.64</v>
+        <v>186.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-541.39</v>
+        <v>-543.8099999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>572.34</v>
+        <v>574.89</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.84</v>
+        <v>-0.89</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="L59" t="n">
-        <v>8.51</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>80.17</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>30.23</v>
+        <v>29.6</v>
       </c>
       <c r="L60" t="n">
-        <v>85.68000000000001</v>
+        <v>83.91</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-104.52</v>
+        <v>-98.86</v>
       </c>
       <c r="K61" t="n">
-        <v>-26.43</v>
+        <v>-25</v>
       </c>
       <c r="L61" t="n">
-        <v>107.81</v>
+        <v>101.97</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>173.02</v>
+        <v>162.03</v>
       </c>
       <c r="K62" t="n">
-        <v>-80.17</v>
+        <v>-75.08</v>
       </c>
       <c r="L62" t="n">
-        <v>190.69</v>
+        <v>178.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>66.62</v>
+        <v>65.17</v>
       </c>
       <c r="K63" t="n">
-        <v>-80.54000000000001</v>
+        <v>-78.78</v>
       </c>
       <c r="L63" t="n">
-        <v>104.52</v>
+        <v>102.24</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-57.12</v>
+        <v>-55.04</v>
       </c>
       <c r="K64" t="n">
-        <v>-116.23</v>
+        <v>-111.99</v>
       </c>
       <c r="L64" t="n">
-        <v>129.51</v>
+        <v>124.79</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-18.72</v>
+        <v>-20.45</v>
       </c>
       <c r="K65" t="n">
-        <v>78.84999999999999</v>
+        <v>86.17</v>
       </c>
       <c r="L65" t="n">
-        <v>81.04000000000001</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>91.84</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>143.69</v>
+        <v>150.54</v>
       </c>
       <c r="L66" t="n">
-        <v>170.53</v>
+        <v>178.66</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>185.92</v>
+        <v>181.7</v>
       </c>
       <c r="K67" t="n">
-        <v>-165.53</v>
+        <v>-161.78</v>
       </c>
       <c r="L67" t="n">
-        <v>248.93</v>
+        <v>243.29</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-486.34</v>
+        <v>-460.1</v>
       </c>
       <c r="K68" t="n">
-        <v>-208.28</v>
+        <v>-197.04</v>
       </c>
       <c r="L68" t="n">
-        <v>529.0700000000001</v>
+        <v>500.51</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-104.27</v>
+        <v>-113.58</v>
       </c>
       <c r="K69" t="n">
-        <v>-194.66</v>
+        <v>-212.05</v>
       </c>
       <c r="L69" t="n">
-        <v>220.83</v>
+        <v>240.56</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>283.17</v>
+        <v>286.85</v>
       </c>
       <c r="K70" t="n">
-        <v>164.9</v>
+        <v>167.04</v>
       </c>
       <c r="L70" t="n">
-        <v>327.68</v>
+        <v>331.94</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-403.37</v>
+        <v>-393.93</v>
       </c>
       <c r="K71" t="n">
-        <v>-462.22</v>
+        <v>-451.4</v>
       </c>
       <c r="L71" t="n">
-        <v>613.48</v>
+        <v>599.12</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-315.89</v>
+        <v>-342.78</v>
       </c>
       <c r="K72" t="n">
-        <v>-37.32</v>
+        <v>-40.5</v>
       </c>
       <c r="L72" t="n">
-        <v>318.08</v>
+        <v>345.17</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>528.5700000000001</v>
+        <v>529.21</v>
       </c>
       <c r="K73" t="n">
-        <v>51.22</v>
+        <v>51.29</v>
       </c>
       <c r="L73" t="n">
-        <v>531.05</v>
+        <v>531.6900000000001</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>114.47</v>
+        <v>107.12</v>
       </c>
       <c r="K74" t="n">
-        <v>-24.08</v>
+        <v>-22.54</v>
       </c>
       <c r="L74" t="n">
-        <v>116.97</v>
+        <v>109.47</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-26.65</v>
+        <v>-25.72</v>
       </c>
       <c r="K75" t="n">
-        <v>100.92</v>
+        <v>97.42</v>
       </c>
       <c r="L75" t="n">
-        <v>104.37</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>122.56</v>
+        <v>113.76</v>
       </c>
       <c r="K76" t="n">
-        <v>32.85</v>
+        <v>30.49</v>
       </c>
       <c r="L76" t="n">
-        <v>126.88</v>
+        <v>117.78</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>94.28</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.55</v>
+        <v>-56.24</v>
       </c>
       <c r="L77" t="n">
-        <v>109.94</v>
+        <v>109.34</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-41.15</v>
+        <v>-39.64</v>
       </c>
       <c r="K78" t="n">
-        <v>-136.37</v>
+        <v>-131.38</v>
       </c>
       <c r="L78" t="n">
-        <v>142.45</v>
+        <v>137.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="K79" t="n">
-        <v>16.41</v>
+        <v>16.94</v>
       </c>
       <c r="L79" t="n">
-        <v>16.54</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-83.66</v>
+        <v>-82.36</v>
       </c>
       <c r="K80" t="n">
-        <v>182.02</v>
+        <v>179.19</v>
       </c>
       <c r="L80" t="n">
-        <v>200.32</v>
+        <v>197.21</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-162.37</v>
+        <v>-153.48</v>
       </c>
       <c r="K81" t="n">
-        <v>-278.18</v>
+        <v>-262.95</v>
       </c>
       <c r="L81" t="n">
-        <v>322.09</v>
+        <v>304.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>196.82</v>
+        <v>195.27</v>
       </c>
       <c r="K82" t="n">
-        <v>39.8</v>
+        <v>39.49</v>
       </c>
       <c r="L82" t="n">
-        <v>200.8</v>
+        <v>199.22</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>218.47</v>
+        <v>221.04</v>
       </c>
       <c r="K83" t="n">
-        <v>-278.89</v>
+        <v>-282.16</v>
       </c>
       <c r="L83" t="n">
-        <v>354.27</v>
+        <v>358.43</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>295.73</v>
+        <v>286.12</v>
       </c>
       <c r="K84" t="n">
-        <v>-400.41</v>
+        <v>-387.41</v>
       </c>
       <c r="L84" t="n">
-        <v>497.78</v>
+        <v>481.61</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-279.53</v>
+        <v>-292.41</v>
       </c>
       <c r="K85" t="n">
-        <v>-51.81</v>
+        <v>-54.2</v>
       </c>
       <c r="L85" t="n">
-        <v>284.29</v>
+        <v>297.4</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-412.14</v>
+        <v>-406.05</v>
       </c>
       <c r="K86" t="n">
-        <v>-473.53</v>
+        <v>-466.53</v>
       </c>
       <c r="L86" t="n">
-        <v>627.76</v>
+        <v>618.49</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>171.39</v>
+        <v>178.51</v>
       </c>
       <c r="K87" t="n">
-        <v>-392.92</v>
+        <v>-409.25</v>
       </c>
       <c r="L87" t="n">
-        <v>428.68</v>
+        <v>446.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>545.66</v>
+        <v>542.96</v>
       </c>
       <c r="K88" t="n">
-        <v>141.84</v>
+        <v>141.13</v>
       </c>
       <c r="L88" t="n">
-        <v>563.79</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -628,25 +628,25 @@
         <v>6.94</v>
       </c>
       <c r="F14" t="n">
-        <v>17.93</v>
+        <v>15.27</v>
       </c>
       <c r="G14" t="n">
-        <v>158.7</v>
+        <v>146.4</v>
       </c>
       <c r="H14" t="n">
-        <v>86.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.61</v>
+        <v>-79.44</v>
       </c>
       <c r="K14" t="n">
-        <v>27.43</v>
+        <v>28.42</v>
       </c>
       <c r="L14" t="n">
-        <v>77.62</v>
+        <v>84.37</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>6.98</v>
       </c>
       <c r="F15" t="n">
-        <v>18.94</v>
+        <v>14.82</v>
       </c>
       <c r="G15" t="n">
-        <v>155</v>
+        <v>166.6</v>
       </c>
       <c r="H15" t="n">
-        <v>85.8</v>
+        <v>91.7</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-36.16</v>
+        <v>-36.65</v>
       </c>
       <c r="K15" t="n">
-        <v>71.26000000000001</v>
+        <v>67.95</v>
       </c>
       <c r="L15" t="n">
-        <v>79.91</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>6.18</v>
       </c>
       <c r="F16" t="n">
-        <v>17.18</v>
+        <v>13.41</v>
       </c>
       <c r="G16" t="n">
-        <v>163.1</v>
+        <v>131.5</v>
       </c>
       <c r="H16" t="n">
-        <v>86.3</v>
+        <v>95.7</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-46.39</v>
+        <v>-45.24</v>
       </c>
       <c r="K16" t="n">
-        <v>-46.75</v>
+        <v>-51.82</v>
       </c>
       <c r="L16" t="n">
-        <v>65.86</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>7.34</v>
       </c>
       <c r="F17" t="n">
-        <v>18.02</v>
+        <v>16.69</v>
       </c>
       <c r="G17" t="n">
-        <v>155.1</v>
+        <v>148.3</v>
       </c>
       <c r="H17" t="n">
-        <v>89.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.61</v>
+        <v>-81.70999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>108.11</v>
+        <v>119.52</v>
       </c>
       <c r="L17" t="n">
-        <v>131.36</v>
+        <v>144.78</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>6.42</v>
       </c>
       <c r="F18" t="n">
-        <v>18.87</v>
+        <v>15.15</v>
       </c>
       <c r="G18" t="n">
-        <v>146.5</v>
+        <v>165.2</v>
       </c>
       <c r="H18" t="n">
-        <v>89.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-38.51</v>
+        <v>-41.31</v>
       </c>
       <c r="K18" t="n">
-        <v>99.23999999999999</v>
+        <v>96.61</v>
       </c>
       <c r="L18" t="n">
-        <v>106.45</v>
+        <v>105.07</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>5.96</v>
       </c>
       <c r="F19" t="n">
-        <v>19.04</v>
+        <v>14.46</v>
       </c>
       <c r="G19" t="n">
-        <v>153.9</v>
+        <v>168.5</v>
       </c>
       <c r="H19" t="n">
-        <v>90.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-137.24</v>
+        <v>-148.31</v>
       </c>
       <c r="K19" t="n">
-        <v>15.24</v>
+        <v>11.39</v>
       </c>
       <c r="L19" t="n">
-        <v>138.08</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>6.43</v>
       </c>
       <c r="F20" t="n">
-        <v>18.19</v>
+        <v>16.21</v>
       </c>
       <c r="G20" t="n">
-        <v>153.8</v>
+        <v>151.6</v>
       </c>
       <c r="H20" t="n">
-        <v>91.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>116.87</v>
+        <v>122.98</v>
       </c>
       <c r="K20" t="n">
-        <v>-117.07</v>
+        <v>-136.63</v>
       </c>
       <c r="L20" t="n">
-        <v>165.43</v>
+        <v>183.83</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>5.87</v>
       </c>
       <c r="F21" t="n">
-        <v>18.25</v>
+        <v>13.18</v>
       </c>
       <c r="G21" t="n">
-        <v>139.8</v>
+        <v>152.7</v>
       </c>
       <c r="H21" t="n">
-        <v>90.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-54.02</v>
+        <v>-56.16</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6</v>
+        <v>146.92</v>
       </c>
       <c r="L21" t="n">
-        <v>154.36</v>
+        <v>157.29</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>6.72</v>
       </c>
       <c r="F22" t="n">
-        <v>17.72</v>
+        <v>13.64</v>
       </c>
       <c r="G22" t="n">
-        <v>166.5</v>
+        <v>142.3</v>
       </c>
       <c r="H22" t="n">
-        <v>83</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>162.22</v>
+        <v>199.99</v>
       </c>
       <c r="K22" t="n">
-        <v>63.73</v>
+        <v>41.2</v>
       </c>
       <c r="L22" t="n">
-        <v>174.29</v>
+        <v>204.19</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>5.98</v>
       </c>
       <c r="F23" t="n">
-        <v>17.38</v>
+        <v>13.9</v>
       </c>
       <c r="G23" t="n">
-        <v>149.8</v>
+        <v>135.5</v>
       </c>
       <c r="H23" t="n">
-        <v>90.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>9.33</v>
+        <v>61.13</v>
       </c>
       <c r="K23" t="n">
-        <v>-210.39</v>
+        <v>-236.27</v>
       </c>
       <c r="L23" t="n">
-        <v>210.6</v>
+        <v>244.05</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>7.07</v>
       </c>
       <c r="F24" t="n">
-        <v>18.41</v>
+        <v>13.81</v>
       </c>
       <c r="G24" t="n">
-        <v>155.1</v>
+        <v>156</v>
       </c>
       <c r="H24" t="n">
-        <v>81.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-291.45</v>
+        <v>-278.15</v>
       </c>
       <c r="K24" t="n">
-        <v>-38.53</v>
+        <v>-78.06</v>
       </c>
       <c r="L24" t="n">
-        <v>293.99</v>
+        <v>288.89</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>5.64</v>
       </c>
       <c r="F25" t="n">
-        <v>18.02</v>
+        <v>12.66</v>
       </c>
       <c r="G25" t="n">
-        <v>148.9</v>
+        <v>148.2</v>
       </c>
       <c r="H25" t="n">
-        <v>93.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>161.21</v>
+        <v>191.6</v>
       </c>
       <c r="K25" t="n">
-        <v>56.31</v>
+        <v>-0.33</v>
       </c>
       <c r="L25" t="n">
-        <v>170.76</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>6.31</v>
       </c>
       <c r="F26" t="n">
-        <v>18.38</v>
+        <v>12.12</v>
       </c>
       <c r="G26" t="n">
-        <v>159.5</v>
+        <v>155.4</v>
       </c>
       <c r="H26" t="n">
-        <v>81.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-30.74</v>
+        <v>27.1</v>
       </c>
       <c r="K26" t="n">
-        <v>310.59</v>
+        <v>344.65</v>
       </c>
       <c r="L26" t="n">
-        <v>312.1</v>
+        <v>345.71</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>5.63</v>
       </c>
       <c r="F27" t="n">
-        <v>17.32</v>
+        <v>12.1</v>
       </c>
       <c r="G27" t="n">
-        <v>158.8</v>
+        <v>134.2</v>
       </c>
       <c r="H27" t="n">
-        <v>97.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-18.74</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-315.24</v>
+        <v>-318.75</v>
       </c>
       <c r="L27" t="n">
-        <v>315.8</v>
+        <v>325.42</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>5.77</v>
       </c>
       <c r="F28" t="n">
-        <v>17.92</v>
+        <v>14.7</v>
       </c>
       <c r="G28" t="n">
-        <v>155.6</v>
+        <v>146.3</v>
       </c>
       <c r="H28" t="n">
-        <v>91.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-143.8</v>
+        <v>-90.94</v>
       </c>
       <c r="K28" t="n">
-        <v>-265.14</v>
+        <v>-353.53</v>
       </c>
       <c r="L28" t="n">
-        <v>301.63</v>
+        <v>365.04</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>6.97</v>
       </c>
       <c r="F29" t="n">
-        <v>17.77</v>
+        <v>19.77</v>
       </c>
       <c r="G29" t="n">
-        <v>162</v>
+        <v>143.2</v>
       </c>
       <c r="H29" t="n">
-        <v>90.8</v>
+        <v>95.2</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-87.37</v>
+        <v>-108.49</v>
       </c>
       <c r="K29" t="n">
-        <v>15.35</v>
+        <v>17.48</v>
       </c>
       <c r="L29" t="n">
-        <v>88.7</v>
+        <v>109.89</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>6.66</v>
       </c>
       <c r="F30" t="n">
-        <v>18.18</v>
+        <v>14.96</v>
       </c>
       <c r="G30" t="n">
-        <v>141.7</v>
+        <v>151.4</v>
       </c>
       <c r="H30" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-43.1</v>
+        <v>-44.68</v>
       </c>
       <c r="K30" t="n">
-        <v>99.23999999999999</v>
+        <v>102.02</v>
       </c>
       <c r="L30" t="n">
-        <v>108.19</v>
+        <v>111.38</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>6.58</v>
       </c>
       <c r="F31" t="n">
-        <v>17.52</v>
+        <v>15.52</v>
       </c>
       <c r="G31" t="n">
-        <v>151.4</v>
+        <v>138.2</v>
       </c>
       <c r="H31" t="n">
-        <v>91.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.17</v>
+        <v>-8.98</v>
       </c>
       <c r="K31" t="n">
-        <v>70.28</v>
+        <v>77.98</v>
       </c>
       <c r="L31" t="n">
-        <v>71.16</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>6.23</v>
       </c>
       <c r="F32" t="n">
-        <v>18.32</v>
+        <v>14.19</v>
       </c>
       <c r="G32" t="n">
-        <v>161.7</v>
+        <v>154.3</v>
       </c>
       <c r="H32" t="n">
-        <v>86.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>100.19</v>
+        <v>112.97</v>
       </c>
       <c r="K32" t="n">
-        <v>78.54000000000001</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>127.3</v>
+        <v>138.72</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>7.12</v>
       </c>
       <c r="F33" t="n">
-        <v>18.27</v>
+        <v>16.68</v>
       </c>
       <c r="G33" t="n">
-        <v>157.6</v>
+        <v>153.2</v>
       </c>
       <c r="H33" t="n">
-        <v>86.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-12.98</v>
+        <v>-9.74</v>
       </c>
       <c r="K33" t="n">
-        <v>-131.62</v>
+        <v>-148.38</v>
       </c>
       <c r="L33" t="n">
-        <v>132.26</v>
+        <v>148.7</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>6.65</v>
       </c>
       <c r="F34" t="n">
-        <v>18.96</v>
+        <v>17.43</v>
       </c>
       <c r="G34" t="n">
-        <v>154.8</v>
+        <v>167.1</v>
       </c>
       <c r="H34" t="n">
-        <v>92.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-46.54</v>
+        <v>-59.44</v>
       </c>
       <c r="K34" t="n">
-        <v>89.22</v>
+        <v>101.07</v>
       </c>
       <c r="L34" t="n">
-        <v>100.63</v>
+        <v>117.25</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>5.9</v>
       </c>
       <c r="F35" t="n">
-        <v>17.79</v>
+        <v>15.3</v>
       </c>
       <c r="G35" t="n">
-        <v>151.5</v>
+        <v>143.6</v>
       </c>
       <c r="H35" t="n">
-        <v>81.5</v>
+        <v>90</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-156.12</v>
+        <v>-168.63</v>
       </c>
       <c r="K35" t="n">
-        <v>45.92</v>
+        <v>25.82</v>
       </c>
       <c r="L35" t="n">
-        <v>162.74</v>
+        <v>170.6</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>6.74</v>
       </c>
       <c r="F36" t="n">
-        <v>18.1</v>
+        <v>16.92</v>
       </c>
       <c r="G36" t="n">
-        <v>145.7</v>
+        <v>149.8</v>
       </c>
       <c r="H36" t="n">
-        <v>90.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>122.82</v>
+        <v>156.88</v>
       </c>
       <c r="K36" t="n">
-        <v>111.31</v>
+        <v>63.06</v>
       </c>
       <c r="L36" t="n">
-        <v>165.76</v>
+        <v>169.08</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>8.17</v>
       </c>
       <c r="F37" t="n">
-        <v>18.35</v>
+        <v>20.1</v>
       </c>
       <c r="G37" t="n">
-        <v>153.5</v>
+        <v>154.9</v>
       </c>
       <c r="H37" t="n">
-        <v>87.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>216.52</v>
+        <v>211.59</v>
       </c>
       <c r="K37" t="n">
-        <v>-146.73</v>
+        <v>-164.96</v>
       </c>
       <c r="L37" t="n">
-        <v>261.55</v>
+        <v>268.3</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>7.34</v>
       </c>
       <c r="F38" t="n">
-        <v>19.17</v>
+        <v>18.47</v>
       </c>
       <c r="G38" t="n">
-        <v>149.3</v>
+        <v>171.2</v>
       </c>
       <c r="H38" t="n">
-        <v>90.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>136.31</v>
+        <v>108.85</v>
       </c>
       <c r="K38" t="n">
-        <v>-309.16</v>
+        <v>-347.19</v>
       </c>
       <c r="L38" t="n">
-        <v>337.87</v>
+        <v>363.85</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>7.81</v>
       </c>
       <c r="F39" t="n">
-        <v>17.99</v>
+        <v>18.62</v>
       </c>
       <c r="G39" t="n">
-        <v>153.9</v>
+        <v>147.7</v>
       </c>
       <c r="H39" t="n">
-        <v>92.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I39" t="n">
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>278.19</v>
+        <v>321.85</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.91</v>
+        <v>-65.33</v>
       </c>
       <c r="L39" t="n">
-        <v>278.23</v>
+        <v>328.41</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>6.76</v>
       </c>
       <c r="F40" t="n">
-        <v>17.94</v>
+        <v>17.41</v>
       </c>
       <c r="G40" t="n">
-        <v>152.3</v>
+        <v>146.7</v>
       </c>
       <c r="H40" t="n">
-        <v>91</v>
+        <v>90.3</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-291.46</v>
+        <v>-297.11</v>
       </c>
       <c r="K40" t="n">
-        <v>64.45999999999999</v>
+        <v>33.37</v>
       </c>
       <c r="L40" t="n">
-        <v>298.5</v>
+        <v>298.98</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>6.63</v>
       </c>
       <c r="F41" t="n">
-        <v>18.33</v>
+        <v>15.38</v>
       </c>
       <c r="G41" t="n">
-        <v>144</v>
+        <v>154.4</v>
       </c>
       <c r="H41" t="n">
-        <v>87.2</v>
+        <v>86.2</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-89.56999999999999</v>
+        <v>-92.06</v>
       </c>
       <c r="K41" t="n">
-        <v>-636.0700000000001</v>
+        <v>-756.84</v>
       </c>
       <c r="L41" t="n">
-        <v>642.35</v>
+        <v>762.42</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>6.97</v>
       </c>
       <c r="F42" t="n">
-        <v>17.68</v>
+        <v>15.36</v>
       </c>
       <c r="G42" t="n">
-        <v>160.5</v>
+        <v>141.3</v>
       </c>
       <c r="H42" t="n">
-        <v>84.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-234.29</v>
+        <v>-201.67</v>
       </c>
       <c r="K42" t="n">
-        <v>518.1799999999999</v>
+        <v>576.64</v>
       </c>
       <c r="L42" t="n">
-        <v>568.6799999999999</v>
+        <v>610.89</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>7.28</v>
       </c>
       <c r="F43" t="n">
-        <v>18.13</v>
+        <v>17.05</v>
       </c>
       <c r="G43" t="n">
-        <v>149.7</v>
+        <v>150.4</v>
       </c>
       <c r="H43" t="n">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-416.25</v>
+        <v>-424.14</v>
       </c>
       <c r="K43" t="n">
-        <v>-83.28</v>
+        <v>-197.41</v>
       </c>
       <c r="L43" t="n">
-        <v>424.5</v>
+        <v>467.83</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>7.46</v>
       </c>
       <c r="F44" t="n">
-        <v>17.5</v>
+        <v>18.79</v>
       </c>
       <c r="G44" t="n">
-        <v>149.5</v>
+        <v>137.9</v>
       </c>
       <c r="H44" t="n">
-        <v>89.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>62.63</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-85</v>
+        <v>-95.22</v>
       </c>
       <c r="L44" t="n">
-        <v>105.58</v>
+        <v>119.23</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>7.1</v>
       </c>
       <c r="F45" t="n">
-        <v>18.11</v>
+        <v>18.26</v>
       </c>
       <c r="G45" t="n">
-        <v>142.3</v>
+        <v>149.9</v>
       </c>
       <c r="H45" t="n">
-        <v>94.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.57</v>
+        <v>-52.16</v>
       </c>
       <c r="K45" t="n">
-        <v>98.39</v>
+        <v>107.15</v>
       </c>
       <c r="L45" t="n">
-        <v>109.28</v>
+        <v>119.17</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>7.45</v>
       </c>
       <c r="F46" t="n">
-        <v>18.2</v>
+        <v>20.93</v>
       </c>
       <c r="G46" t="n">
-        <v>139.8</v>
+        <v>151.7</v>
       </c>
       <c r="H46" t="n">
-        <v>97.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-90.45</v>
+        <v>-98.87</v>
       </c>
       <c r="K46" t="n">
-        <v>26.62</v>
+        <v>24.61</v>
       </c>
       <c r="L46" t="n">
-        <v>94.29000000000001</v>
+        <v>101.89</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>6.32</v>
       </c>
       <c r="F47" t="n">
-        <v>17.81</v>
+        <v>17.86</v>
       </c>
       <c r="G47" t="n">
-        <v>137</v>
+        <v>144.1</v>
       </c>
       <c r="H47" t="n">
-        <v>91.2</v>
+        <v>82.7</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>4.8</v>
+        <v>7.26</v>
       </c>
       <c r="K47" t="n">
-        <v>-177.72</v>
+        <v>-180</v>
       </c>
       <c r="L47" t="n">
-        <v>177.78</v>
+        <v>180.14</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>7.69</v>
       </c>
       <c r="F48" t="n">
-        <v>17.93</v>
+        <v>18.47</v>
       </c>
       <c r="G48" t="n">
-        <v>159.8</v>
+        <v>146.4</v>
       </c>
       <c r="H48" t="n">
-        <v>86.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>37.18</v>
+        <v>47.76</v>
       </c>
       <c r="K48" t="n">
-        <v>160.91</v>
+        <v>166.58</v>
       </c>
       <c r="L48" t="n">
-        <v>165.15</v>
+        <v>173.29</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>7.93</v>
       </c>
       <c r="F49" t="n">
-        <v>18.46</v>
+        <v>20.93</v>
       </c>
       <c r="G49" t="n">
-        <v>141.7</v>
+        <v>157</v>
       </c>
       <c r="H49" t="n">
-        <v>93.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>87.09</v>
+        <v>85.41</v>
       </c>
       <c r="K49" t="n">
-        <v>-69.87</v>
+        <v>-88.42</v>
       </c>
       <c r="L49" t="n">
-        <v>111.65</v>
+        <v>122.93</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>7.32</v>
       </c>
       <c r="F50" t="n">
-        <v>18.46</v>
+        <v>14.13</v>
       </c>
       <c r="G50" t="n">
-        <v>153.2</v>
+        <v>156.9</v>
       </c>
       <c r="H50" t="n">
-        <v>77.8</v>
+        <v>90.8</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-176.98</v>
+        <v>-182.76</v>
       </c>
       <c r="K50" t="n">
-        <v>61.75</v>
+        <v>19.23</v>
       </c>
       <c r="L50" t="n">
-        <v>187.44</v>
+        <v>183.77</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>6.98</v>
       </c>
       <c r="F51" t="n">
-        <v>18.38</v>
+        <v>18.53</v>
       </c>
       <c r="G51" t="n">
-        <v>154.3</v>
+        <v>154.7</v>
       </c>
       <c r="H51" t="n">
-        <v>84.7</v>
+        <v>94.3</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>72.70999999999999</v>
+        <v>-302.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-175.13</v>
+        <v>-111.79</v>
       </c>
       <c r="L51" t="n">
-        <v>189.62</v>
+        <v>322.23</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.63</v>
+        <v>7.49</v>
       </c>
       <c r="F52" t="n">
-        <v>18.52</v>
+        <v>20.63</v>
       </c>
       <c r="G52" t="n">
-        <v>149</v>
+        <v>162.1</v>
       </c>
       <c r="H52" t="n">
-        <v>93.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>163.76</v>
+        <v>195.44</v>
       </c>
       <c r="K52" t="n">
-        <v>-49.87</v>
+        <v>41.45</v>
       </c>
       <c r="L52" t="n">
-        <v>171.18</v>
+        <v>199.79</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7.36</v>
+        <v>7.96</v>
       </c>
       <c r="F53" t="n">
-        <v>18.54</v>
+        <v>19.97</v>
       </c>
       <c r="G53" t="n">
-        <v>148.1</v>
+        <v>153.7</v>
       </c>
       <c r="H53" t="n">
-        <v>83.3</v>
+        <v>96.3</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>154.92</v>
+        <v>346.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-210.18</v>
+        <v>188.98</v>
       </c>
       <c r="L53" t="n">
-        <v>261.11</v>
+        <v>394.38</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>7.55</v>
+        <v>6.9</v>
       </c>
       <c r="F54" t="n">
-        <v>18.67</v>
+        <v>19.78</v>
       </c>
       <c r="G54" t="n">
-        <v>154.4</v>
+        <v>157.7</v>
       </c>
       <c r="H54" t="n">
-        <v>88.7</v>
+        <v>97.7</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>310.44</v>
+        <v>83.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-66.17</v>
+        <v>160.23</v>
       </c>
       <c r="L54" t="n">
-        <v>317.41</v>
+        <v>180.72</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>7.09</v>
+        <v>7.05</v>
       </c>
       <c r="F55" t="n">
-        <v>18.72</v>
+        <v>16.72</v>
       </c>
       <c r="G55" t="n">
-        <v>143.3</v>
+        <v>148.3</v>
       </c>
       <c r="H55" t="n">
-        <v>90.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-223.37</v>
+        <v>432.52</v>
       </c>
       <c r="K55" t="n">
-        <v>-81.27</v>
+        <v>-149.93</v>
       </c>
       <c r="L55" t="n">
-        <v>237.7</v>
+        <v>457.76</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>8.300000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="F56" t="n">
-        <v>18.86</v>
+        <v>20.19</v>
       </c>
       <c r="G56" t="n">
-        <v>147.4</v>
+        <v>143.8</v>
       </c>
       <c r="H56" t="n">
-        <v>87.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-272.53</v>
+        <v>342.37</v>
       </c>
       <c r="K56" t="n">
-        <v>791.38</v>
+        <v>-591.4</v>
       </c>
       <c r="L56" t="n">
-        <v>836.99</v>
+        <v>683.35</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>7.5</v>
+        <v>7.13</v>
       </c>
       <c r="F57" t="n">
-        <v>18.94</v>
+        <v>19.94</v>
       </c>
       <c r="G57" t="n">
-        <v>158.6</v>
+        <v>147.5</v>
       </c>
       <c r="H57" t="n">
-        <v>90.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-294.57</v>
+        <v>-231.46</v>
       </c>
       <c r="K57" t="n">
-        <v>364.01</v>
+        <v>-656.39</v>
       </c>
       <c r="L57" t="n">
-        <v>468.27</v>
+        <v>696.01</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.76</v>
+        <v>6.14</v>
       </c>
       <c r="F58" t="n">
-        <v>17.84</v>
+        <v>14.67</v>
       </c>
       <c r="G58" t="n">
-        <v>139.3</v>
+        <v>154.3</v>
       </c>
       <c r="H58" t="n">
-        <v>83.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>186.47</v>
+        <v>-732.95</v>
       </c>
       <c r="K58" t="n">
-        <v>-543.8099999999999</v>
+        <v>-346.55</v>
       </c>
       <c r="L58" t="n">
-        <v>574.89</v>
+        <v>810.75</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.39</v>
+        <v>6.95</v>
       </c>
       <c r="F59" t="n">
-        <v>17.95</v>
+        <v>20.63</v>
       </c>
       <c r="G59" t="n">
-        <v>164</v>
+        <v>151.6</v>
       </c>
       <c r="H59" t="n">
-        <v>87.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.89</v>
+        <v>-92.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.93</v>
+        <v>-15.96</v>
       </c>
       <c r="L59" t="n">
-        <v>8.98</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.74</v>
+        <v>6.78</v>
       </c>
       <c r="F60" t="n">
-        <v>18.11</v>
+        <v>17.48</v>
       </c>
       <c r="G60" t="n">
-        <v>153.2</v>
+        <v>159.7</v>
       </c>
       <c r="H60" t="n">
-        <v>87</v>
+        <v>86.3</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>78.51000000000001</v>
+        <v>-77.95</v>
       </c>
       <c r="K60" t="n">
-        <v>29.6</v>
+        <v>11.88</v>
       </c>
       <c r="L60" t="n">
-        <v>83.91</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.98</v>
+        <v>7.19</v>
       </c>
       <c r="F61" t="n">
-        <v>17.95</v>
+        <v>19.04</v>
       </c>
       <c r="G61" t="n">
-        <v>152.4</v>
+        <v>138.8</v>
       </c>
       <c r="H61" t="n">
-        <v>86.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-98.86</v>
+        <v>59.16</v>
       </c>
       <c r="K61" t="n">
-        <v>-25</v>
+        <v>-72.01000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>101.97</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>7.59</v>
+        <v>8.73</v>
       </c>
       <c r="F62" t="n">
-        <v>18.72</v>
+        <v>20.93</v>
       </c>
       <c r="G62" t="n">
-        <v>158.9</v>
+        <v>166.6</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="I62" t="n">
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>162.03</v>
+        <v>-233.64</v>
       </c>
       <c r="K62" t="n">
-        <v>-75.08</v>
+        <v>-61.28</v>
       </c>
       <c r="L62" t="n">
-        <v>178.58</v>
+        <v>241.55</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.77</v>
+        <v>8.09</v>
       </c>
       <c r="F63" t="n">
-        <v>18.73</v>
+        <v>20.93</v>
       </c>
       <c r="G63" t="n">
-        <v>154</v>
+        <v>144.3</v>
       </c>
       <c r="H63" t="n">
-        <v>90.7</v>
+        <v>93.3</v>
       </c>
       <c r="I63" t="n">
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>65.17</v>
+        <v>176.73</v>
       </c>
       <c r="K63" t="n">
-        <v>-78.78</v>
+        <v>-6.46</v>
       </c>
       <c r="L63" t="n">
-        <v>102.24</v>
+        <v>176.85</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.64</v>
+        <v>6.92</v>
       </c>
       <c r="F64" t="n">
-        <v>17.95</v>
+        <v>17.29</v>
       </c>
       <c r="G64" t="n">
-        <v>146.8</v>
+        <v>141.5</v>
       </c>
       <c r="H64" t="n">
-        <v>90.5</v>
+        <v>87.3</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.04</v>
+        <v>-13.46</v>
       </c>
       <c r="K64" t="n">
-        <v>-111.99</v>
+        <v>-112.24</v>
       </c>
       <c r="L64" t="n">
-        <v>124.79</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.43</v>
+        <v>7.95</v>
       </c>
       <c r="F65" t="n">
-        <v>18.31</v>
+        <v>20.93</v>
       </c>
       <c r="G65" t="n">
-        <v>154.1</v>
+        <v>154.7</v>
       </c>
       <c r="H65" t="n">
-        <v>94.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-20.45</v>
+        <v>23.13</v>
       </c>
       <c r="K65" t="n">
-        <v>86.17</v>
+        <v>215.42</v>
       </c>
       <c r="L65" t="n">
-        <v>88.56999999999999</v>
+        <v>216.66</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>8.210000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>18.66</v>
       </c>
       <c r="G66" t="n">
-        <v>158.1</v>
+        <v>153.9</v>
       </c>
       <c r="H66" t="n">
-        <v>90.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="I66" t="n">
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>96.20999999999999</v>
+        <v>188.82</v>
       </c>
       <c r="K66" t="n">
-        <v>150.54</v>
+        <v>15.83</v>
       </c>
       <c r="L66" t="n">
-        <v>178.66</v>
+        <v>189.48</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>7.67</v>
+        <v>7.13</v>
       </c>
       <c r="F67" t="n">
-        <v>18.37</v>
+        <v>19.8</v>
       </c>
       <c r="G67" t="n">
-        <v>156.2</v>
+        <v>160.7</v>
       </c>
       <c r="H67" t="n">
-        <v>86.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>181.7</v>
+        <v>-75.7</v>
       </c>
       <c r="K67" t="n">
-        <v>-161.78</v>
+        <v>211.17</v>
       </c>
       <c r="L67" t="n">
-        <v>243.29</v>
+        <v>224.33</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7.01</v>
+        <v>7.86</v>
       </c>
       <c r="F68" t="n">
-        <v>18.31</v>
+        <v>20.93</v>
       </c>
       <c r="G68" t="n">
-        <v>148.9</v>
+        <v>129.8</v>
       </c>
       <c r="H68" t="n">
-        <v>93.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-460.1</v>
+        <v>126.95</v>
       </c>
       <c r="K68" t="n">
-        <v>-197.04</v>
+        <v>-303.27</v>
       </c>
       <c r="L68" t="n">
-        <v>500.51</v>
+        <v>328.77</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="F69" t="n">
-        <v>17.78</v>
+        <v>19.48</v>
       </c>
       <c r="G69" t="n">
         <v>149.2</v>
       </c>
       <c r="H69" t="n">
-        <v>94.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-113.58</v>
+        <v>-22.26</v>
       </c>
       <c r="K69" t="n">
-        <v>-212.05</v>
+        <v>486.03</v>
       </c>
       <c r="L69" t="n">
-        <v>240.56</v>
+        <v>486.54</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>7.21</v>
+        <v>6.07</v>
       </c>
       <c r="F70" t="n">
-        <v>18.2</v>
+        <v>16.18</v>
       </c>
       <c r="G70" t="n">
-        <v>148.7</v>
+        <v>159</v>
       </c>
       <c r="H70" t="n">
-        <v>81.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>286.85</v>
+        <v>36.12</v>
       </c>
       <c r="K70" t="n">
-        <v>167.04</v>
+        <v>-243.4</v>
       </c>
       <c r="L70" t="n">
-        <v>331.94</v>
+        <v>246.07</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>7.88</v>
+        <v>7.34</v>
       </c>
       <c r="F71" t="n">
-        <v>18.3</v>
+        <v>19.51</v>
       </c>
       <c r="G71" t="n">
-        <v>150.3</v>
+        <v>157.8</v>
       </c>
       <c r="H71" t="n">
-        <v>89.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-393.93</v>
+        <v>-319.19</v>
       </c>
       <c r="K71" t="n">
-        <v>-451.4</v>
+        <v>-751.85</v>
       </c>
       <c r="L71" t="n">
-        <v>599.12</v>
+        <v>816.8</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.4</v>
+        <v>7.92</v>
       </c>
       <c r="F72" t="n">
-        <v>17.63</v>
+        <v>20.93</v>
       </c>
       <c r="G72" t="n">
-        <v>155.8</v>
+        <v>166.1</v>
       </c>
       <c r="H72" t="n">
-        <v>91.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-342.78</v>
+        <v>242.79</v>
       </c>
       <c r="K72" t="n">
-        <v>-40.5</v>
+        <v>428.18</v>
       </c>
       <c r="L72" t="n">
-        <v>345.17</v>
+        <v>492.22</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7.93</v>
+        <v>6.85</v>
       </c>
       <c r="F73" t="n">
-        <v>18.32</v>
+        <v>18.64</v>
       </c>
       <c r="G73" t="n">
-        <v>174.7</v>
+        <v>164.7</v>
       </c>
       <c r="H73" t="n">
-        <v>90.8</v>
+        <v>91.3</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>529.21</v>
+        <v>183.85</v>
       </c>
       <c r="K73" t="n">
-        <v>51.29</v>
+        <v>-533.83</v>
       </c>
       <c r="L73" t="n">
-        <v>531.6900000000001</v>
+        <v>564.6</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.91</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>18.28</v>
+        <v>20.93</v>
       </c>
       <c r="G74" t="n">
-        <v>164.6</v>
+        <v>130.6</v>
       </c>
       <c r="H74" t="n">
-        <v>84.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>107.12</v>
+        <v>96.44</v>
       </c>
       <c r="K74" t="n">
-        <v>-22.54</v>
+        <v>-40.11</v>
       </c>
       <c r="L74" t="n">
-        <v>109.47</v>
+        <v>104.45</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>7.88</v>
+        <v>7.91</v>
       </c>
       <c r="F75" t="n">
-        <v>18.17</v>
+        <v>19.31</v>
       </c>
       <c r="G75" t="n">
-        <v>141.4</v>
+        <v>149</v>
       </c>
       <c r="H75" t="n">
-        <v>86.7</v>
+        <v>90.2</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-25.72</v>
+        <v>-90.95</v>
       </c>
       <c r="K75" t="n">
-        <v>97.42</v>
+        <v>25.76</v>
       </c>
       <c r="L75" t="n">
-        <v>100.75</v>
+        <v>94.53</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>7.01</v>
+        <v>7.54</v>
       </c>
       <c r="F76" t="n">
-        <v>17.67</v>
+        <v>18.3</v>
       </c>
       <c r="G76" t="n">
-        <v>139.3</v>
+        <v>167.6</v>
       </c>
       <c r="H76" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>113.76</v>
+        <v>-87.43000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>30.49</v>
+        <v>-164.39</v>
       </c>
       <c r="L76" t="n">
-        <v>117.78</v>
+        <v>186.19</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.52</v>
+        <v>7.95</v>
       </c>
       <c r="F77" t="n">
-        <v>17.85</v>
+        <v>20.93</v>
       </c>
       <c r="G77" t="n">
-        <v>160.9</v>
+        <v>158.6</v>
       </c>
       <c r="H77" t="n">
-        <v>89.7</v>
+        <v>91.5</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>93.76000000000001</v>
+        <v>-99.12</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.24</v>
+        <v>-44.77</v>
       </c>
       <c r="L77" t="n">
-        <v>109.34</v>
+        <v>108.76</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>7.29</v>
+        <v>7.85</v>
       </c>
       <c r="F78" t="n">
-        <v>18.19</v>
+        <v>20.93</v>
       </c>
       <c r="G78" t="n">
-        <v>156.1</v>
+        <v>141.2</v>
       </c>
       <c r="H78" t="n">
-        <v>91.7</v>
+        <v>88.3</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-39.64</v>
+        <v>-76.48</v>
       </c>
       <c r="K78" t="n">
-        <v>-131.38</v>
+        <v>-114.53</v>
       </c>
       <c r="L78" t="n">
-        <v>137.23</v>
+        <v>137.72</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>8.69</v>
+        <v>7.5</v>
       </c>
       <c r="F79" t="n">
-        <v>18.05</v>
+        <v>19.71</v>
       </c>
       <c r="G79" t="n">
-        <v>152.3</v>
+        <v>153.2</v>
       </c>
       <c r="H79" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>2.11</v>
+        <v>181.82</v>
       </c>
       <c r="K79" t="n">
-        <v>16.94</v>
+        <v>-29.1</v>
       </c>
       <c r="L79" t="n">
-        <v>17.07</v>
+        <v>184.14</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.19</v>
+        <v>7.9</v>
       </c>
       <c r="F80" t="n">
-        <v>17.65</v>
+        <v>20.7</v>
       </c>
       <c r="G80" t="n">
-        <v>156.4</v>
+        <v>163.6</v>
       </c>
       <c r="H80" t="n">
-        <v>89.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-82.36</v>
+        <v>171.07</v>
       </c>
       <c r="K80" t="n">
-        <v>179.19</v>
+        <v>-203.11</v>
       </c>
       <c r="L80" t="n">
-        <v>197.21</v>
+        <v>265.55</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="F81" t="n">
-        <v>18.71</v>
+        <v>20.93</v>
       </c>
       <c r="G81" t="n">
-        <v>149.8</v>
+        <v>136.2</v>
       </c>
       <c r="H81" t="n">
-        <v>88.3</v>
+        <v>84.8</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-153.48</v>
+        <v>-76.11</v>
       </c>
       <c r="K81" t="n">
-        <v>-262.95</v>
+        <v>-270.88</v>
       </c>
       <c r="L81" t="n">
-        <v>304.47</v>
+        <v>281.37</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.94</v>
+        <v>7.14</v>
       </c>
       <c r="F82" t="n">
-        <v>17.39</v>
+        <v>17.8</v>
       </c>
       <c r="G82" t="n">
-        <v>145.9</v>
+        <v>155</v>
       </c>
       <c r="H82" t="n">
-        <v>83.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>195.27</v>
+        <v>-117.57</v>
       </c>
       <c r="K82" t="n">
-        <v>39.49</v>
+        <v>-267.74</v>
       </c>
       <c r="L82" t="n">
-        <v>199.22</v>
+        <v>292.42</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="F83" t="n">
-        <v>18.55</v>
+        <v>20.93</v>
       </c>
       <c r="G83" t="n">
-        <v>151.5</v>
+        <v>152</v>
       </c>
       <c r="H83" t="n">
-        <v>85.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>221.04</v>
+        <v>-3.49</v>
       </c>
       <c r="K83" t="n">
-        <v>-282.16</v>
+        <v>439.08</v>
       </c>
       <c r="L83" t="n">
-        <v>358.43</v>
+        <v>439.09</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.61</v>
+        <v>6.57</v>
       </c>
       <c r="F84" t="n">
-        <v>17.5</v>
+        <v>19.76</v>
       </c>
       <c r="G84" t="n">
-        <v>168.1</v>
+        <v>146.7</v>
       </c>
       <c r="H84" t="n">
-        <v>89.3</v>
+        <v>84.2</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>286.12</v>
+        <v>-0.82</v>
       </c>
       <c r="K84" t="n">
-        <v>-387.41</v>
+        <v>-429.66</v>
       </c>
       <c r="L84" t="n">
-        <v>481.61</v>
+        <v>429.66</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>7.24</v>
+        <v>7.96</v>
       </c>
       <c r="F85" t="n">
-        <v>18.47</v>
+        <v>20.93</v>
       </c>
       <c r="G85" t="n">
-        <v>156.6</v>
+        <v>144.6</v>
       </c>
       <c r="H85" t="n">
-        <v>83.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-292.41</v>
+        <v>585.98</v>
       </c>
       <c r="K85" t="n">
-        <v>-54.2</v>
+        <v>-56.59</v>
       </c>
       <c r="L85" t="n">
-        <v>297.4</v>
+        <v>588.71</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>7.11</v>
+        <v>6.95</v>
       </c>
       <c r="F86" t="n">
-        <v>17.72</v>
+        <v>16.89</v>
       </c>
       <c r="G86" t="n">
-        <v>152.6</v>
+        <v>143.5</v>
       </c>
       <c r="H86" t="n">
-        <v>98.7</v>
+        <v>85.3</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-406.05</v>
+        <v>552.3</v>
       </c>
       <c r="K86" t="n">
-        <v>-466.53</v>
+        <v>120.74</v>
       </c>
       <c r="L86" t="n">
-        <v>618.49</v>
+        <v>565.34</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>7.04</v>
+        <v>7.95</v>
       </c>
       <c r="F87" t="n">
-        <v>17.76</v>
+        <v>20.89</v>
       </c>
       <c r="G87" t="n">
-        <v>156</v>
+        <v>149.6</v>
       </c>
       <c r="H87" t="n">
-        <v>92.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>178.51</v>
+        <v>-197.64</v>
       </c>
       <c r="K87" t="n">
-        <v>-409.25</v>
+        <v>-160.62</v>
       </c>
       <c r="L87" t="n">
-        <v>446.49</v>
+        <v>254.68</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>7.49</v>
+        <v>8.58</v>
       </c>
       <c r="F88" t="n">
-        <v>18.84</v>
+        <v>20.93</v>
       </c>
       <c r="G88" t="n">
-        <v>153.6</v>
+        <v>140.1</v>
       </c>
       <c r="H88" t="n">
-        <v>88.7</v>
+        <v>92.3</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>542.96</v>
+        <v>-266.22</v>
       </c>
       <c r="K88" t="n">
-        <v>141.13</v>
+        <v>-535.98</v>
       </c>
       <c r="L88" t="n">
-        <v>561</v>
+        <v>598.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-79.44</v>
+        <v>-82.25</v>
       </c>
       <c r="K14" t="n">
-        <v>28.42</v>
+        <v>29.42</v>
       </c>
       <c r="L14" t="n">
-        <v>84.37</v>
+        <v>87.34999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-36.65</v>
+        <v>-35.45</v>
       </c>
       <c r="K15" t="n">
-        <v>67.95</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>77.20999999999999</v>
+        <v>74.69</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.24</v>
+        <v>-45.96</v>
       </c>
       <c r="K16" t="n">
-        <v>-51.82</v>
+        <v>-52.65</v>
       </c>
       <c r="L16" t="n">
-        <v>68.79000000000001</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-81.70999999999999</v>
+        <v>-88.33</v>
       </c>
       <c r="K17" t="n">
-        <v>119.52</v>
+        <v>129.21</v>
       </c>
       <c r="L17" t="n">
-        <v>144.78</v>
+        <v>156.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-41.31</v>
+        <v>-41.49</v>
       </c>
       <c r="K18" t="n">
-        <v>96.61</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>105.07</v>
+        <v>105.53</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-148.31</v>
+        <v>-156.92</v>
       </c>
       <c r="K19" t="n">
-        <v>11.39</v>
+        <v>12.05</v>
       </c>
       <c r="L19" t="n">
-        <v>148.75</v>
+        <v>157.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>122.98</v>
+        <v>124.77</v>
       </c>
       <c r="K20" t="n">
-        <v>-136.63</v>
+        <v>-138.62</v>
       </c>
       <c r="L20" t="n">
-        <v>183.83</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-56.16</v>
+        <v>-61.91</v>
       </c>
       <c r="K21" t="n">
-        <v>146.92</v>
+        <v>161.94</v>
       </c>
       <c r="L21" t="n">
-        <v>157.29</v>
+        <v>173.37</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>199.99</v>
+        <v>217.03</v>
       </c>
       <c r="K22" t="n">
-        <v>41.2</v>
+        <v>44.71</v>
       </c>
       <c r="L22" t="n">
-        <v>204.19</v>
+        <v>221.59</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>61.13</v>
+        <v>68.45</v>
       </c>
       <c r="K23" t="n">
-        <v>-236.27</v>
+        <v>-264.56</v>
       </c>
       <c r="L23" t="n">
-        <v>244.05</v>
+        <v>273.27</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-278.15</v>
+        <v>-287.31</v>
       </c>
       <c r="K24" t="n">
-        <v>-78.06</v>
+        <v>-80.63</v>
       </c>
       <c r="L24" t="n">
-        <v>288.89</v>
+        <v>298.41</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>191.6</v>
+        <v>201.1</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="L25" t="n">
-        <v>191.6</v>
+        <v>201.1</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>27.1</v>
+        <v>30.28</v>
       </c>
       <c r="K26" t="n">
-        <v>344.65</v>
+        <v>385.06</v>
       </c>
       <c r="L26" t="n">
-        <v>345.71</v>
+        <v>386.25</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>65.51000000000001</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-318.75</v>
+        <v>-332.01</v>
       </c>
       <c r="L27" t="n">
-        <v>325.42</v>
+        <v>338.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-90.94</v>
+        <v>-102.92</v>
       </c>
       <c r="K28" t="n">
-        <v>-353.53</v>
+        <v>-400.08</v>
       </c>
       <c r="L28" t="n">
-        <v>365.04</v>
+        <v>413.1</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-108.49</v>
+        <v>-115.59</v>
       </c>
       <c r="K29" t="n">
-        <v>17.48</v>
+        <v>18.62</v>
       </c>
       <c r="L29" t="n">
-        <v>109.89</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-44.68</v>
+        <v>-47.05</v>
       </c>
       <c r="K30" t="n">
-        <v>102.02</v>
+        <v>107.44</v>
       </c>
       <c r="L30" t="n">
-        <v>111.38</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.98</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>77.98</v>
+        <v>77.08</v>
       </c>
       <c r="L31" t="n">
-        <v>78.5</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>112.97</v>
+        <v>117.49</v>
       </c>
       <c r="K32" t="n">
-        <v>80.51000000000001</v>
+        <v>83.73</v>
       </c>
       <c r="L32" t="n">
-        <v>138.72</v>
+        <v>144.28</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-9.74</v>
+        <v>-9.75</v>
       </c>
       <c r="K33" t="n">
-        <v>-148.38</v>
+        <v>-148.51</v>
       </c>
       <c r="L33" t="n">
-        <v>148.7</v>
+        <v>148.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-59.44</v>
+        <v>-63.57</v>
       </c>
       <c r="K34" t="n">
-        <v>101.07</v>
+        <v>108.1</v>
       </c>
       <c r="L34" t="n">
-        <v>117.25</v>
+        <v>125.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-168.63</v>
+        <v>-177.39</v>
       </c>
       <c r="K35" t="n">
-        <v>25.82</v>
+        <v>27.16</v>
       </c>
       <c r="L35" t="n">
-        <v>170.6</v>
+        <v>179.45</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>156.88</v>
+        <v>159.12</v>
       </c>
       <c r="K36" t="n">
-        <v>63.06</v>
+        <v>63.96</v>
       </c>
       <c r="L36" t="n">
-        <v>169.08</v>
+        <v>171.49</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>211.59</v>
+        <v>214.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-164.96</v>
+        <v>-167.15</v>
       </c>
       <c r="L37" t="n">
-        <v>268.3</v>
+        <v>271.86</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>108.85</v>
+        <v>114.55</v>
       </c>
       <c r="K38" t="n">
-        <v>-347.19</v>
+        <v>-365.38</v>
       </c>
       <c r="L38" t="n">
-        <v>363.85</v>
+        <v>382.92</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>321.85</v>
+        <v>344.8</v>
       </c>
       <c r="K39" t="n">
-        <v>-65.33</v>
+        <v>-69.98999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>328.41</v>
+        <v>351.84</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-297.11</v>
+        <v>-317.9</v>
       </c>
       <c r="K40" t="n">
-        <v>33.37</v>
+        <v>35.71</v>
       </c>
       <c r="L40" t="n">
-        <v>298.98</v>
+        <v>319.9</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-92.06</v>
+        <v>-104.49</v>
       </c>
       <c r="K41" t="n">
-        <v>-756.84</v>
+        <v>-859.01</v>
       </c>
       <c r="L41" t="n">
-        <v>762.42</v>
+        <v>865.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-201.67</v>
+        <v>-229.1</v>
       </c>
       <c r="K42" t="n">
-        <v>576.64</v>
+        <v>655.09</v>
       </c>
       <c r="L42" t="n">
-        <v>610.89</v>
+        <v>693.99</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-424.14</v>
+        <v>-440.46</v>
       </c>
       <c r="K43" t="n">
-        <v>-197.41</v>
+        <v>-205</v>
       </c>
       <c r="L43" t="n">
-        <v>467.83</v>
+        <v>485.83</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>71.76000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="K44" t="n">
-        <v>-95.22</v>
+        <v>-98.22</v>
       </c>
       <c r="L44" t="n">
-        <v>119.23</v>
+        <v>122.99</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-52.16</v>
+        <v>-54.74</v>
       </c>
       <c r="K45" t="n">
-        <v>107.15</v>
+        <v>112.45</v>
       </c>
       <c r="L45" t="n">
-        <v>119.17</v>
+        <v>125.07</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-98.87</v>
+        <v>-100.42</v>
       </c>
       <c r="K46" t="n">
-        <v>24.61</v>
+        <v>24.99</v>
       </c>
       <c r="L46" t="n">
-        <v>101.89</v>
+        <v>103.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>7.26</v>
+        <v>7.3</v>
       </c>
       <c r="K47" t="n">
-        <v>-180</v>
+        <v>-180.9</v>
       </c>
       <c r="L47" t="n">
-        <v>180.14</v>
+        <v>181.05</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>47.76</v>
+        <v>50.09</v>
       </c>
       <c r="K48" t="n">
-        <v>166.58</v>
+        <v>174.71</v>
       </c>
       <c r="L48" t="n">
-        <v>173.29</v>
+        <v>181.75</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>85.41</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-88.42</v>
+        <v>-89.73999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>122.93</v>
+        <v>124.77</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-182.76</v>
+        <v>-188.71</v>
       </c>
       <c r="K50" t="n">
-        <v>19.23</v>
+        <v>19.85</v>
       </c>
       <c r="L50" t="n">
-        <v>183.77</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-302.21</v>
+        <v>-332.78</v>
       </c>
       <c r="K51" t="n">
-        <v>-111.79</v>
+        <v>-123.1</v>
       </c>
       <c r="L51" t="n">
-        <v>322.23</v>
+        <v>354.82</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>195.44</v>
+        <v>208.7</v>
       </c>
       <c r="K52" t="n">
-        <v>41.45</v>
+        <v>44.26</v>
       </c>
       <c r="L52" t="n">
-        <v>199.79</v>
+        <v>213.34</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>346.16</v>
+        <v>364.53</v>
       </c>
       <c r="K53" t="n">
-        <v>188.98</v>
+        <v>199.02</v>
       </c>
       <c r="L53" t="n">
-        <v>394.38</v>
+        <v>415.32</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>83.58</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>160.23</v>
+        <v>177.05</v>
       </c>
       <c r="L54" t="n">
-        <v>180.72</v>
+        <v>199.69</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>432.52</v>
+        <v>455.02</v>
       </c>
       <c r="K55" t="n">
-        <v>-149.93</v>
+        <v>-157.73</v>
       </c>
       <c r="L55" t="n">
-        <v>457.76</v>
+        <v>481.58</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>342.37</v>
+        <v>394.21</v>
       </c>
       <c r="K56" t="n">
-        <v>-591.4</v>
+        <v>-680.96</v>
       </c>
       <c r="L56" t="n">
-        <v>683.35</v>
+        <v>786.84</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-231.46</v>
+        <v>-263.22</v>
       </c>
       <c r="K57" t="n">
-        <v>-656.39</v>
+        <v>-746.47</v>
       </c>
       <c r="L57" t="n">
-        <v>696.01</v>
+        <v>791.52</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-732.95</v>
+        <v>-830.61</v>
       </c>
       <c r="K58" t="n">
-        <v>-346.55</v>
+        <v>-392.72</v>
       </c>
       <c r="L58" t="n">
-        <v>810.75</v>
+        <v>918.77</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-92.08</v>
+        <v>-95.33</v>
       </c>
       <c r="K59" t="n">
-        <v>-15.96</v>
+        <v>-16.52</v>
       </c>
       <c r="L59" t="n">
-        <v>93.45999999999999</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-77.95</v>
+        <v>-83.17</v>
       </c>
       <c r="K60" t="n">
-        <v>11.88</v>
+        <v>12.68</v>
       </c>
       <c r="L60" t="n">
-        <v>78.84999999999999</v>
+        <v>84.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>59.16</v>
+        <v>58.2</v>
       </c>
       <c r="K61" t="n">
-        <v>-72.01000000000001</v>
+        <v>-70.84</v>
       </c>
       <c r="L61" t="n">
-        <v>93.2</v>
+        <v>91.68000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-233.64</v>
+        <v>-251.29</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.28</v>
+        <v>-65.91</v>
       </c>
       <c r="L62" t="n">
-        <v>241.55</v>
+        <v>259.79</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>176.73</v>
+        <v>182.22</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.46</v>
+        <v>-6.66</v>
       </c>
       <c r="L63" t="n">
-        <v>176.85</v>
+        <v>182.34</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-13.46</v>
+        <v>-14.17</v>
       </c>
       <c r="K64" t="n">
-        <v>-112.24</v>
+        <v>-118.12</v>
       </c>
       <c r="L64" t="n">
-        <v>113.05</v>
+        <v>118.97</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>23.13</v>
+        <v>25.46</v>
       </c>
       <c r="K65" t="n">
-        <v>215.42</v>
+        <v>237.05</v>
       </c>
       <c r="L65" t="n">
-        <v>216.66</v>
+        <v>238.42</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>188.82</v>
+        <v>198.38</v>
       </c>
       <c r="K66" t="n">
-        <v>15.83</v>
+        <v>16.63</v>
       </c>
       <c r="L66" t="n">
-        <v>189.48</v>
+        <v>199.07</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-75.7</v>
+        <v>-78.18000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>211.17</v>
+        <v>218.08</v>
       </c>
       <c r="L67" t="n">
-        <v>224.33</v>
+        <v>231.67</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>126.95</v>
+        <v>133.68</v>
       </c>
       <c r="K68" t="n">
-        <v>-303.27</v>
+        <v>-319.34</v>
       </c>
       <c r="L68" t="n">
-        <v>328.77</v>
+        <v>346.19</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-22.26</v>
+        <v>-25.34</v>
       </c>
       <c r="K69" t="n">
-        <v>486.03</v>
+        <v>553.14</v>
       </c>
       <c r="L69" t="n">
-        <v>486.54</v>
+        <v>553.72</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>36.12</v>
+        <v>39.86</v>
       </c>
       <c r="K70" t="n">
-        <v>-243.4</v>
+        <v>-268.6</v>
       </c>
       <c r="L70" t="n">
-        <v>246.07</v>
+        <v>271.54</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-319.19</v>
+        <v>-353.38</v>
       </c>
       <c r="K71" t="n">
-        <v>-751.85</v>
+        <v>-832.41</v>
       </c>
       <c r="L71" t="n">
-        <v>816.8</v>
+        <v>904.3099999999999</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>242.79</v>
+        <v>268.81</v>
       </c>
       <c r="K72" t="n">
-        <v>428.18</v>
+        <v>474.05</v>
       </c>
       <c r="L72" t="n">
-        <v>492.22</v>
+        <v>544.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>183.85</v>
+        <v>192.29</v>
       </c>
       <c r="K73" t="n">
-        <v>-533.83</v>
+        <v>-558.33</v>
       </c>
       <c r="L73" t="n">
-        <v>564.6</v>
+        <v>590.51</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>96.44</v>
+        <v>99.08</v>
       </c>
       <c r="K74" t="n">
-        <v>-40.11</v>
+        <v>-41.21</v>
       </c>
       <c r="L74" t="n">
-        <v>104.45</v>
+        <v>107.31</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-90.95</v>
+        <v>-87.43000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>25.76</v>
+        <v>24.76</v>
       </c>
       <c r="L75" t="n">
-        <v>94.53</v>
+        <v>90.87</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-87.43000000000001</v>
+        <v>-88.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-164.39</v>
+        <v>-166.86</v>
       </c>
       <c r="L76" t="n">
-        <v>186.19</v>
+        <v>188.99</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-99.12</v>
+        <v>-97.06</v>
       </c>
       <c r="K77" t="n">
-        <v>-44.77</v>
+        <v>-43.85</v>
       </c>
       <c r="L77" t="n">
-        <v>108.76</v>
+        <v>106.51</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-76.48</v>
+        <v>-80.16</v>
       </c>
       <c r="K78" t="n">
-        <v>-114.53</v>
+        <v>-120.05</v>
       </c>
       <c r="L78" t="n">
-        <v>137.72</v>
+        <v>144.35</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>181.82</v>
+        <v>193.69</v>
       </c>
       <c r="K79" t="n">
-        <v>-29.1</v>
+        <v>-31</v>
       </c>
       <c r="L79" t="n">
-        <v>184.14</v>
+        <v>196.16</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>171.07</v>
+        <v>188.25</v>
       </c>
       <c r="K80" t="n">
-        <v>-203.11</v>
+        <v>-223.51</v>
       </c>
       <c r="L80" t="n">
-        <v>265.55</v>
+        <v>292.22</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-76.11</v>
+        <v>-79.95999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-270.88</v>
+        <v>-284.59</v>
       </c>
       <c r="L81" t="n">
-        <v>281.37</v>
+        <v>295.61</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-117.57</v>
+        <v>-129.45</v>
       </c>
       <c r="K82" t="n">
-        <v>-267.74</v>
+        <v>-294.79</v>
       </c>
       <c r="L82" t="n">
-        <v>292.42</v>
+        <v>321.96</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.49</v>
+        <v>-3.74</v>
       </c>
       <c r="K83" t="n">
-        <v>439.08</v>
+        <v>470.24</v>
       </c>
       <c r="L83" t="n">
-        <v>439.09</v>
+        <v>470.26</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.82</v>
+        <v>-0.93</v>
       </c>
       <c r="K84" t="n">
-        <v>-429.66</v>
+        <v>-488.4</v>
       </c>
       <c r="L84" t="n">
-        <v>429.66</v>
+        <v>488.4</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>585.98</v>
+        <v>657.9</v>
       </c>
       <c r="K85" t="n">
-        <v>-56.59</v>
+        <v>-63.54</v>
       </c>
       <c r="L85" t="n">
-        <v>588.71</v>
+        <v>660.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>552.3</v>
+        <v>618.2</v>
       </c>
       <c r="K86" t="n">
-        <v>120.74</v>
+        <v>135.15</v>
       </c>
       <c r="L86" t="n">
-        <v>565.34</v>
+        <v>632.8</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-197.64</v>
+        <v>-218.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-160.62</v>
+        <v>-177.83</v>
       </c>
       <c r="L87" t="n">
-        <v>254.68</v>
+        <v>281.97</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-266.22</v>
+        <v>-276.46</v>
       </c>
       <c r="K88" t="n">
-        <v>-535.98</v>
+        <v>-556.6</v>
       </c>
       <c r="L88" t="n">
-        <v>598.46</v>
+        <v>621.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>6.94</v>
+        <v>7.18</v>
       </c>
       <c r="F14" t="n">
-        <v>15.27</v>
+        <v>15.3</v>
       </c>
       <c r="G14" t="n">
-        <v>146.4</v>
+        <v>144.4</v>
       </c>
       <c r="H14" t="n">
-        <v>93.59999999999999</v>
+        <v>54.7</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-82.25</v>
+        <v>28.76</v>
       </c>
       <c r="K14" t="n">
-        <v>29.42</v>
+        <v>-116.57</v>
       </c>
       <c r="L14" t="n">
-        <v>87.34999999999999</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:00:29</t>
+          <t>05:59:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6.98</v>
+        <v>6.46</v>
       </c>
       <c r="F15" t="n">
-        <v>14.82</v>
+        <v>16.2</v>
       </c>
       <c r="G15" t="n">
-        <v>166.6</v>
+        <v>161.2</v>
       </c>
       <c r="H15" t="n">
-        <v>91.7</v>
+        <v>71.7</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-35.45</v>
+        <v>-35.41</v>
       </c>
       <c r="K15" t="n">
-        <v>65.73999999999999</v>
+        <v>-141.11</v>
       </c>
       <c r="L15" t="n">
-        <v>74.69</v>
+        <v>145.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:02:51</t>
+          <t>06:01:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.18</v>
+        <v>6.45</v>
       </c>
       <c r="F16" t="n">
-        <v>13.41</v>
+        <v>13.07</v>
       </c>
       <c r="G16" t="n">
-        <v>131.5</v>
+        <v>143.1</v>
       </c>
       <c r="H16" t="n">
-        <v>95.7</v>
+        <v>60.6</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.96</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-52.65</v>
+        <v>-168.07</v>
       </c>
       <c r="L16" t="n">
-        <v>69.89</v>
+        <v>182.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:07:11</t>
+          <t>06:06:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>7.34</v>
+        <v>5.4</v>
       </c>
       <c r="F17" t="n">
-        <v>16.69</v>
+        <v>14.54</v>
       </c>
       <c r="G17" t="n">
-        <v>148.3</v>
+        <v>159.3</v>
       </c>
       <c r="H17" t="n">
-        <v>91.8</v>
+        <v>35.8</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
-        <v>-88.33</v>
+        <v>-28.03</v>
       </c>
       <c r="K17" t="n">
-        <v>129.21</v>
+        <v>-164.51</v>
       </c>
       <c r="L17" t="n">
-        <v>156.52</v>
+        <v>166.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:09:42</t>
+          <t>06:07:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,31 +796,31 @@
         <v>6.42</v>
       </c>
       <c r="F18" t="n">
-        <v>15.15</v>
+        <v>19.08</v>
       </c>
       <c r="G18" t="n">
-        <v>165.2</v>
+        <v>154.3</v>
       </c>
       <c r="H18" t="n">
-        <v>87.5</v>
+        <v>29.9</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-41.49</v>
+        <v>35.62</v>
       </c>
       <c r="K18" t="n">
-        <v>97.04000000000001</v>
+        <v>-171.19</v>
       </c>
       <c r="L18" t="n">
-        <v>105.53</v>
+        <v>174.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:10:23</t>
+          <t>06:09:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.96</v>
+        <v>7.23</v>
       </c>
       <c r="F19" t="n">
-        <v>14.46</v>
+        <v>15.45</v>
       </c>
       <c r="G19" t="n">
-        <v>168.5</v>
+        <v>161.1</v>
       </c>
       <c r="H19" t="n">
-        <v>91.09999999999999</v>
+        <v>59</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-156.92</v>
+        <v>197.25</v>
       </c>
       <c r="K19" t="n">
-        <v>12.05</v>
+        <v>45.69</v>
       </c>
       <c r="L19" t="n">
-        <v>157.39</v>
+        <v>202.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:14:17</t>
+          <t>06:14:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>6.43</v>
+        <v>5.91</v>
       </c>
       <c r="F20" t="n">
-        <v>16.21</v>
+        <v>12.77</v>
       </c>
       <c r="G20" t="n">
-        <v>151.6</v>
+        <v>156.4</v>
       </c>
       <c r="H20" t="n">
-        <v>91.09999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>124.77</v>
+        <v>186.15</v>
       </c>
       <c r="K20" t="n">
-        <v>-138.62</v>
+        <v>191.58</v>
       </c>
       <c r="L20" t="n">
-        <v>186.5</v>
+        <v>267.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:16:34</t>
+          <t>06:15:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.87</v>
+        <v>5.8</v>
       </c>
       <c r="F21" t="n">
-        <v>13.18</v>
+        <v>12.6</v>
       </c>
       <c r="G21" t="n">
-        <v>152.7</v>
+        <v>163.6</v>
       </c>
       <c r="H21" t="n">
-        <v>84.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I21" t="n">
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-61.91</v>
+        <v>-8.6</v>
       </c>
       <c r="K21" t="n">
-        <v>161.94</v>
+        <v>-253.79</v>
       </c>
       <c r="L21" t="n">
-        <v>173.37</v>
+        <v>253.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:18:39</t>
+          <t>06:16:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6.72</v>
+        <v>6.71</v>
       </c>
       <c r="F22" t="n">
-        <v>13.64</v>
+        <v>16.76</v>
       </c>
       <c r="G22" t="n">
-        <v>142.3</v>
+        <v>144.7</v>
       </c>
       <c r="H22" t="n">
-        <v>97.40000000000001</v>
+        <v>38.8</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>217.03</v>
+        <v>-78.98</v>
       </c>
       <c r="K22" t="n">
-        <v>44.71</v>
+        <v>-34.89</v>
       </c>
       <c r="L22" t="n">
-        <v>221.59</v>
+        <v>86.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:22:53</t>
+          <t>06:20:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.98</v>
+        <v>6.15</v>
       </c>
       <c r="F23" t="n">
-        <v>13.9</v>
+        <v>17.22</v>
       </c>
       <c r="G23" t="n">
-        <v>135.5</v>
+        <v>167.1</v>
       </c>
       <c r="H23" t="n">
-        <v>89.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>68.45</v>
+        <v>317.55</v>
       </c>
       <c r="K23" t="n">
-        <v>-264.56</v>
+        <v>-2.99</v>
       </c>
       <c r="L23" t="n">
-        <v>273.27</v>
+        <v>317.56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:23:37</t>
+          <t>06:23:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>7.07</v>
+        <v>6.16</v>
       </c>
       <c r="F24" t="n">
-        <v>13.81</v>
+        <v>15.62</v>
       </c>
       <c r="G24" t="n">
-        <v>156</v>
+        <v>156.5</v>
       </c>
       <c r="H24" t="n">
-        <v>91.7</v>
+        <v>48</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-287.31</v>
+        <v>97.02</v>
       </c>
       <c r="K24" t="n">
-        <v>-80.63</v>
+        <v>-315.21</v>
       </c>
       <c r="L24" t="n">
-        <v>298.41</v>
+        <v>329.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:25:09</t>
+          <t>06:24:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.64</v>
+        <v>6.53</v>
       </c>
       <c r="F25" t="n">
-        <v>12.66</v>
+        <v>15.2</v>
       </c>
       <c r="G25" t="n">
-        <v>148.2</v>
+        <v>155.2</v>
       </c>
       <c r="H25" t="n">
-        <v>88.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>201.1</v>
+        <v>144.78</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.34</v>
+        <v>-232.4</v>
       </c>
       <c r="L25" t="n">
-        <v>201.1</v>
+        <v>273.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:29:21</t>
+          <t>06:31:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6.31</v>
+        <v>6.58</v>
       </c>
       <c r="F26" t="n">
-        <v>12.12</v>
+        <v>17.46</v>
       </c>
       <c r="G26" t="n">
-        <v>155.4</v>
+        <v>157.2</v>
       </c>
       <c r="H26" t="n">
-        <v>94</v>
+        <v>40.3</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>30.28</v>
+        <v>292.54</v>
       </c>
       <c r="K26" t="n">
-        <v>385.06</v>
+        <v>-425.3</v>
       </c>
       <c r="L26" t="n">
-        <v>386.25</v>
+        <v>516.1900000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:31:10</t>
+          <t>06:33:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.63</v>
+        <v>6.68</v>
       </c>
       <c r="F27" t="n">
-        <v>12.1</v>
+        <v>16.41</v>
       </c>
       <c r="G27" t="n">
-        <v>134.2</v>
+        <v>151.5</v>
       </c>
       <c r="H27" t="n">
-        <v>93.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>68.23999999999999</v>
+        <v>374.82</v>
       </c>
       <c r="K27" t="n">
-        <v>-332.01</v>
+        <v>53.27</v>
       </c>
       <c r="L27" t="n">
-        <v>338.95</v>
+        <v>378.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:32:14</t>
+          <t>06:35:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.77</v>
+        <v>5.86</v>
       </c>
       <c r="F28" t="n">
-        <v>14.7</v>
+        <v>15.04</v>
       </c>
       <c r="G28" t="n">
-        <v>146.3</v>
+        <v>142.2</v>
       </c>
       <c r="H28" t="n">
-        <v>92</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-102.92</v>
+        <v>4.73</v>
       </c>
       <c r="K28" t="n">
-        <v>-400.08</v>
+        <v>-550.76</v>
       </c>
       <c r="L28" t="n">
-        <v>413.1</v>
+        <v>550.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:41:48</t>
+          <t>06:46:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.97</v>
+        <v>7.42</v>
       </c>
       <c r="F29" t="n">
-        <v>19.77</v>
+        <v>17.49</v>
       </c>
       <c r="G29" t="n">
-        <v>143.2</v>
+        <v>153.8</v>
       </c>
       <c r="H29" t="n">
-        <v>95.2</v>
+        <v>63.3</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-115.59</v>
+        <v>104.57</v>
       </c>
       <c r="K29" t="n">
-        <v>18.62</v>
+        <v>64.75</v>
       </c>
       <c r="L29" t="n">
-        <v>117.08</v>
+        <v>122.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:42:53</t>
+          <t>06:47:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.66</v>
+        <v>6.91</v>
       </c>
       <c r="F30" t="n">
-        <v>14.96</v>
+        <v>16.01</v>
       </c>
       <c r="G30" t="n">
-        <v>151.4</v>
+        <v>162.5</v>
       </c>
       <c r="H30" t="n">
-        <v>85</v>
+        <v>70.2</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>-47.05</v>
+        <v>-59.7</v>
       </c>
       <c r="K30" t="n">
-        <v>107.44</v>
+        <v>-146.88</v>
       </c>
       <c r="L30" t="n">
-        <v>117.29</v>
+        <v>158.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:44:05</t>
+          <t>06:50:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.58</v>
+        <v>7.04</v>
       </c>
       <c r="F31" t="n">
-        <v>15.52</v>
+        <v>17.44</v>
       </c>
       <c r="G31" t="n">
-        <v>138.2</v>
+        <v>145</v>
       </c>
       <c r="H31" t="n">
-        <v>89.90000000000001</v>
+        <v>50.5</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.880000000000001</v>
+        <v>-91.88</v>
       </c>
       <c r="K31" t="n">
-        <v>77.08</v>
+        <v>137.48</v>
       </c>
       <c r="L31" t="n">
-        <v>77.59</v>
+        <v>165.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:48:59</t>
+          <t>06:55:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.23</v>
+        <v>6.8</v>
       </c>
       <c r="F32" t="n">
-        <v>14.19</v>
+        <v>18.25</v>
       </c>
       <c r="G32" t="n">
-        <v>154.3</v>
+        <v>143.9</v>
       </c>
       <c r="H32" t="n">
-        <v>95</v>
+        <v>56.3</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>117.49</v>
+        <v>-6.18</v>
       </c>
       <c r="K32" t="n">
-        <v>83.73</v>
+        <v>234.08</v>
       </c>
       <c r="L32" t="n">
-        <v>144.28</v>
+        <v>234.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:49:47</t>
+          <t>06:57:24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>7.12</v>
+        <v>6.62</v>
       </c>
       <c r="F33" t="n">
-        <v>16.68</v>
+        <v>17.05</v>
       </c>
       <c r="G33" t="n">
-        <v>153.2</v>
+        <v>162.5</v>
       </c>
       <c r="H33" t="n">
-        <v>93</v>
+        <v>93.8</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-9.75</v>
+        <v>-194.58</v>
       </c>
       <c r="K33" t="n">
-        <v>-148.51</v>
+        <v>-56.66</v>
       </c>
       <c r="L33" t="n">
-        <v>148.83</v>
+        <v>202.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:51:15</t>
+          <t>06:58:49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>6.65</v>
+        <v>6.87</v>
       </c>
       <c r="F34" t="n">
-        <v>17.43</v>
+        <v>18.68</v>
       </c>
       <c r="G34" t="n">
-        <v>167.1</v>
+        <v>146.3</v>
       </c>
       <c r="H34" t="n">
-        <v>91.59999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-63.57</v>
+        <v>-7.7</v>
       </c>
       <c r="K34" t="n">
-        <v>108.1</v>
+        <v>-193.18</v>
       </c>
       <c r="L34" t="n">
-        <v>125.41</v>
+        <v>193.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:56:25</t>
+          <t>07:02:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.9</v>
+        <v>7.04</v>
       </c>
       <c r="F35" t="n">
-        <v>15.3</v>
+        <v>18.02</v>
       </c>
       <c r="G35" t="n">
-        <v>143.6</v>
+        <v>147.9</v>
       </c>
       <c r="H35" t="n">
-        <v>90</v>
+        <v>26.3</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-177.39</v>
+        <v>-10.78</v>
       </c>
       <c r="K35" t="n">
-        <v>27.16</v>
+        <v>-87.04000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>179.45</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:57:31</t>
+          <t>07:04:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.74</v>
+        <v>7.66</v>
       </c>
       <c r="F36" t="n">
-        <v>16.92</v>
+        <v>20.76</v>
       </c>
       <c r="G36" t="n">
-        <v>149.8</v>
+        <v>133</v>
       </c>
       <c r="H36" t="n">
-        <v>87</v>
+        <v>59.9</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>159.12</v>
+        <v>-165.81</v>
       </c>
       <c r="K36" t="n">
-        <v>63.96</v>
+        <v>-214</v>
       </c>
       <c r="L36" t="n">
-        <v>171.49</v>
+        <v>270.72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:58:59</t>
+          <t>07:06:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,25 +1591,25 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>8.17</v>
+        <v>7.19</v>
       </c>
       <c r="F37" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="G37" t="n">
-        <v>154.9</v>
+        <v>145</v>
       </c>
       <c r="H37" t="n">
-        <v>90.90000000000001</v>
+        <v>29.7</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>214.4</v>
+        <v>-266.36</v>
       </c>
       <c r="K37" t="n">
-        <v>-167.15</v>
+        <v>-54.38</v>
       </c>
       <c r="L37" t="n">
         <v>271.86</v>
@@ -1618,7 +1618,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:03:14</t>
+          <t>07:11:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>7.34</v>
+        <v>6.5</v>
       </c>
       <c r="F38" t="n">
-        <v>18.47</v>
+        <v>13.44</v>
       </c>
       <c r="G38" t="n">
-        <v>171.2</v>
+        <v>151.9</v>
       </c>
       <c r="H38" t="n">
-        <v>88.8</v>
+        <v>53.4</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>114.55</v>
+        <v>-66.81</v>
       </c>
       <c r="K38" t="n">
-        <v>-365.38</v>
+        <v>-366.52</v>
       </c>
       <c r="L38" t="n">
-        <v>382.92</v>
+        <v>372.56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:03:53</t>
+          <t>07:13:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>7.81</v>
+        <v>6.78</v>
       </c>
       <c r="F39" t="n">
-        <v>18.62</v>
+        <v>16.9</v>
       </c>
       <c r="G39" t="n">
-        <v>147.7</v>
+        <v>147.4</v>
       </c>
       <c r="H39" t="n">
-        <v>91.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>344.8</v>
+        <v>151.27</v>
       </c>
       <c r="K39" t="n">
-        <v>-69.98999999999999</v>
+        <v>-307.85</v>
       </c>
       <c r="L39" t="n">
-        <v>351.84</v>
+        <v>343.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:05:42</t>
+          <t>07:14:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>6.76</v>
+        <v>7.07</v>
       </c>
       <c r="F40" t="n">
-        <v>17.41</v>
+        <v>19.26</v>
       </c>
       <c r="G40" t="n">
-        <v>146.7</v>
+        <v>167</v>
       </c>
       <c r="H40" t="n">
-        <v>90.3</v>
+        <v>49.4</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-317.9</v>
+        <v>298.13</v>
       </c>
       <c r="K40" t="n">
-        <v>35.71</v>
+        <v>68.16</v>
       </c>
       <c r="L40" t="n">
-        <v>319.9</v>
+        <v>305.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:10:42</t>
+          <t>07:18:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>6.63</v>
+        <v>7.22</v>
       </c>
       <c r="F41" t="n">
-        <v>15.38</v>
+        <v>20.93</v>
       </c>
       <c r="G41" t="n">
-        <v>154.4</v>
+        <v>163.3</v>
       </c>
       <c r="H41" t="n">
-        <v>86.2</v>
+        <v>54.6</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-104.49</v>
+        <v>-309.25</v>
       </c>
       <c r="K41" t="n">
-        <v>-859.01</v>
+        <v>-366.21</v>
       </c>
       <c r="L41" t="n">
-        <v>865.35</v>
+        <v>479.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:12:46</t>
+          <t>07:20:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6.97</v>
+        <v>6.72</v>
       </c>
       <c r="F42" t="n">
-        <v>15.36</v>
+        <v>18.05</v>
       </c>
       <c r="G42" t="n">
-        <v>141.3</v>
+        <v>143.8</v>
       </c>
       <c r="H42" t="n">
-        <v>94.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-229.1</v>
+        <v>141.31</v>
       </c>
       <c r="K42" t="n">
-        <v>655.09</v>
+        <v>-471.2</v>
       </c>
       <c r="L42" t="n">
-        <v>693.99</v>
+        <v>491.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:14:34</t>
+          <t>07:22:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>7.28</v>
+        <v>8.4</v>
       </c>
       <c r="F43" t="n">
-        <v>17.05</v>
+        <v>20.93</v>
       </c>
       <c r="G43" t="n">
-        <v>150.4</v>
+        <v>160.1</v>
       </c>
       <c r="H43" t="n">
-        <v>89.09999999999999</v>
+        <v>50.8</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-440.46</v>
+        <v>335.38</v>
       </c>
       <c r="K43" t="n">
-        <v>-205</v>
+        <v>-393.91</v>
       </c>
       <c r="L43" t="n">
-        <v>485.83</v>
+        <v>517.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:22:43</t>
+          <t>07:31:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>7.46</v>
+        <v>7.08</v>
       </c>
       <c r="F44" t="n">
-        <v>18.79</v>
+        <v>17.33</v>
       </c>
       <c r="G44" t="n">
-        <v>137.9</v>
+        <v>141.1</v>
       </c>
       <c r="H44" t="n">
-        <v>88.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>74.02</v>
+        <v>160.47</v>
       </c>
       <c r="K44" t="n">
-        <v>-98.22</v>
+        <v>61.94</v>
       </c>
       <c r="L44" t="n">
-        <v>122.99</v>
+        <v>172.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:24:57</t>
+          <t>07:33:05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>7.1</v>
+        <v>7.24</v>
       </c>
       <c r="F45" t="n">
-        <v>18.26</v>
+        <v>15.83</v>
       </c>
       <c r="G45" t="n">
-        <v>149.9</v>
+        <v>160.9</v>
       </c>
       <c r="H45" t="n">
-        <v>85.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-54.74</v>
+        <v>142.36</v>
       </c>
       <c r="K45" t="n">
-        <v>112.45</v>
+        <v>-58.25</v>
       </c>
       <c r="L45" t="n">
-        <v>125.07</v>
+        <v>153.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:25:57</t>
+          <t>07:33:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>7.45</v>
+        <v>7.2</v>
       </c>
       <c r="F46" t="n">
-        <v>20.93</v>
+        <v>20.24</v>
       </c>
       <c r="G46" t="n">
-        <v>151.7</v>
+        <v>144.8</v>
       </c>
       <c r="H46" t="n">
-        <v>84.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-100.42</v>
+        <v>-128.91</v>
       </c>
       <c r="K46" t="n">
-        <v>24.99</v>
+        <v>-51.04</v>
       </c>
       <c r="L46" t="n">
-        <v>103.48</v>
+        <v>138.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:31:19</t>
+          <t>07:37:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.32</v>
+        <v>7.33</v>
       </c>
       <c r="F47" t="n">
-        <v>17.86</v>
+        <v>20.93</v>
       </c>
       <c r="G47" t="n">
-        <v>144.1</v>
+        <v>147.9</v>
       </c>
       <c r="H47" t="n">
-        <v>82.7</v>
+        <v>62.7</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>7.3</v>
+        <v>190.96</v>
       </c>
       <c r="K47" t="n">
-        <v>-180.9</v>
+        <v>36.92</v>
       </c>
       <c r="L47" t="n">
-        <v>181.05</v>
+        <v>194.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:32:24</t>
+          <t>07:39:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>7.69</v>
+        <v>7.66</v>
       </c>
       <c r="F48" t="n">
-        <v>18.47</v>
+        <v>20.25</v>
       </c>
       <c r="G48" t="n">
-        <v>146.4</v>
+        <v>153.2</v>
       </c>
       <c r="H48" t="n">
-        <v>94.09999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>50.09</v>
+        <v>71.06</v>
       </c>
       <c r="K48" t="n">
-        <v>174.71</v>
+        <v>167.87</v>
       </c>
       <c r="L48" t="n">
-        <v>181.75</v>
+        <v>182.29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:34:44</t>
+          <t>07:40:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>7.93</v>
+        <v>6.99</v>
       </c>
       <c r="F49" t="n">
-        <v>20.93</v>
+        <v>18.88</v>
       </c>
       <c r="G49" t="n">
-        <v>157</v>
+        <v>162.8</v>
       </c>
       <c r="H49" t="n">
-        <v>85.09999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>86.68000000000001</v>
+        <v>-43.91</v>
       </c>
       <c r="K49" t="n">
-        <v>-89.73999999999999</v>
+        <v>172.09</v>
       </c>
       <c r="L49" t="n">
-        <v>124.77</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:40:56</t>
+          <t>07:45:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7.32</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>14.13</v>
+        <v>20.5</v>
       </c>
       <c r="G50" t="n">
-        <v>156.9</v>
+        <v>148</v>
       </c>
       <c r="H50" t="n">
-        <v>90.8</v>
+        <v>68.2</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-188.71</v>
+        <v>191.74</v>
       </c>
       <c r="K50" t="n">
-        <v>19.85</v>
+        <v>-200.83</v>
       </c>
       <c r="L50" t="n">
-        <v>189.75</v>
+        <v>277.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:43:20</t>
+          <t>07:47:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2182,31 +2182,31 @@
         <v>6.98</v>
       </c>
       <c r="F51" t="n">
-        <v>18.53</v>
+        <v>16.53</v>
       </c>
       <c r="G51" t="n">
-        <v>154.7</v>
+        <v>156.4</v>
       </c>
       <c r="H51" t="n">
-        <v>94.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-332.78</v>
+        <v>-67.95</v>
       </c>
       <c r="K51" t="n">
-        <v>-123.1</v>
+        <v>-212.45</v>
       </c>
       <c r="L51" t="n">
-        <v>354.82</v>
+        <v>223.05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:44:53</t>
+          <t>07:49:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>7.49</v>
+        <v>7.28</v>
       </c>
       <c r="F52" t="n">
-        <v>20.63</v>
+        <v>16.83</v>
       </c>
       <c r="G52" t="n">
-        <v>162.1</v>
+        <v>150.2</v>
       </c>
       <c r="H52" t="n">
-        <v>90.7</v>
+        <v>62.9</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>208.7</v>
+        <v>210.28</v>
       </c>
       <c r="K52" t="n">
-        <v>44.26</v>
+        <v>-172.88</v>
       </c>
       <c r="L52" t="n">
-        <v>213.34</v>
+        <v>272.22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:50:50</t>
+          <t>07:53:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7.96</v>
+        <v>6.46</v>
       </c>
       <c r="F53" t="n">
-        <v>19.97</v>
+        <v>17.12</v>
       </c>
       <c r="G53" t="n">
-        <v>153.7</v>
+        <v>136</v>
       </c>
       <c r="H53" t="n">
-        <v>96.3</v>
+        <v>56.5</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>364.53</v>
+        <v>64.95</v>
       </c>
       <c r="K53" t="n">
-        <v>199.02</v>
+        <v>-324.74</v>
       </c>
       <c r="L53" t="n">
-        <v>415.32</v>
+        <v>331.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:53:11</t>
+          <t>07:53:49</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="F54" t="n">
-        <v>19.78</v>
+        <v>20.71</v>
       </c>
       <c r="G54" t="n">
-        <v>157.7</v>
+        <v>159.5</v>
       </c>
       <c r="H54" t="n">
-        <v>97.7</v>
+        <v>74.7</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>92.34999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="K54" t="n">
-        <v>177.05</v>
+        <v>-3.72</v>
       </c>
       <c r="L54" t="n">
-        <v>199.69</v>
+        <v>91.93000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:55:34</t>
+          <t>07:55:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>7.05</v>
+        <v>7.74</v>
       </c>
       <c r="F55" t="n">
-        <v>16.72</v>
+        <v>17.9</v>
       </c>
       <c r="G55" t="n">
-        <v>148.3</v>
+        <v>158</v>
       </c>
       <c r="H55" t="n">
-        <v>85.5</v>
+        <v>54.5</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>455.02</v>
+        <v>-140.34</v>
       </c>
       <c r="K55" t="n">
-        <v>-157.73</v>
+        <v>-373.05</v>
       </c>
       <c r="L55" t="n">
-        <v>481.58</v>
+        <v>398.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:58:36</t>
+          <t>07:59:44</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.75</v>
+        <v>7.43</v>
       </c>
       <c r="F56" t="n">
-        <v>20.19</v>
+        <v>16.85</v>
       </c>
       <c r="G56" t="n">
-        <v>143.8</v>
+        <v>162.4</v>
       </c>
       <c r="H56" t="n">
-        <v>78.90000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>394.21</v>
+        <v>-404.28</v>
       </c>
       <c r="K56" t="n">
-        <v>-680.96</v>
+        <v>-172.12</v>
       </c>
       <c r="L56" t="n">
-        <v>786.84</v>
+        <v>439.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:00:48</t>
+          <t>08:01:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>7.13</v>
+        <v>6.41</v>
       </c>
       <c r="F57" t="n">
-        <v>19.94</v>
+        <v>15.98</v>
       </c>
       <c r="G57" t="n">
-        <v>147.5</v>
+        <v>161.1</v>
       </c>
       <c r="H57" t="n">
-        <v>91.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-263.22</v>
+        <v>190.58</v>
       </c>
       <c r="K57" t="n">
-        <v>-746.47</v>
+        <v>379.59</v>
       </c>
       <c r="L57" t="n">
-        <v>791.52</v>
+        <v>424.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:02:40</t>
+          <t>08:03:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.14</v>
+        <v>7.7</v>
       </c>
       <c r="F58" t="n">
-        <v>14.67</v>
+        <v>20.93</v>
       </c>
       <c r="G58" t="n">
-        <v>154.3</v>
+        <v>167.8</v>
       </c>
       <c r="H58" t="n">
-        <v>85.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-830.61</v>
+        <v>246.55</v>
       </c>
       <c r="K58" t="n">
-        <v>-392.72</v>
+        <v>-332.71</v>
       </c>
       <c r="L58" t="n">
-        <v>918.77</v>
+        <v>414.11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:11:42</t>
+          <t>08:13:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.95</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>20.63</v>
+        <v>20.93</v>
       </c>
       <c r="G59" t="n">
-        <v>151.6</v>
+        <v>149.9</v>
       </c>
       <c r="H59" t="n">
-        <v>93.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-95.33</v>
+        <v>74.78</v>
       </c>
       <c r="K59" t="n">
-        <v>-16.52</v>
+        <v>139.18</v>
       </c>
       <c r="L59" t="n">
-        <v>96.75</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:12:48</t>
+          <t>08:15:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.78</v>
+        <v>7.58</v>
       </c>
       <c r="F60" t="n">
-        <v>17.48</v>
+        <v>20.79</v>
       </c>
       <c r="G60" t="n">
-        <v>159.7</v>
+        <v>152.3</v>
       </c>
       <c r="H60" t="n">
-        <v>86.3</v>
+        <v>66.3</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-83.17</v>
+        <v>-21.11</v>
       </c>
       <c r="K60" t="n">
-        <v>12.68</v>
+        <v>-134.73</v>
       </c>
       <c r="L60" t="n">
-        <v>84.13</v>
+        <v>136.37</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:14:02</t>
+          <t>08:16:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>7.19</v>
+        <v>6.55</v>
       </c>
       <c r="F61" t="n">
-        <v>19.04</v>
+        <v>15.79</v>
       </c>
       <c r="G61" t="n">
-        <v>138.8</v>
+        <v>156.5</v>
       </c>
       <c r="H61" t="n">
-        <v>86.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>58.2</v>
+        <v>125.32</v>
       </c>
       <c r="K61" t="n">
-        <v>-70.84</v>
+        <v>-25.35</v>
       </c>
       <c r="L61" t="n">
-        <v>91.68000000000001</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:17:35</t>
+          <t>08:21:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>8.73</v>
+        <v>6.6</v>
       </c>
       <c r="F62" t="n">
-        <v>20.93</v>
+        <v>18.63</v>
       </c>
       <c r="G62" t="n">
-        <v>166.6</v>
+        <v>156.7</v>
       </c>
       <c r="H62" t="n">
-        <v>93.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-251.29</v>
+        <v>200.68</v>
       </c>
       <c r="K62" t="n">
-        <v>-65.91</v>
+        <v>-58.88</v>
       </c>
       <c r="L62" t="n">
-        <v>259.79</v>
+        <v>209.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:18:48</t>
+          <t>08:22:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>8.09</v>
+        <v>7.78</v>
       </c>
       <c r="F63" t="n">
         <v>20.93</v>
       </c>
       <c r="G63" t="n">
-        <v>144.3</v>
+        <v>157.4</v>
       </c>
       <c r="H63" t="n">
-        <v>93.3</v>
+        <v>14.6</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>182.22</v>
+        <v>134.58</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.66</v>
+        <v>-199.09</v>
       </c>
       <c r="L63" t="n">
-        <v>182.34</v>
+        <v>240.31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:20:54</t>
+          <t>08:24:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.92</v>
+        <v>7.38</v>
       </c>
       <c r="F64" t="n">
-        <v>17.29</v>
+        <v>20.76</v>
       </c>
       <c r="G64" t="n">
-        <v>141.5</v>
+        <v>161.7</v>
       </c>
       <c r="H64" t="n">
-        <v>87.3</v>
+        <v>31.1</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-14.17</v>
+        <v>30.81</v>
       </c>
       <c r="K64" t="n">
-        <v>-118.12</v>
+        <v>-233.7</v>
       </c>
       <c r="L64" t="n">
-        <v>118.97</v>
+        <v>235.73</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:25:43</t>
+          <t>08:29:33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>7.95</v>
+        <v>6.87</v>
       </c>
       <c r="F65" t="n">
-        <v>20.93</v>
+        <v>18.44</v>
       </c>
       <c r="G65" t="n">
-        <v>154.7</v>
+        <v>153.2</v>
       </c>
       <c r="H65" t="n">
-        <v>89.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>25.46</v>
+        <v>128.34</v>
       </c>
       <c r="K65" t="n">
-        <v>237.05</v>
+        <v>-253.69</v>
       </c>
       <c r="L65" t="n">
-        <v>238.42</v>
+        <v>284.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:27:40</t>
+          <t>08:30:50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>7.32</v>
+        <v>7.01</v>
       </c>
       <c r="F66" t="n">
-        <v>18.66</v>
+        <v>17.47</v>
       </c>
       <c r="G66" t="n">
-        <v>153.9</v>
+        <v>150.1</v>
       </c>
       <c r="H66" t="n">
-        <v>82.8</v>
+        <v>90</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J66" t="n">
-        <v>198.38</v>
+        <v>251.3</v>
       </c>
       <c r="K66" t="n">
-        <v>16.63</v>
+        <v>58.61</v>
       </c>
       <c r="L66" t="n">
-        <v>199.07</v>
+        <v>258.04</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:29:57</t>
+          <t>08:32:08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>7.13</v>
+        <v>7.06</v>
       </c>
       <c r="F67" t="n">
-        <v>19.8</v>
+        <v>20.21</v>
       </c>
       <c r="G67" t="n">
-        <v>160.7</v>
+        <v>144.1</v>
       </c>
       <c r="H67" t="n">
-        <v>87.90000000000001</v>
+        <v>53.7</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-78.18000000000001</v>
+        <v>-177.55</v>
       </c>
       <c r="K67" t="n">
-        <v>218.08</v>
+        <v>-235.98</v>
       </c>
       <c r="L67" t="n">
-        <v>231.67</v>
+        <v>295.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:32:57</t>
+          <t>08:37:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7.86</v>
+        <v>7.34</v>
       </c>
       <c r="F68" t="n">
-        <v>20.93</v>
+        <v>20.52</v>
       </c>
       <c r="G68" t="n">
-        <v>129.8</v>
+        <v>156.2</v>
       </c>
       <c r="H68" t="n">
-        <v>90.7</v>
+        <v>0.3</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>133.68</v>
+        <v>289.14</v>
       </c>
       <c r="K68" t="n">
-        <v>-319.34</v>
+        <v>-145.03</v>
       </c>
       <c r="L68" t="n">
-        <v>346.19</v>
+        <v>323.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:34:49</t>
+          <t>08:40:04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>7.5</v>
+        <v>8.82</v>
       </c>
       <c r="F69" t="n">
-        <v>19.48</v>
+        <v>20.93</v>
       </c>
       <c r="G69" t="n">
-        <v>149.2</v>
+        <v>160.3</v>
       </c>
       <c r="H69" t="n">
-        <v>91.40000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-25.34</v>
+        <v>-89.41</v>
       </c>
       <c r="K69" t="n">
-        <v>553.14</v>
+        <v>-230.88</v>
       </c>
       <c r="L69" t="n">
-        <v>553.72</v>
+        <v>247.59</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:37:22</t>
+          <t>08:41:16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.07</v>
+        <v>6.62</v>
       </c>
       <c r="F70" t="n">
-        <v>16.18</v>
+        <v>17.83</v>
       </c>
       <c r="G70" t="n">
-        <v>159</v>
+        <v>158.6</v>
       </c>
       <c r="H70" t="n">
-        <v>87</v>
+        <v>47.1</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>39.86</v>
+        <v>345.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-268.6</v>
+        <v>-227.15</v>
       </c>
       <c r="L70" t="n">
-        <v>271.54</v>
+        <v>413.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:42:28</t>
+          <t>08:44:34</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>7.34</v>
+        <v>7.05</v>
       </c>
       <c r="F71" t="n">
-        <v>19.51</v>
+        <v>19.72</v>
       </c>
       <c r="G71" t="n">
-        <v>157.8</v>
+        <v>168.9</v>
       </c>
       <c r="H71" t="n">
-        <v>91.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-353.38</v>
+        <v>247.53</v>
       </c>
       <c r="K71" t="n">
-        <v>-832.41</v>
+        <v>235.5</v>
       </c>
       <c r="L71" t="n">
-        <v>904.3099999999999</v>
+        <v>341.66</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:44:33</t>
+          <t>08:45:17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.92</v>
+        <v>7.11</v>
       </c>
       <c r="F72" t="n">
-        <v>20.93</v>
+        <v>18.8</v>
       </c>
       <c r="G72" t="n">
-        <v>166.1</v>
+        <v>148.6</v>
       </c>
       <c r="H72" t="n">
-        <v>84.40000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>268.81</v>
+        <v>416.84</v>
       </c>
       <c r="K72" t="n">
-        <v>474.05</v>
+        <v>-64.55</v>
       </c>
       <c r="L72" t="n">
-        <v>544.96</v>
+        <v>421.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:46:53</t>
+          <t>08:47:20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.85</v>
+        <v>7.12</v>
       </c>
       <c r="F73" t="n">
-        <v>18.64</v>
+        <v>18.73</v>
       </c>
       <c r="G73" t="n">
-        <v>164.7</v>
+        <v>144.8</v>
       </c>
       <c r="H73" t="n">
-        <v>91.3</v>
+        <v>49.6</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>192.29</v>
+        <v>426.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-558.33</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>590.51</v>
+        <v>433.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:57:52</t>
+          <t>08:57:20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="F74" t="n">
-        <v>20.93</v>
+        <v>19.39</v>
       </c>
       <c r="G74" t="n">
-        <v>130.6</v>
+        <v>143.1</v>
       </c>
       <c r="H74" t="n">
-        <v>90.90000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>99.08</v>
+        <v>155.1</v>
       </c>
       <c r="K74" t="n">
-        <v>-41.21</v>
+        <v>-10.15</v>
       </c>
       <c r="L74" t="n">
-        <v>107.31</v>
+        <v>155.43</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:59:31</t>
+          <t>08:58:23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>7.91</v>
+        <v>6.97</v>
       </c>
       <c r="F75" t="n">
-        <v>19.31</v>
+        <v>16.54</v>
       </c>
       <c r="G75" t="n">
-        <v>149</v>
+        <v>154.7</v>
       </c>
       <c r="H75" t="n">
-        <v>90.2</v>
+        <v>16</v>
       </c>
       <c r="I75" t="n">
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-87.43000000000001</v>
+        <v>-30.45</v>
       </c>
       <c r="K75" t="n">
-        <v>24.76</v>
+        <v>-114.3</v>
       </c>
       <c r="L75" t="n">
-        <v>90.87</v>
+        <v>118.29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:00:14</t>
+          <t>08:59:29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>7.54</v>
+        <v>7.1</v>
       </c>
       <c r="F76" t="n">
-        <v>18.3</v>
+        <v>17.15</v>
       </c>
       <c r="G76" t="n">
-        <v>167.6</v>
+        <v>147.6</v>
       </c>
       <c r="H76" t="n">
-        <v>90.09999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-88.75</v>
+        <v>158.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-166.86</v>
+        <v>-65.59</v>
       </c>
       <c r="L76" t="n">
-        <v>188.99</v>
+        <v>171.09</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:04:22</t>
+          <t>09:03:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.95</v>
+        <v>7.19</v>
       </c>
       <c r="F77" t="n">
-        <v>20.93</v>
+        <v>19.91</v>
       </c>
       <c r="G77" t="n">
-        <v>158.6</v>
+        <v>171.4</v>
       </c>
       <c r="H77" t="n">
-        <v>91.5</v>
+        <v>54.8</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-97.06</v>
+        <v>-10.33</v>
       </c>
       <c r="K77" t="n">
-        <v>-43.85</v>
+        <v>-190.17</v>
       </c>
       <c r="L77" t="n">
-        <v>106.51</v>
+        <v>190.45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:06:42</t>
+          <t>09:04:57</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>7.85</v>
+        <v>7.78</v>
       </c>
       <c r="F78" t="n">
-        <v>20.93</v>
+        <v>19</v>
       </c>
       <c r="G78" t="n">
-        <v>141.2</v>
+        <v>147.9</v>
       </c>
       <c r="H78" t="n">
-        <v>88.3</v>
+        <v>37.5</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-80.16</v>
+        <v>227.79</v>
       </c>
       <c r="K78" t="n">
-        <v>-120.05</v>
+        <v>17.27</v>
       </c>
       <c r="L78" t="n">
-        <v>144.35</v>
+        <v>228.44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:07:42</t>
+          <t>09:07:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>7.5</v>
+        <v>6.69</v>
       </c>
       <c r="F79" t="n">
-        <v>19.71</v>
+        <v>18.87</v>
       </c>
       <c r="G79" t="n">
-        <v>153.2</v>
+        <v>150.1</v>
       </c>
       <c r="H79" t="n">
-        <v>89.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>193.69</v>
+        <v>-224.79</v>
       </c>
       <c r="K79" t="n">
-        <v>-31</v>
+        <v>13.17</v>
       </c>
       <c r="L79" t="n">
-        <v>196.16</v>
+        <v>225.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:11:33</t>
+          <t>09:09:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>7.9</v>
+        <v>6.93</v>
       </c>
       <c r="F80" t="n">
-        <v>20.7</v>
+        <v>18.57</v>
       </c>
       <c r="G80" t="n">
-        <v>163.6</v>
+        <v>165.2</v>
       </c>
       <c r="H80" t="n">
-        <v>87.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>188.25</v>
+        <v>-212.14</v>
       </c>
       <c r="K80" t="n">
-        <v>-223.51</v>
+        <v>-125.83</v>
       </c>
       <c r="L80" t="n">
-        <v>292.22</v>
+        <v>246.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:12:06</t>
+          <t>09:11:17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>7.3</v>
+        <v>8.31</v>
       </c>
       <c r="F81" t="n">
         <v>20.93</v>
       </c>
       <c r="G81" t="n">
-        <v>136.2</v>
+        <v>142.4</v>
       </c>
       <c r="H81" t="n">
-        <v>84.8</v>
+        <v>44</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-79.95999999999999</v>
+        <v>-232.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-284.59</v>
+        <v>-229.14</v>
       </c>
       <c r="L81" t="n">
-        <v>295.61</v>
+        <v>326.22</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:13:13</t>
+          <t>09:13:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>7.14</v>
+        <v>8.15</v>
       </c>
       <c r="F82" t="n">
-        <v>17.8</v>
+        <v>20.93</v>
       </c>
       <c r="G82" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H82" t="n">
-        <v>94.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-129.45</v>
+        <v>62</v>
       </c>
       <c r="K82" t="n">
-        <v>-294.79</v>
+        <v>-266.07</v>
       </c>
       <c r="L82" t="n">
-        <v>321.96</v>
+        <v>273.2</v>
       </c>
     </row>
     <row r="83">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>7.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F83" t="n">
         <v>20.93</v>
       </c>
       <c r="G83" t="n">
-        <v>152</v>
+        <v>153.8</v>
       </c>
       <c r="H83" t="n">
-        <v>87.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.74</v>
+        <v>-114.47</v>
       </c>
       <c r="K83" t="n">
-        <v>470.24</v>
+        <v>-285.43</v>
       </c>
       <c r="L83" t="n">
-        <v>470.26</v>
+        <v>307.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:19:18</t>
+          <t>09:18:47</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.57</v>
+        <v>7.62</v>
       </c>
       <c r="F84" t="n">
-        <v>19.76</v>
+        <v>17.73</v>
       </c>
       <c r="G84" t="n">
-        <v>146.7</v>
+        <v>159.9</v>
       </c>
       <c r="H84" t="n">
-        <v>84.2</v>
+        <v>52.4</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.93</v>
+        <v>-133.42</v>
       </c>
       <c r="K84" t="n">
-        <v>-488.4</v>
+        <v>-324.65</v>
       </c>
       <c r="L84" t="n">
-        <v>488.4</v>
+        <v>350.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:21:42</t>
+          <t>09:19:50</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>7.96</v>
+        <v>8.1</v>
       </c>
       <c r="F85" t="n">
         <v>20.93</v>
       </c>
       <c r="G85" t="n">
-        <v>144.6</v>
+        <v>158.6</v>
       </c>
       <c r="H85" t="n">
-        <v>90.40000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>657.9</v>
+        <v>-113.09</v>
       </c>
       <c r="K85" t="n">
-        <v>-63.54</v>
+        <v>-273.72</v>
       </c>
       <c r="L85" t="n">
-        <v>660.97</v>
+        <v>296.16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:27:21</t>
+          <t>09:24:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.95</v>
+        <v>7.51</v>
       </c>
       <c r="F86" t="n">
-        <v>16.89</v>
+        <v>17.96</v>
       </c>
       <c r="G86" t="n">
-        <v>143.5</v>
+        <v>145.6</v>
       </c>
       <c r="H86" t="n">
-        <v>85.3</v>
+        <v>88.2</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>618.2</v>
+        <v>347.04</v>
       </c>
       <c r="K86" t="n">
-        <v>135.15</v>
+        <v>-208.64</v>
       </c>
       <c r="L86" t="n">
-        <v>632.8</v>
+        <v>404.93</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:29:24</t>
+          <t>09:25:48</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>7.95</v>
+        <v>7.63</v>
       </c>
       <c r="F87" t="n">
-        <v>20.89</v>
+        <v>20.93</v>
       </c>
       <c r="G87" t="n">
-        <v>149.6</v>
+        <v>149.3</v>
       </c>
       <c r="H87" t="n">
-        <v>87.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-218.82</v>
+        <v>55.45</v>
       </c>
       <c r="K87" t="n">
-        <v>-177.83</v>
+        <v>-445.01</v>
       </c>
       <c r="L87" t="n">
-        <v>281.97</v>
+        <v>448.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:30:35</t>
+          <t>09:27:08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>8.58</v>
+        <v>7.25</v>
       </c>
       <c r="F88" t="n">
-        <v>20.93</v>
+        <v>19.82</v>
       </c>
       <c r="G88" t="n">
-        <v>140.1</v>
+        <v>151</v>
       </c>
       <c r="H88" t="n">
-        <v>92.3</v>
+        <v>77.3</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-276.46</v>
+        <v>117.68</v>
       </c>
       <c r="K88" t="n">
-        <v>-556.6</v>
+        <v>-414.54</v>
       </c>
       <c r="L88" t="n">
-        <v>621.48</v>
+        <v>430.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>7.18</v>
+        <v>5.81</v>
       </c>
       <c r="F14" t="n">
-        <v>15.3</v>
+        <v>14.82</v>
       </c>
       <c r="G14" t="n">
-        <v>144.4</v>
+        <v>155</v>
       </c>
       <c r="H14" t="n">
-        <v>54.7</v>
+        <v>67.8</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>28.76</v>
+        <v>144.84</v>
       </c>
       <c r="K14" t="n">
-        <v>-116.57</v>
+        <v>-159.93</v>
       </c>
       <c r="L14" t="n">
-        <v>120.06</v>
+        <v>215.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:59:18</t>
+          <t>06:00:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6.46</v>
+        <v>6.77</v>
       </c>
       <c r="F15" t="n">
-        <v>16.2</v>
+        <v>16.78</v>
       </c>
       <c r="G15" t="n">
-        <v>161.2</v>
+        <v>153.4</v>
       </c>
       <c r="H15" t="n">
-        <v>71.7</v>
+        <v>63.8</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-35.41</v>
+        <v>87.12</v>
       </c>
       <c r="K15" t="n">
-        <v>-141.11</v>
+        <v>-127.4</v>
       </c>
       <c r="L15" t="n">
-        <v>145.49</v>
+        <v>154.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:01:35</t>
+          <t>06:02:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.45</v>
+        <v>6.61</v>
       </c>
       <c r="F16" t="n">
-        <v>13.07</v>
+        <v>15.05</v>
       </c>
       <c r="G16" t="n">
-        <v>143.1</v>
+        <v>159.7</v>
       </c>
       <c r="H16" t="n">
-        <v>60.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-70.09999999999999</v>
+        <v>16.84</v>
       </c>
       <c r="K16" t="n">
-        <v>-168.07</v>
+        <v>60.13</v>
       </c>
       <c r="L16" t="n">
-        <v>182.1</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:06:40</t>
+          <t>06:08:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="F17" t="n">
-        <v>14.54</v>
+        <v>12.01</v>
       </c>
       <c r="G17" t="n">
-        <v>159.3</v>
+        <v>152.9</v>
       </c>
       <c r="H17" t="n">
-        <v>35.8</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-28.03</v>
+        <v>-14.95</v>
       </c>
       <c r="K17" t="n">
-        <v>-164.51</v>
+        <v>-168.14</v>
       </c>
       <c r="L17" t="n">
-        <v>166.88</v>
+        <v>168.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:07:38</t>
+          <t>06:09:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>6.42</v>
+        <v>6.38</v>
       </c>
       <c r="F18" t="n">
-        <v>19.08</v>
+        <v>16.62</v>
       </c>
       <c r="G18" t="n">
-        <v>154.3</v>
+        <v>151.3</v>
       </c>
       <c r="H18" t="n">
-        <v>29.9</v>
+        <v>66.2</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>35.62</v>
+        <v>200.11</v>
       </c>
       <c r="K18" t="n">
-        <v>-171.19</v>
+        <v>121.9</v>
       </c>
       <c r="L18" t="n">
-        <v>174.86</v>
+        <v>234.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:09:22</t>
+          <t>06:11:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>7.23</v>
+        <v>6.2</v>
       </c>
       <c r="F19" t="n">
-        <v>15.45</v>
+        <v>16.58</v>
       </c>
       <c r="G19" t="n">
-        <v>161.1</v>
+        <v>146.5</v>
       </c>
       <c r="H19" t="n">
-        <v>59</v>
+        <v>46.7</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>197.25</v>
+        <v>-117.5</v>
       </c>
       <c r="K19" t="n">
-        <v>45.69</v>
+        <v>214.91</v>
       </c>
       <c r="L19" t="n">
-        <v>202.47</v>
+        <v>244.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:14:43</t>
+          <t>06:16:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.91</v>
+        <v>6.27</v>
       </c>
       <c r="F20" t="n">
-        <v>12.77</v>
+        <v>13.06</v>
       </c>
       <c r="G20" t="n">
-        <v>156.4</v>
+        <v>145.2</v>
       </c>
       <c r="H20" t="n">
-        <v>45.5</v>
+        <v>27.6</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>186.15</v>
+        <v>44.57</v>
       </c>
       <c r="K20" t="n">
-        <v>191.58</v>
+        <v>-269.85</v>
       </c>
       <c r="L20" t="n">
-        <v>267.13</v>
+        <v>273.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:15:46</t>
+          <t>06:17:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.8</v>
+        <v>5.41</v>
       </c>
       <c r="F21" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="G21" t="n">
-        <v>163.6</v>
+        <v>151.8</v>
       </c>
       <c r="H21" t="n">
-        <v>76.2</v>
+        <v>33.6</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.6</v>
+        <v>78.8</v>
       </c>
       <c r="K21" t="n">
-        <v>-253.79</v>
+        <v>-147.81</v>
       </c>
       <c r="L21" t="n">
-        <v>253.94</v>
+        <v>167.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:16:56</t>
+          <t>06:18:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6.71</v>
+        <v>6.89</v>
       </c>
       <c r="F22" t="n">
-        <v>16.76</v>
+        <v>15.97</v>
       </c>
       <c r="G22" t="n">
-        <v>144.7</v>
+        <v>162.7</v>
       </c>
       <c r="H22" t="n">
-        <v>38.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-78.98</v>
+        <v>241.11</v>
       </c>
       <c r="K22" t="n">
-        <v>-34.89</v>
+        <v>-175.92</v>
       </c>
       <c r="L22" t="n">
-        <v>86.34</v>
+        <v>298.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:20:56</t>
+          <t>06:23:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>6.15</v>
+        <v>5.78</v>
       </c>
       <c r="F23" t="n">
-        <v>17.22</v>
+        <v>14.08</v>
       </c>
       <c r="G23" t="n">
-        <v>167.1</v>
+        <v>146.3</v>
       </c>
       <c r="H23" t="n">
-        <v>75.90000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>317.55</v>
+        <v>161.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.99</v>
+        <v>-431.51</v>
       </c>
       <c r="L23" t="n">
-        <v>317.56</v>
+        <v>460.88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:23:19</t>
+          <t>06:24:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.16</v>
+        <v>7.08</v>
       </c>
       <c r="F24" t="n">
-        <v>15.62</v>
+        <v>16.3</v>
       </c>
       <c r="G24" t="n">
-        <v>156.5</v>
+        <v>151.2</v>
       </c>
       <c r="H24" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>97.02</v>
+        <v>59.41</v>
       </c>
       <c r="K24" t="n">
-        <v>-315.21</v>
+        <v>-498.17</v>
       </c>
       <c r="L24" t="n">
-        <v>329.8</v>
+        <v>501.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:24:59</t>
+          <t>06:25:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>6.53</v>
+        <v>6.92</v>
       </c>
       <c r="F25" t="n">
-        <v>15.2</v>
+        <v>18.77</v>
       </c>
       <c r="G25" t="n">
-        <v>155.2</v>
+        <v>151.5</v>
       </c>
       <c r="H25" t="n">
-        <v>63.4</v>
+        <v>28</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>144.78</v>
+        <v>-344.71</v>
       </c>
       <c r="K25" t="n">
-        <v>-232.4</v>
+        <v>-51.9</v>
       </c>
       <c r="L25" t="n">
-        <v>273.81</v>
+        <v>348.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:31:04</t>
+          <t>06:31:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6.58</v>
+        <v>6.12</v>
       </c>
       <c r="F26" t="n">
-        <v>17.46</v>
+        <v>12.19</v>
       </c>
       <c r="G26" t="n">
-        <v>157.2</v>
+        <v>156.8</v>
       </c>
       <c r="H26" t="n">
-        <v>40.3</v>
+        <v>85.5</v>
       </c>
       <c r="I26" t="n">
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>292.54</v>
+        <v>-392.06</v>
       </c>
       <c r="K26" t="n">
-        <v>-425.3</v>
+        <v>-230.37</v>
       </c>
       <c r="L26" t="n">
-        <v>516.1900000000001</v>
+        <v>454.73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:33:07</t>
+          <t>06:33:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>6.68</v>
+        <v>6.84</v>
       </c>
       <c r="F27" t="n">
-        <v>16.41</v>
+        <v>19.16</v>
       </c>
       <c r="G27" t="n">
-        <v>151.5</v>
+        <v>149.4</v>
       </c>
       <c r="H27" t="n">
-        <v>72.2</v>
+        <v>78.5</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>374.82</v>
+        <v>268.03</v>
       </c>
       <c r="K27" t="n">
-        <v>53.27</v>
+        <v>-347.08</v>
       </c>
       <c r="L27" t="n">
-        <v>378.59</v>
+        <v>438.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:35:20</t>
+          <t>06:34:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.86</v>
+        <v>6.93</v>
       </c>
       <c r="F28" t="n">
-        <v>15.04</v>
+        <v>15.57</v>
       </c>
       <c r="G28" t="n">
-        <v>142.2</v>
+        <v>147.5</v>
       </c>
       <c r="H28" t="n">
-        <v>72.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>4.73</v>
+        <v>90.73</v>
       </c>
       <c r="K28" t="n">
-        <v>-550.76</v>
+        <v>515.14</v>
       </c>
       <c r="L28" t="n">
-        <v>550.78</v>
+        <v>523.0700000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:46:47</t>
+          <t>06:44:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>7.42</v>
+        <v>6.06</v>
       </c>
       <c r="F29" t="n">
-        <v>17.49</v>
+        <v>14.67</v>
       </c>
       <c r="G29" t="n">
-        <v>153.8</v>
+        <v>147.4</v>
       </c>
       <c r="H29" t="n">
-        <v>63.3</v>
+        <v>55.9</v>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>104.57</v>
+        <v>134.08</v>
       </c>
       <c r="K29" t="n">
-        <v>64.75</v>
+        <v>-41.48</v>
       </c>
       <c r="L29" t="n">
-        <v>122.99</v>
+        <v>140.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:47:29</t>
+          <t>06:46:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.91</v>
+        <v>6.36</v>
       </c>
       <c r="F30" t="n">
-        <v>16.01</v>
+        <v>14.13</v>
       </c>
       <c r="G30" t="n">
-        <v>162.5</v>
+        <v>152.4</v>
       </c>
       <c r="H30" t="n">
-        <v>70.2</v>
+        <v>45.2</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-59.7</v>
+        <v>-127.68</v>
       </c>
       <c r="K30" t="n">
-        <v>-146.88</v>
+        <v>-21.49</v>
       </c>
       <c r="L30" t="n">
-        <v>158.55</v>
+        <v>129.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:50:12</t>
+          <t>06:48:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>7.04</v>
+        <v>6.91</v>
       </c>
       <c r="F31" t="n">
-        <v>17.44</v>
+        <v>17.24</v>
       </c>
       <c r="G31" t="n">
-        <v>145</v>
+        <v>139.5</v>
       </c>
       <c r="H31" t="n">
-        <v>50.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-91.88</v>
+        <v>-138.63</v>
       </c>
       <c r="K31" t="n">
-        <v>137.48</v>
+        <v>47.78</v>
       </c>
       <c r="L31" t="n">
-        <v>165.36</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:55:25</t>
+          <t>06:51:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.8</v>
+        <v>6.11</v>
       </c>
       <c r="F32" t="n">
-        <v>18.25</v>
+        <v>16.26</v>
       </c>
       <c r="G32" t="n">
-        <v>143.9</v>
+        <v>158.6</v>
       </c>
       <c r="H32" t="n">
-        <v>56.3</v>
+        <v>43.9</v>
       </c>
       <c r="I32" t="n">
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-6.18</v>
+        <v>86.55</v>
       </c>
       <c r="K32" t="n">
-        <v>234.08</v>
+        <v>-200.4</v>
       </c>
       <c r="L32" t="n">
-        <v>234.16</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:57:24</t>
+          <t>06:53:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.62</v>
+        <v>6.28</v>
       </c>
       <c r="F33" t="n">
-        <v>17.05</v>
+        <v>15.64</v>
       </c>
       <c r="G33" t="n">
-        <v>162.5</v>
+        <v>142.6</v>
       </c>
       <c r="H33" t="n">
-        <v>93.8</v>
+        <v>67.2</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-194.58</v>
+        <v>-146.44</v>
       </c>
       <c r="K33" t="n">
-        <v>-56.66</v>
+        <v>-167.41</v>
       </c>
       <c r="L33" t="n">
-        <v>202.66</v>
+        <v>222.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:58:49</t>
+          <t>06:54:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>6.87</v>
+        <v>7.06</v>
       </c>
       <c r="F34" t="n">
-        <v>18.68</v>
+        <v>17.58</v>
       </c>
       <c r="G34" t="n">
-        <v>146.3</v>
+        <v>165.5</v>
       </c>
       <c r="H34" t="n">
-        <v>46.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.7</v>
+        <v>164.13</v>
       </c>
       <c r="K34" t="n">
-        <v>-193.18</v>
+        <v>-60.16</v>
       </c>
       <c r="L34" t="n">
-        <v>193.33</v>
+        <v>174.81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:02:43</t>
+          <t>06:58:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>7.04</v>
+        <v>6.37</v>
       </c>
       <c r="F35" t="n">
-        <v>18.02</v>
+        <v>16.25</v>
       </c>
       <c r="G35" t="n">
-        <v>147.9</v>
+        <v>147.2</v>
       </c>
       <c r="H35" t="n">
-        <v>26.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.78</v>
+        <v>81.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-87.04000000000001</v>
+        <v>-263.28</v>
       </c>
       <c r="L35" t="n">
-        <v>87.7</v>
+        <v>275.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:04:29</t>
+          <t>07:01:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>7.66</v>
+        <v>6.3</v>
       </c>
       <c r="F36" t="n">
-        <v>20.76</v>
+        <v>17.92</v>
       </c>
       <c r="G36" t="n">
-        <v>133</v>
+        <v>150.8</v>
       </c>
       <c r="H36" t="n">
-        <v>59.9</v>
+        <v>35.8</v>
       </c>
       <c r="I36" t="n">
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-165.81</v>
+        <v>-226.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-214</v>
+        <v>84.13</v>
       </c>
       <c r="L36" t="n">
-        <v>270.72</v>
+        <v>241.97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:06:30</t>
+          <t>07:02:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>7.19</v>
+        <v>6.71</v>
       </c>
       <c r="F37" t="n">
-        <v>19.9</v>
+        <v>16.15</v>
       </c>
       <c r="G37" t="n">
-        <v>145</v>
+        <v>154.9</v>
       </c>
       <c r="H37" t="n">
-        <v>29.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-266.36</v>
+        <v>131.75</v>
       </c>
       <c r="K37" t="n">
-        <v>-54.38</v>
+        <v>-171.4</v>
       </c>
       <c r="L37" t="n">
-        <v>271.86</v>
+        <v>216.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:11:24</t>
+          <t>07:08:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.5</v>
+        <v>7.26</v>
       </c>
       <c r="F38" t="n">
-        <v>13.44</v>
+        <v>16.8</v>
       </c>
       <c r="G38" t="n">
-        <v>151.9</v>
+        <v>153.2</v>
       </c>
       <c r="H38" t="n">
-        <v>53.4</v>
+        <v>61.3</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-66.81</v>
+        <v>-50.35</v>
       </c>
       <c r="K38" t="n">
-        <v>-366.52</v>
+        <v>-380</v>
       </c>
       <c r="L38" t="n">
-        <v>372.56</v>
+        <v>383.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:13:17</t>
+          <t>07:09:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.78</v>
+        <v>6.98</v>
       </c>
       <c r="F39" t="n">
-        <v>16.9</v>
+        <v>20.27</v>
       </c>
       <c r="G39" t="n">
-        <v>147.4</v>
+        <v>154.8</v>
       </c>
       <c r="H39" t="n">
-        <v>70.5</v>
+        <v>72.7</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>151.27</v>
+        <v>-341.48</v>
       </c>
       <c r="K39" t="n">
-        <v>-307.85</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>343.01</v>
+        <v>347.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:14:49</t>
+          <t>07:11:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>7.07</v>
+        <v>7.36</v>
       </c>
       <c r="F40" t="n">
-        <v>19.26</v>
+        <v>17.58</v>
       </c>
       <c r="G40" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="H40" t="n">
-        <v>49.4</v>
+        <v>89</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>298.13</v>
+        <v>-353.16</v>
       </c>
       <c r="K40" t="n">
-        <v>68.16</v>
+        <v>30.24</v>
       </c>
       <c r="L40" t="n">
-        <v>305.83</v>
+        <v>354.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:18:00</t>
+          <t>07:15:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>7.22</v>
+        <v>6.96</v>
       </c>
       <c r="F41" t="n">
-        <v>20.93</v>
+        <v>15.06</v>
       </c>
       <c r="G41" t="n">
-        <v>163.3</v>
+        <v>155</v>
       </c>
       <c r="H41" t="n">
-        <v>54.6</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-309.25</v>
+        <v>-170.47</v>
       </c>
       <c r="K41" t="n">
-        <v>-366.21</v>
+        <v>-301.56</v>
       </c>
       <c r="L41" t="n">
-        <v>479.32</v>
+        <v>346.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:20:27</t>
+          <t>07:17:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6.72</v>
+        <v>7.75</v>
       </c>
       <c r="F42" t="n">
-        <v>18.05</v>
+        <v>20.93</v>
       </c>
       <c r="G42" t="n">
-        <v>143.8</v>
+        <v>133</v>
       </c>
       <c r="H42" t="n">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>141.31</v>
+        <v>-424.8</v>
       </c>
       <c r="K42" t="n">
-        <v>-471.2</v>
+        <v>-256.47</v>
       </c>
       <c r="L42" t="n">
-        <v>491.93</v>
+        <v>496.22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:22:08</t>
+          <t>07:18:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>8.4</v>
+        <v>7.28</v>
       </c>
       <c r="F43" t="n">
-        <v>20.93</v>
+        <v>20.28</v>
       </c>
       <c r="G43" t="n">
-        <v>160.1</v>
+        <v>145</v>
       </c>
       <c r="H43" t="n">
-        <v>50.8</v>
+        <v>29.7</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>335.38</v>
+        <v>-490.45</v>
       </c>
       <c r="K43" t="n">
-        <v>-393.91</v>
+        <v>51.54</v>
       </c>
       <c r="L43" t="n">
-        <v>517.34</v>
+        <v>493.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:31:32</t>
+          <t>07:30:49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>7.08</v>
+        <v>6.64</v>
       </c>
       <c r="F44" t="n">
-        <v>17.33</v>
+        <v>14.01</v>
       </c>
       <c r="G44" t="n">
-        <v>141.1</v>
+        <v>151.9</v>
       </c>
       <c r="H44" t="n">
-        <v>83</v>
+        <v>53.4</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>160.47</v>
+        <v>-68.36</v>
       </c>
       <c r="K44" t="n">
-        <v>61.94</v>
+        <v>-150.16</v>
       </c>
       <c r="L44" t="n">
-        <v>172.01</v>
+        <v>164.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:33:05</t>
+          <t>07:31:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>7.24</v>
+        <v>6.91</v>
       </c>
       <c r="F45" t="n">
-        <v>15.83</v>
+        <v>17.45</v>
       </c>
       <c r="G45" t="n">
-        <v>160.9</v>
+        <v>147.4</v>
       </c>
       <c r="H45" t="n">
-        <v>75.3</v>
+        <v>70.5</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>142.36</v>
+        <v>60.93</v>
       </c>
       <c r="K45" t="n">
-        <v>-58.25</v>
+        <v>-140.56</v>
       </c>
       <c r="L45" t="n">
-        <v>153.82</v>
+        <v>153.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:33:59</t>
+          <t>07:33:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1972,31 +1972,31 @@
         <v>7.2</v>
       </c>
       <c r="F46" t="n">
-        <v>20.24</v>
+        <v>19.81</v>
       </c>
       <c r="G46" t="n">
-        <v>144.8</v>
+        <v>167</v>
       </c>
       <c r="H46" t="n">
-        <v>83</v>
+        <v>49.4</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-128.91</v>
+        <v>113.05</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.04</v>
+        <v>73.7</v>
       </c>
       <c r="L46" t="n">
-        <v>138.64</v>
+        <v>134.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:37:39</t>
+          <t>07:37:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>7.33</v>
+        <v>7.35</v>
       </c>
       <c r="F47" t="n">
         <v>20.93</v>
       </c>
       <c r="G47" t="n">
-        <v>147.9</v>
+        <v>163.3</v>
       </c>
       <c r="H47" t="n">
-        <v>62.7</v>
+        <v>54.6</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>190.96</v>
+        <v>-190.09</v>
       </c>
       <c r="K47" t="n">
-        <v>36.92</v>
+        <v>-113.69</v>
       </c>
       <c r="L47" t="n">
-        <v>194.5</v>
+        <v>221.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:39:42</t>
+          <t>07:39:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>7.66</v>
+        <v>6.85</v>
       </c>
       <c r="F48" t="n">
-        <v>20.25</v>
+        <v>18.6</v>
       </c>
       <c r="G48" t="n">
-        <v>153.2</v>
+        <v>143.8</v>
       </c>
       <c r="H48" t="n">
-        <v>62.4</v>
+        <v>60.4</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>71.06</v>
+        <v>34.15</v>
       </c>
       <c r="K48" t="n">
-        <v>167.87</v>
+        <v>-223.57</v>
       </c>
       <c r="L48" t="n">
-        <v>182.29</v>
+        <v>226.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:40:51</t>
+          <t>07:41:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.99</v>
+        <v>8.52</v>
       </c>
       <c r="F49" t="n">
-        <v>18.88</v>
+        <v>20.93</v>
       </c>
       <c r="G49" t="n">
-        <v>162.8</v>
+        <v>160.1</v>
       </c>
       <c r="H49" t="n">
-        <v>45.5</v>
+        <v>50.8</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-43.91</v>
+        <v>180.27</v>
       </c>
       <c r="K49" t="n">
-        <v>172.09</v>
+        <v>-153.53</v>
       </c>
       <c r="L49" t="n">
-        <v>177.6</v>
+        <v>236.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:45:45</t>
+          <t>07:47:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>8.380000000000001</v>
+        <v>7.18</v>
       </c>
       <c r="F50" t="n">
-        <v>20.5</v>
+        <v>17.77</v>
       </c>
       <c r="G50" t="n">
-        <v>148</v>
+        <v>141.1</v>
       </c>
       <c r="H50" t="n">
-        <v>68.2</v>
+        <v>83</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>191.74</v>
+        <v>242.53</v>
       </c>
       <c r="K50" t="n">
-        <v>-200.83</v>
+        <v>214.99</v>
       </c>
       <c r="L50" t="n">
-        <v>277.66</v>
+        <v>324.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:47:54</t>
+          <t>07:49:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.98</v>
+        <v>7.34</v>
       </c>
       <c r="F51" t="n">
-        <v>16.53</v>
+        <v>16.28</v>
       </c>
       <c r="G51" t="n">
-        <v>156.4</v>
+        <v>160.9</v>
       </c>
       <c r="H51" t="n">
-        <v>69.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="I51" t="n">
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-67.95</v>
+        <v>285.07</v>
       </c>
       <c r="K51" t="n">
-        <v>-212.45</v>
+        <v>-23.8</v>
       </c>
       <c r="L51" t="n">
-        <v>223.05</v>
+        <v>286.06</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:49:15</t>
+          <t>07:51:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>7.28</v>
+        <v>7.32</v>
       </c>
       <c r="F52" t="n">
-        <v>16.83</v>
+        <v>20.75</v>
       </c>
       <c r="G52" t="n">
-        <v>150.2</v>
+        <v>144.8</v>
       </c>
       <c r="H52" t="n">
-        <v>62.9</v>
+        <v>83</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>210.28</v>
+        <v>-257.88</v>
       </c>
       <c r="K52" t="n">
-        <v>-172.88</v>
+        <v>-11.62</v>
       </c>
       <c r="L52" t="n">
-        <v>272.22</v>
+        <v>258.14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:53:02</t>
+          <t>07:55:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6.46</v>
+        <v>7.45</v>
       </c>
       <c r="F53" t="n">
-        <v>17.12</v>
+        <v>20.93</v>
       </c>
       <c r="G53" t="n">
-        <v>136</v>
+        <v>147.9</v>
       </c>
       <c r="H53" t="n">
-        <v>56.5</v>
+        <v>62.7</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>64.95</v>
+        <v>323.63</v>
       </c>
       <c r="K53" t="n">
-        <v>-324.74</v>
+        <v>197.42</v>
       </c>
       <c r="L53" t="n">
-        <v>331.17</v>
+        <v>379.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:53:49</t>
+          <t>07:57:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>7.1</v>
+        <v>7.78</v>
       </c>
       <c r="F54" t="n">
-        <v>20.71</v>
+        <v>20.78</v>
       </c>
       <c r="G54" t="n">
-        <v>159.5</v>
+        <v>153.2</v>
       </c>
       <c r="H54" t="n">
-        <v>74.7</v>
+        <v>62.4</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>91.86</v>
+        <v>54.76</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.72</v>
+        <v>358.59</v>
       </c>
       <c r="L54" t="n">
-        <v>91.93000000000001</v>
+        <v>362.74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:55:22</t>
+          <t>07:58:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>7.74</v>
+        <v>7.11</v>
       </c>
       <c r="F55" t="n">
-        <v>17.9</v>
+        <v>19.39</v>
       </c>
       <c r="G55" t="n">
-        <v>158</v>
+        <v>162.8</v>
       </c>
       <c r="H55" t="n">
-        <v>54.5</v>
+        <v>45.5</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-140.34</v>
+        <v>-91.26000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-373.05</v>
+        <v>336.23</v>
       </c>
       <c r="L55" t="n">
-        <v>398.58</v>
+        <v>348.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:59:44</t>
+          <t>08:04:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>7.43</v>
+        <v>8.5</v>
       </c>
       <c r="F56" t="n">
-        <v>16.85</v>
+        <v>20.93</v>
       </c>
       <c r="G56" t="n">
-        <v>162.4</v>
+        <v>148</v>
       </c>
       <c r="H56" t="n">
-        <v>54.3</v>
+        <v>68.2</v>
       </c>
       <c r="I56" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-404.28</v>
+        <v>420.6</v>
       </c>
       <c r="K56" t="n">
-        <v>-172.12</v>
+        <v>-365.33</v>
       </c>
       <c r="L56" t="n">
-        <v>439.4</v>
+        <v>557.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:01:39</t>
+          <t>08:07:09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.41</v>
+        <v>7.11</v>
       </c>
       <c r="F57" t="n">
-        <v>15.98</v>
+        <v>17.08</v>
       </c>
       <c r="G57" t="n">
-        <v>161.1</v>
+        <v>156.4</v>
       </c>
       <c r="H57" t="n">
-        <v>85.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>190.58</v>
+        <v>-245.46</v>
       </c>
       <c r="K57" t="n">
-        <v>379.59</v>
+        <v>-375.92</v>
       </c>
       <c r="L57" t="n">
-        <v>424.74</v>
+        <v>448.96</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:03:50</t>
+          <t>08:08:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="F58" t="n">
-        <v>20.93</v>
+        <v>17.36</v>
       </c>
       <c r="G58" t="n">
-        <v>167.8</v>
+        <v>150.2</v>
       </c>
       <c r="H58" t="n">
-        <v>94.09999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>246.55</v>
+        <v>473.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-332.71</v>
+        <v>-280.54</v>
       </c>
       <c r="L58" t="n">
-        <v>414.11</v>
+        <v>550.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:13:39</t>
+          <t>08:19:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>8.369999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="F59" t="n">
-        <v>20.93</v>
+        <v>17.8</v>
       </c>
       <c r="G59" t="n">
-        <v>149.9</v>
+        <v>136</v>
       </c>
       <c r="H59" t="n">
-        <v>94.40000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>74.78</v>
+        <v>-3.15</v>
       </c>
       <c r="K59" t="n">
-        <v>139.18</v>
+        <v>-168.58</v>
       </c>
       <c r="L59" t="n">
-        <v>158</v>
+        <v>168.61</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:15:14</t>
+          <t>08:20:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>7.58</v>
+        <v>7.27</v>
       </c>
       <c r="F60" t="n">
-        <v>20.79</v>
+        <v>20.93</v>
       </c>
       <c r="G60" t="n">
-        <v>152.3</v>
+        <v>159.5</v>
       </c>
       <c r="H60" t="n">
-        <v>66.3</v>
+        <v>74.7</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-21.11</v>
+        <v>16.51</v>
       </c>
       <c r="K60" t="n">
-        <v>-134.73</v>
+        <v>81.2</v>
       </c>
       <c r="L60" t="n">
-        <v>136.37</v>
+        <v>82.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:16:16</t>
+          <t>08:22:53</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.55</v>
+        <v>7.92</v>
       </c>
       <c r="F61" t="n">
-        <v>15.79</v>
+        <v>18.7</v>
       </c>
       <c r="G61" t="n">
-        <v>156.5</v>
+        <v>158</v>
       </c>
       <c r="H61" t="n">
-        <v>77.90000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="I61" t="n">
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>125.32</v>
+        <v>54.45</v>
       </c>
       <c r="K61" t="n">
-        <v>-25.35</v>
+        <v>194.16</v>
       </c>
       <c r="L61" t="n">
-        <v>127.85</v>
+        <v>201.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:21:00</t>
+          <t>08:27:47</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="F62" t="n">
-        <v>18.63</v>
+        <v>17.61</v>
       </c>
       <c r="G62" t="n">
-        <v>156.7</v>
+        <v>162.4</v>
       </c>
       <c r="H62" t="n">
-        <v>64.90000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>200.68</v>
+        <v>-230.34</v>
       </c>
       <c r="K62" t="n">
-        <v>-58.88</v>
+        <v>-9.44</v>
       </c>
       <c r="L62" t="n">
-        <v>209.14</v>
+        <v>230.53</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:22:22</t>
+          <t>08:29:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>7.78</v>
+        <v>6.59</v>
       </c>
       <c r="F63" t="n">
-        <v>20.93</v>
+        <v>16.73</v>
       </c>
       <c r="G63" t="n">
-        <v>157.4</v>
+        <v>161.1</v>
       </c>
       <c r="H63" t="n">
-        <v>14.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>134.58</v>
+        <v>-173.04</v>
       </c>
       <c r="K63" t="n">
-        <v>-199.09</v>
+        <v>144.16</v>
       </c>
       <c r="L63" t="n">
-        <v>240.31</v>
+        <v>225.23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:24:32</t>
+          <t>08:31:11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>7.38</v>
+        <v>7.55</v>
       </c>
       <c r="F64" t="n">
-        <v>20.76</v>
+        <v>20.93</v>
       </c>
       <c r="G64" t="n">
-        <v>161.7</v>
+        <v>158.4</v>
       </c>
       <c r="H64" t="n">
-        <v>31.1</v>
+        <v>55.3</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>30.81</v>
+        <v>7.95</v>
       </c>
       <c r="K64" t="n">
-        <v>-233.7</v>
+        <v>215.99</v>
       </c>
       <c r="L64" t="n">
-        <v>235.73</v>
+        <v>216.13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:29:33</t>
+          <t>08:34:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.87</v>
+        <v>7.61</v>
       </c>
       <c r="F65" t="n">
-        <v>18.44</v>
+        <v>20.35</v>
       </c>
       <c r="G65" t="n">
-        <v>153.2</v>
+        <v>152.9</v>
       </c>
       <c r="H65" t="n">
-        <v>68.8</v>
+        <v>56.8</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>128.34</v>
+        <v>-136.37</v>
       </c>
       <c r="K65" t="n">
-        <v>-253.69</v>
+        <v>-248.01</v>
       </c>
       <c r="L65" t="n">
-        <v>284.3</v>
+        <v>283.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:30:50</t>
+          <t>08:36:49</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>7.01</v>
+        <v>8.65</v>
       </c>
       <c r="F66" t="n">
-        <v>17.47</v>
+        <v>20.93</v>
       </c>
       <c r="G66" t="n">
-        <v>150.1</v>
+        <v>154.3</v>
       </c>
       <c r="H66" t="n">
-        <v>90</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>251.3</v>
+        <v>206.49</v>
       </c>
       <c r="K66" t="n">
-        <v>58.61</v>
+        <v>-218.26</v>
       </c>
       <c r="L66" t="n">
-        <v>258.04</v>
+        <v>300.46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:32:08</t>
+          <t>08:38:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>7.06</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>20.21</v>
+        <v>20.93</v>
       </c>
       <c r="G67" t="n">
-        <v>144.1</v>
+        <v>159</v>
       </c>
       <c r="H67" t="n">
-        <v>53.7</v>
+        <v>58</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-177.55</v>
+        <v>166.23</v>
       </c>
       <c r="K67" t="n">
-        <v>-235.98</v>
+        <v>-276.12</v>
       </c>
       <c r="L67" t="n">
-        <v>295.32</v>
+        <v>322.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:37:30</t>
+          <t>08:42:42</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7.34</v>
+        <v>7.26</v>
       </c>
       <c r="F68" t="n">
-        <v>20.52</v>
+        <v>16.96</v>
       </c>
       <c r="G68" t="n">
-        <v>156.2</v>
+        <v>142.8</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3</v>
+        <v>36.8</v>
       </c>
       <c r="I68" t="n">
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>289.14</v>
+        <v>278.89</v>
       </c>
       <c r="K68" t="n">
-        <v>-145.03</v>
+        <v>-694.87</v>
       </c>
       <c r="L68" t="n">
-        <v>323.47</v>
+        <v>748.74</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:40:04</t>
+          <t>08:44:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>8.82</v>
+        <v>6.55</v>
       </c>
       <c r="F69" t="n">
-        <v>20.93</v>
+        <v>13.22</v>
       </c>
       <c r="G69" t="n">
-        <v>160.3</v>
+        <v>158.5</v>
       </c>
       <c r="H69" t="n">
-        <v>29.8</v>
+        <v>23.6</v>
       </c>
       <c r="I69" t="n">
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-89.41</v>
+        <v>554.29</v>
       </c>
       <c r="K69" t="n">
-        <v>-230.88</v>
+        <v>201.76</v>
       </c>
       <c r="L69" t="n">
-        <v>247.59</v>
+        <v>589.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:41:16</t>
+          <t>08:45:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.62</v>
+        <v>7.06</v>
       </c>
       <c r="F70" t="n">
-        <v>17.83</v>
+        <v>18.59</v>
       </c>
       <c r="G70" t="n">
-        <v>158.6</v>
+        <v>144.5</v>
       </c>
       <c r="H70" t="n">
-        <v>47.1</v>
+        <v>62.6</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>345.81</v>
+        <v>-171.29</v>
       </c>
       <c r="K70" t="n">
-        <v>-227.15</v>
+        <v>-440.2</v>
       </c>
       <c r="L70" t="n">
-        <v>413.74</v>
+        <v>472.35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:44:34</t>
+          <t>08:50:23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>7.05</v>
+        <v>7.41</v>
       </c>
       <c r="F71" t="n">
-        <v>19.72</v>
+        <v>20.93</v>
       </c>
       <c r="G71" t="n">
-        <v>168.9</v>
+        <v>152.8</v>
       </c>
       <c r="H71" t="n">
-        <v>75.2</v>
+        <v>58.3</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>247.53</v>
+        <v>-197.56</v>
       </c>
       <c r="K71" t="n">
-        <v>235.5</v>
+        <v>-479.86</v>
       </c>
       <c r="L71" t="n">
-        <v>341.66</v>
+        <v>518.9400000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:45:17</t>
+          <t>08:51:33</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.11</v>
+        <v>7.46</v>
       </c>
       <c r="F72" t="n">
-        <v>18.8</v>
+        <v>19.17</v>
       </c>
       <c r="G72" t="n">
-        <v>148.6</v>
+        <v>140.6</v>
       </c>
       <c r="H72" t="n">
-        <v>45.4</v>
+        <v>48.9</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>416.84</v>
+        <v>460.52</v>
       </c>
       <c r="K72" t="n">
-        <v>-64.55</v>
+        <v>189.59</v>
       </c>
       <c r="L72" t="n">
-        <v>421.8</v>
+        <v>498.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:47:20</t>
+          <t>08:53:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7.12</v>
+        <v>7.37</v>
       </c>
       <c r="F73" t="n">
-        <v>18.73</v>
+        <v>20.1</v>
       </c>
       <c r="G73" t="n">
-        <v>144.8</v>
+        <v>159.2</v>
       </c>
       <c r="H73" t="n">
-        <v>49.6</v>
+        <v>17.5</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>426.7</v>
+        <v>301.28</v>
       </c>
       <c r="K73" t="n">
-        <v>78.01000000000001</v>
+        <v>-313.54</v>
       </c>
       <c r="L73" t="n">
-        <v>433.77</v>
+        <v>434.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:57:20</t>
+          <t>09:04:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7.86</v>
+        <v>7.64</v>
       </c>
       <c r="F74" t="n">
-        <v>19.39</v>
+        <v>20.93</v>
       </c>
       <c r="G74" t="n">
-        <v>143.1</v>
+        <v>158.7</v>
       </c>
       <c r="H74" t="n">
-        <v>40.8</v>
+        <v>59</v>
       </c>
       <c r="I74" t="n">
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>155.1</v>
+        <v>142.22</v>
       </c>
       <c r="K74" t="n">
-        <v>-10.15</v>
+        <v>120.76</v>
       </c>
       <c r="L74" t="n">
-        <v>155.43</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:58:23</t>
+          <t>09:06:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.97</v>
+        <v>7.77</v>
       </c>
       <c r="F75" t="n">
-        <v>16.54</v>
+        <v>20.93</v>
       </c>
       <c r="G75" t="n">
-        <v>154.7</v>
+        <v>144.9</v>
       </c>
       <c r="H75" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="I75" t="n">
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.45</v>
+        <v>-91.16</v>
       </c>
       <c r="K75" t="n">
-        <v>-114.3</v>
+        <v>-96.31999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>118.29</v>
+        <v>132.62</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:59:29</t>
+          <t>09:07:40</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>7.1</v>
+        <v>6.55</v>
       </c>
       <c r="F76" t="n">
-        <v>17.15</v>
+        <v>15.71</v>
       </c>
       <c r="G76" t="n">
-        <v>147.6</v>
+        <v>141.1</v>
       </c>
       <c r="H76" t="n">
-        <v>53.3</v>
+        <v>72.3</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>158.02</v>
+        <v>-49.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-65.59</v>
+        <v>-149.91</v>
       </c>
       <c r="L76" t="n">
-        <v>171.09</v>
+        <v>157.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:03:37</t>
+          <t>09:11:28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.19</v>
+        <v>8.5</v>
       </c>
       <c r="F77" t="n">
-        <v>19.91</v>
+        <v>20.93</v>
       </c>
       <c r="G77" t="n">
-        <v>171.4</v>
+        <v>149.4</v>
       </c>
       <c r="H77" t="n">
-        <v>54.8</v>
+        <v>47.3</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-10.33</v>
+        <v>-251.05</v>
       </c>
       <c r="K77" t="n">
-        <v>-190.17</v>
+        <v>-62.36</v>
       </c>
       <c r="L77" t="n">
-        <v>190.45</v>
+        <v>258.68</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:04:57</t>
+          <t>09:12:14</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>7.78</v>
+        <v>6.78</v>
       </c>
       <c r="F78" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="G78" t="n">
-        <v>147.9</v>
+        <v>147.5</v>
       </c>
       <c r="H78" t="n">
-        <v>37.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>227.79</v>
+        <v>50.28</v>
       </c>
       <c r="K78" t="n">
-        <v>17.27</v>
+        <v>-201.52</v>
       </c>
       <c r="L78" t="n">
-        <v>228.44</v>
+        <v>207.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:07:01</t>
+          <t>09:13:47</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.69</v>
+        <v>7.52</v>
       </c>
       <c r="F79" t="n">
-        <v>18.87</v>
+        <v>20.93</v>
       </c>
       <c r="G79" t="n">
-        <v>150.1</v>
+        <v>143.4</v>
       </c>
       <c r="H79" t="n">
-        <v>68.2</v>
+        <v>49.3</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-224.79</v>
+        <v>-205.46</v>
       </c>
       <c r="K79" t="n">
-        <v>13.17</v>
+        <v>45.47</v>
       </c>
       <c r="L79" t="n">
-        <v>225.17</v>
+        <v>210.43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:09:34</t>
+          <t>09:18:09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.93</v>
+        <v>7.65</v>
       </c>
       <c r="F80" t="n">
-        <v>18.57</v>
+        <v>20.93</v>
       </c>
       <c r="G80" t="n">
-        <v>165.2</v>
+        <v>157</v>
       </c>
       <c r="H80" t="n">
-        <v>89</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-212.14</v>
+        <v>-141.29</v>
       </c>
       <c r="K80" t="n">
-        <v>-125.83</v>
+        <v>-203.41</v>
       </c>
       <c r="L80" t="n">
-        <v>246.65</v>
+        <v>247.67</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:11:17</t>
+          <t>09:20:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>8.31</v>
+        <v>7.77</v>
       </c>
       <c r="F81" t="n">
-        <v>20.93</v>
+        <v>17.14</v>
       </c>
       <c r="G81" t="n">
-        <v>142.4</v>
+        <v>168.2</v>
       </c>
       <c r="H81" t="n">
-        <v>44</v>
+        <v>42.1</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-232.2</v>
+        <v>113.17</v>
       </c>
       <c r="K81" t="n">
-        <v>-229.14</v>
+        <v>152.96</v>
       </c>
       <c r="L81" t="n">
-        <v>326.22</v>
+        <v>190.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:13:38</t>
+          <t>09:22:16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>8.15</v>
+        <v>6.81</v>
       </c>
       <c r="F82" t="n">
-        <v>20.93</v>
+        <v>19.66</v>
       </c>
       <c r="G82" t="n">
-        <v>148</v>
+        <v>146.3</v>
       </c>
       <c r="H82" t="n">
-        <v>61.5</v>
+        <v>96.3</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>62</v>
+        <v>89.48</v>
       </c>
       <c r="K82" t="n">
-        <v>-266.07</v>
+        <v>257.79</v>
       </c>
       <c r="L82" t="n">
-        <v>273.2</v>
+        <v>272.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:17:28</t>
+          <t>09:26:34</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>8.359999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F83" t="n">
         <v>20.93</v>
       </c>
       <c r="G83" t="n">
-        <v>153.8</v>
+        <v>146.1</v>
       </c>
       <c r="H83" t="n">
-        <v>94.2</v>
+        <v>53.5</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-114.47</v>
+        <v>-84.45999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-285.43</v>
+        <v>413.35</v>
       </c>
       <c r="L83" t="n">
-        <v>307.53</v>
+        <v>421.89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:18:47</t>
+          <t>09:28:29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.62</v>
+        <v>8.4</v>
       </c>
       <c r="F84" t="n">
-        <v>17.73</v>
+        <v>20.93</v>
       </c>
       <c r="G84" t="n">
-        <v>159.9</v>
+        <v>153</v>
       </c>
       <c r="H84" t="n">
-        <v>52.4</v>
+        <v>55.7</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-133.42</v>
+        <v>284.92</v>
       </c>
       <c r="K84" t="n">
-        <v>-324.65</v>
+        <v>-398.45</v>
       </c>
       <c r="L84" t="n">
-        <v>350.99</v>
+        <v>489.84</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:19:50</t>
+          <t>09:30:23</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="F85" t="n">
         <v>20.93</v>
       </c>
       <c r="G85" t="n">
-        <v>158.6</v>
+        <v>149.5</v>
       </c>
       <c r="H85" t="n">
-        <v>57.2</v>
+        <v>54.7</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-113.09</v>
+        <v>-426.69</v>
       </c>
       <c r="K85" t="n">
-        <v>-273.72</v>
+        <v>-32.66</v>
       </c>
       <c r="L85" t="n">
-        <v>296.16</v>
+        <v>427.94</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:24:55</t>
+          <t>09:35:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>7.51</v>
+        <v>7.59</v>
       </c>
       <c r="F86" t="n">
-        <v>17.96</v>
+        <v>20.93</v>
       </c>
       <c r="G86" t="n">
-        <v>145.6</v>
+        <v>157.7</v>
       </c>
       <c r="H86" t="n">
-        <v>88.2</v>
+        <v>30.6</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>347.04</v>
+        <v>-275.66</v>
       </c>
       <c r="K86" t="n">
-        <v>-208.64</v>
+        <v>217.22</v>
       </c>
       <c r="L86" t="n">
-        <v>404.93</v>
+        <v>350.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:25:48</t>
+          <t>09:36:07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>7.63</v>
+        <v>7.89</v>
       </c>
       <c r="F87" t="n">
         <v>20.93</v>
       </c>
       <c r="G87" t="n">
-        <v>149.3</v>
+        <v>147.7</v>
       </c>
       <c r="H87" t="n">
-        <v>89.7</v>
+        <v>51</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>55.45</v>
+        <v>615.55</v>
       </c>
       <c r="K87" t="n">
-        <v>-445.01</v>
+        <v>89.78</v>
       </c>
       <c r="L87" t="n">
-        <v>448.45</v>
+        <v>622.0599999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:27:08</t>
+          <t>09:38:39</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>7.25</v>
+        <v>7.22</v>
       </c>
       <c r="F88" t="n">
-        <v>19.82</v>
+        <v>19.5</v>
       </c>
       <c r="G88" t="n">
-        <v>151</v>
+        <v>168.6</v>
       </c>
       <c r="H88" t="n">
-        <v>77.3</v>
+        <v>95.3</v>
       </c>
       <c r="I88" t="n">
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>117.68</v>
+        <v>-178.92</v>
       </c>
       <c r="K88" t="n">
-        <v>-414.54</v>
+        <v>397.12</v>
       </c>
       <c r="L88" t="n">
-        <v>430.92</v>
+        <v>435.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.61</v>
+        <v>-92.06999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>27.43</v>
+        <v>34.78</v>
       </c>
       <c r="L14" t="n">
-        <v>77.62</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-36.16</v>
+        <v>-46.12</v>
       </c>
       <c r="K15" t="n">
-        <v>71.26000000000001</v>
+        <v>90.87</v>
       </c>
       <c r="L15" t="n">
-        <v>79.91</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-46.39</v>
+        <v>-59.62</v>
       </c>
       <c r="K16" t="n">
-        <v>-46.75</v>
+        <v>-60.09</v>
       </c>
       <c r="L16" t="n">
-        <v>65.86</v>
+        <v>84.65000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.61</v>
+        <v>-91.52</v>
       </c>
       <c r="K17" t="n">
-        <v>108.11</v>
+        <v>132.62</v>
       </c>
       <c r="L17" t="n">
-        <v>131.36</v>
+        <v>161.13</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-38.51</v>
+        <v>-48.21</v>
       </c>
       <c r="K18" t="n">
-        <v>99.23999999999999</v>
+        <v>124.25</v>
       </c>
       <c r="L18" t="n">
-        <v>106.45</v>
+        <v>133.28</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-137.24</v>
+        <v>-157.44</v>
       </c>
       <c r="K19" t="n">
-        <v>15.24</v>
+        <v>17.48</v>
       </c>
       <c r="L19" t="n">
-        <v>138.08</v>
+        <v>158.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>116.87</v>
+        <v>152.83</v>
       </c>
       <c r="K20" t="n">
-        <v>-117.07</v>
+        <v>-153.09</v>
       </c>
       <c r="L20" t="n">
-        <v>165.43</v>
+        <v>216.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-54.02</v>
+        <v>-69.86</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6</v>
+        <v>186.98</v>
       </c>
       <c r="L21" t="n">
-        <v>154.36</v>
+        <v>199.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>162.22</v>
+        <v>206.94</v>
       </c>
       <c r="K22" t="n">
-        <v>63.73</v>
+        <v>81.3</v>
       </c>
       <c r="L22" t="n">
-        <v>174.29</v>
+        <v>222.34</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>9.33</v>
+        <v>13.54</v>
       </c>
       <c r="K23" t="n">
-        <v>-210.39</v>
+        <v>-305.39</v>
       </c>
       <c r="L23" t="n">
-        <v>210.6</v>
+        <v>305.69</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-291.45</v>
+        <v>-410.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-38.53</v>
+        <v>-54.27</v>
       </c>
       <c r="L24" t="n">
-        <v>293.99</v>
+        <v>414.16</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>161.21</v>
+        <v>237.43</v>
       </c>
       <c r="K25" t="n">
-        <v>56.31</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>170.76</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-30.74</v>
+        <v>-46.53</v>
       </c>
       <c r="K26" t="n">
-        <v>310.59</v>
+        <v>470.23</v>
       </c>
       <c r="L26" t="n">
-        <v>312.1</v>
+        <v>472.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-18.74</v>
+        <v>-27.89</v>
       </c>
       <c r="K27" t="n">
-        <v>-315.24</v>
+        <v>-469.25</v>
       </c>
       <c r="L27" t="n">
-        <v>315.8</v>
+        <v>470.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-143.8</v>
+        <v>-216.29</v>
       </c>
       <c r="K28" t="n">
-        <v>-265.14</v>
+        <v>-398.79</v>
       </c>
       <c r="L28" t="n">
-        <v>301.63</v>
+        <v>453.67</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-87.37</v>
+        <v>-107.38</v>
       </c>
       <c r="K29" t="n">
-        <v>15.35</v>
+        <v>18.87</v>
       </c>
       <c r="L29" t="n">
-        <v>88.7</v>
+        <v>109.02</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-43.1</v>
+        <v>-51.12</v>
       </c>
       <c r="K30" t="n">
-        <v>99.23999999999999</v>
+        <v>117.71</v>
       </c>
       <c r="L30" t="n">
-        <v>108.19</v>
+        <v>128.33</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.17</v>
+        <v>-14.29</v>
       </c>
       <c r="K31" t="n">
-        <v>70.28</v>
+        <v>89.88</v>
       </c>
       <c r="L31" t="n">
-        <v>71.16</v>
+        <v>91.01000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>100.19</v>
+        <v>118.44</v>
       </c>
       <c r="K32" t="n">
-        <v>78.54000000000001</v>
+        <v>92.84</v>
       </c>
       <c r="L32" t="n">
-        <v>127.3</v>
+        <v>150.49</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-12.98</v>
+        <v>-15.61</v>
       </c>
       <c r="K33" t="n">
-        <v>-131.62</v>
+        <v>-158.28</v>
       </c>
       <c r="L33" t="n">
-        <v>132.26</v>
+        <v>159.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-46.54</v>
+        <v>-59.81</v>
       </c>
       <c r="K34" t="n">
-        <v>89.22</v>
+        <v>114.67</v>
       </c>
       <c r="L34" t="n">
-        <v>100.63</v>
+        <v>129.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-156.12</v>
+        <v>-198.74</v>
       </c>
       <c r="K35" t="n">
-        <v>45.92</v>
+        <v>58.46</v>
       </c>
       <c r="L35" t="n">
-        <v>162.74</v>
+        <v>207.16</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>122.82</v>
+        <v>166.21</v>
       </c>
       <c r="K36" t="n">
-        <v>111.31</v>
+        <v>150.63</v>
       </c>
       <c r="L36" t="n">
-        <v>165.76</v>
+        <v>224.3</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>216.52</v>
+        <v>276.91</v>
       </c>
       <c r="K37" t="n">
-        <v>-146.73</v>
+        <v>-187.65</v>
       </c>
       <c r="L37" t="n">
-        <v>261.55</v>
+        <v>334.5</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>136.31</v>
+        <v>194.94</v>
       </c>
       <c r="K38" t="n">
-        <v>-309.16</v>
+        <v>-442.12</v>
       </c>
       <c r="L38" t="n">
-        <v>337.87</v>
+        <v>483.19</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>278.19</v>
+        <v>399.24</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.91</v>
+        <v>-7.04</v>
       </c>
       <c r="L39" t="n">
-        <v>278.23</v>
+        <v>399.31</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-291.46</v>
+        <v>-417.77</v>
       </c>
       <c r="K40" t="n">
-        <v>64.45999999999999</v>
+        <v>92.39</v>
       </c>
       <c r="L40" t="n">
-        <v>298.5</v>
+        <v>427.86</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-89.56999999999999</v>
+        <v>-118.59</v>
       </c>
       <c r="K41" t="n">
-        <v>-636.0700000000001</v>
+        <v>-842.13</v>
       </c>
       <c r="L41" t="n">
-        <v>642.35</v>
+        <v>850.4400000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-234.29</v>
+        <v>-311.7</v>
       </c>
       <c r="K42" t="n">
-        <v>518.1799999999999</v>
+        <v>689.38</v>
       </c>
       <c r="L42" t="n">
-        <v>568.6799999999999</v>
+        <v>756.5700000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-416.25</v>
+        <v>-580.3099999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-83.28</v>
+        <v>-116.1</v>
       </c>
       <c r="L43" t="n">
-        <v>424.5</v>
+        <v>591.8099999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>62.63</v>
+        <v>76.27</v>
       </c>
       <c r="K44" t="n">
-        <v>-85</v>
+        <v>-103.51</v>
       </c>
       <c r="L44" t="n">
-        <v>105.58</v>
+        <v>128.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.57</v>
+        <v>-57.4</v>
       </c>
       <c r="K45" t="n">
-        <v>98.39</v>
+        <v>118.71</v>
       </c>
       <c r="L45" t="n">
-        <v>109.28</v>
+        <v>131.85</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-90.45</v>
+        <v>-115.82</v>
       </c>
       <c r="K46" t="n">
-        <v>26.62</v>
+        <v>34.08</v>
       </c>
       <c r="L46" t="n">
-        <v>94.29000000000001</v>
+        <v>120.73</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>4.8</v>
+        <v>5.46</v>
       </c>
       <c r="K47" t="n">
-        <v>-177.72</v>
+        <v>-202.45</v>
       </c>
       <c r="L47" t="n">
-        <v>177.78</v>
+        <v>202.53</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>37.18</v>
+        <v>44.94</v>
       </c>
       <c r="K48" t="n">
-        <v>160.91</v>
+        <v>194.48</v>
       </c>
       <c r="L48" t="n">
-        <v>165.15</v>
+        <v>199.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>87.09</v>
+        <v>119.07</v>
       </c>
       <c r="K49" t="n">
-        <v>-69.87</v>
+        <v>-95.53</v>
       </c>
       <c r="L49" t="n">
-        <v>111.65</v>
+        <v>152.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-176.98</v>
+        <v>-232.48</v>
       </c>
       <c r="K50" t="n">
-        <v>61.75</v>
+        <v>81.12</v>
       </c>
       <c r="L50" t="n">
-        <v>187.44</v>
+        <v>246.22</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>72.70999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-175.13</v>
+        <v>-223.99</v>
       </c>
       <c r="L51" t="n">
-        <v>189.62</v>
+        <v>242.53</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>163.76</v>
+        <v>202.91</v>
       </c>
       <c r="K52" t="n">
-        <v>-49.87</v>
+        <v>-61.79</v>
       </c>
       <c r="L52" t="n">
-        <v>171.18</v>
+        <v>212.11</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>154.92</v>
+        <v>228.05</v>
       </c>
       <c r="K53" t="n">
-        <v>-210.18</v>
+        <v>-309.4</v>
       </c>
       <c r="L53" t="n">
-        <v>261.11</v>
+        <v>384.36</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>310.44</v>
+        <v>442.02</v>
       </c>
       <c r="K54" t="n">
-        <v>-66.17</v>
+        <v>-94.22</v>
       </c>
       <c r="L54" t="n">
-        <v>317.41</v>
+        <v>451.95</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-223.37</v>
+        <v>-348.12</v>
       </c>
       <c r="K55" t="n">
-        <v>-81.27</v>
+        <v>-126.65</v>
       </c>
       <c r="L55" t="n">
-        <v>237.7</v>
+        <v>370.44</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-272.53</v>
+        <v>-332.08</v>
       </c>
       <c r="K56" t="n">
-        <v>791.38</v>
+        <v>964.3</v>
       </c>
       <c r="L56" t="n">
-        <v>836.99</v>
+        <v>1019.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-294.57</v>
+        <v>-408.83</v>
       </c>
       <c r="K57" t="n">
-        <v>364.01</v>
+        <v>505.21</v>
       </c>
       <c r="L57" t="n">
-        <v>468.27</v>
+        <v>649.9</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>186.47</v>
+        <v>258.3</v>
       </c>
       <c r="K58" t="n">
-        <v>-543.8099999999999</v>
+        <v>-753.3</v>
       </c>
       <c r="L58" t="n">
-        <v>574.89</v>
+        <v>796.35</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.89</v>
+        <v>-1.09</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.93</v>
+        <v>-10.98</v>
       </c>
       <c r="L59" t="n">
-        <v>8.98</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>78.51000000000001</v>
+        <v>96.86</v>
       </c>
       <c r="K60" t="n">
-        <v>29.6</v>
+        <v>36.52</v>
       </c>
       <c r="L60" t="n">
-        <v>83.91</v>
+        <v>103.52</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-98.86</v>
+        <v>-116.96</v>
       </c>
       <c r="K61" t="n">
-        <v>-25</v>
+        <v>-29.57</v>
       </c>
       <c r="L61" t="n">
-        <v>101.97</v>
+        <v>120.64</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>162.03</v>
+        <v>194.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-75.08</v>
+        <v>-90.29000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>178.58</v>
+        <v>214.76</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>65.17</v>
+        <v>79.42</v>
       </c>
       <c r="K63" t="n">
-        <v>-78.78</v>
+        <v>-96.01000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>102.24</v>
+        <v>124.61</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.04</v>
+        <v>-66.84999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-111.99</v>
+        <v>-136.03</v>
       </c>
       <c r="L64" t="n">
-        <v>124.79</v>
+        <v>151.57</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-20.45</v>
+        <v>-28.89</v>
       </c>
       <c r="K65" t="n">
-        <v>86.17</v>
+        <v>121.72</v>
       </c>
       <c r="L65" t="n">
-        <v>88.56999999999999</v>
+        <v>125.1</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>96.20999999999999</v>
+        <v>131.82</v>
       </c>
       <c r="K66" t="n">
-        <v>150.54</v>
+        <v>206.24</v>
       </c>
       <c r="L66" t="n">
-        <v>178.66</v>
+        <v>244.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>181.7</v>
+        <v>227.86</v>
       </c>
       <c r="K67" t="n">
-        <v>-161.78</v>
+        <v>-202.88</v>
       </c>
       <c r="L67" t="n">
-        <v>243.29</v>
+        <v>305.09</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-460.1</v>
+        <v>-591.53</v>
       </c>
       <c r="K68" t="n">
-        <v>-197.04</v>
+        <v>-253.33</v>
       </c>
       <c r="L68" t="n">
-        <v>500.51</v>
+        <v>643.49</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-113.58</v>
+        <v>-174.35</v>
       </c>
       <c r="K69" t="n">
-        <v>-212.05</v>
+        <v>-325.51</v>
       </c>
       <c r="L69" t="n">
-        <v>240.56</v>
+        <v>369.26</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>286.85</v>
+        <v>400.76</v>
       </c>
       <c r="K70" t="n">
-        <v>167.04</v>
+        <v>233.38</v>
       </c>
       <c r="L70" t="n">
-        <v>331.94</v>
+        <v>463.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-393.93</v>
+        <v>-502.23</v>
       </c>
       <c r="K71" t="n">
-        <v>-451.4</v>
+        <v>-575.51</v>
       </c>
       <c r="L71" t="n">
-        <v>599.12</v>
+        <v>763.84</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-342.78</v>
+        <v>-526.66</v>
       </c>
       <c r="K72" t="n">
-        <v>-40.5</v>
+        <v>-62.22</v>
       </c>
       <c r="L72" t="n">
-        <v>345.17</v>
+        <v>530.33</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>529.21</v>
+        <v>698.8200000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>51.29</v>
+        <v>67.72</v>
       </c>
       <c r="L73" t="n">
-        <v>531.6900000000001</v>
+        <v>702.09</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>107.12</v>
+        <v>124.46</v>
       </c>
       <c r="K74" t="n">
-        <v>-22.54</v>
+        <v>-26.19</v>
       </c>
       <c r="L74" t="n">
-        <v>109.47</v>
+        <v>127.19</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-25.72</v>
+        <v>-31.67</v>
       </c>
       <c r="K75" t="n">
-        <v>97.42</v>
+        <v>119.92</v>
       </c>
       <c r="L75" t="n">
-        <v>100.75</v>
+        <v>124.03</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>113.76</v>
+        <v>131.83</v>
       </c>
       <c r="K76" t="n">
-        <v>30.49</v>
+        <v>35.33</v>
       </c>
       <c r="L76" t="n">
-        <v>117.78</v>
+        <v>136.48</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>93.76000000000001</v>
+        <v>118.54</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.24</v>
+        <v>-71.09999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>109.34</v>
+        <v>138.23</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-39.64</v>
+        <v>-48.66</v>
       </c>
       <c r="K78" t="n">
-        <v>-131.38</v>
+        <v>-161.25</v>
       </c>
       <c r="L78" t="n">
-        <v>137.23</v>
+        <v>168.43</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>2.11</v>
+        <v>2.85</v>
       </c>
       <c r="K79" t="n">
-        <v>16.94</v>
+        <v>22.92</v>
       </c>
       <c r="L79" t="n">
-        <v>17.07</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-82.36</v>
+        <v>-102.86</v>
       </c>
       <c r="K80" t="n">
-        <v>179.19</v>
+        <v>223.81</v>
       </c>
       <c r="L80" t="n">
-        <v>197.21</v>
+        <v>246.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-153.48</v>
+        <v>-184.01</v>
       </c>
       <c r="K81" t="n">
-        <v>-262.95</v>
+        <v>-315.26</v>
       </c>
       <c r="L81" t="n">
-        <v>304.47</v>
+        <v>365.03</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>195.27</v>
+        <v>246.15</v>
       </c>
       <c r="K82" t="n">
-        <v>39.49</v>
+        <v>49.78</v>
       </c>
       <c r="L82" t="n">
-        <v>199.22</v>
+        <v>251.14</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>221.04</v>
+        <v>297.49</v>
       </c>
       <c r="K83" t="n">
-        <v>-282.16</v>
+        <v>-379.75</v>
       </c>
       <c r="L83" t="n">
-        <v>358.43</v>
+        <v>482.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>286.12</v>
+        <v>370.6</v>
       </c>
       <c r="K84" t="n">
-        <v>-387.41</v>
+        <v>-501.8</v>
       </c>
       <c r="L84" t="n">
-        <v>481.61</v>
+        <v>623.8200000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-292.41</v>
+        <v>-426.59</v>
       </c>
       <c r="K85" t="n">
-        <v>-54.2</v>
+        <v>-79.06999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>297.4</v>
+        <v>433.86</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-406.05</v>
+        <v>-520.72</v>
       </c>
       <c r="K86" t="n">
-        <v>-466.53</v>
+        <v>-598.28</v>
       </c>
       <c r="L86" t="n">
-        <v>618.49</v>
+        <v>793.16</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>178.51</v>
+        <v>246.79</v>
       </c>
       <c r="K87" t="n">
-        <v>-409.25</v>
+        <v>-565.78</v>
       </c>
       <c r="L87" t="n">
-        <v>446.49</v>
+        <v>617.27</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>542.96</v>
+        <v>708.9299999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>141.13</v>
+        <v>184.27</v>
       </c>
       <c r="L88" t="n">
-        <v>561</v>
+        <v>732.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-19.xlsx
+++ b/output/2024-04-19.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-92.06999999999999</v>
+        <v>-190.28</v>
       </c>
       <c r="K14" t="n">
-        <v>34.78</v>
+        <v>71.87</v>
       </c>
       <c r="L14" t="n">
-        <v>98.42</v>
+        <v>203.4</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.12</v>
+        <v>-95.91</v>
       </c>
       <c r="K15" t="n">
-        <v>90.87</v>
+        <v>188.99</v>
       </c>
       <c r="L15" t="n">
-        <v>101.9</v>
+        <v>211.93</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-59.62</v>
+        <v>-108.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-60.09</v>
+        <v>-109.65</v>
       </c>
       <c r="L16" t="n">
-        <v>84.65000000000001</v>
+        <v>154.47</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-91.52</v>
+        <v>-169.83</v>
       </c>
       <c r="K17" t="n">
-        <v>132.62</v>
+        <v>246.1</v>
       </c>
       <c r="L17" t="n">
-        <v>161.13</v>
+        <v>299.01</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-48.21</v>
+        <v>-79.20999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>124.25</v>
+        <v>204.13</v>
       </c>
       <c r="L18" t="n">
-        <v>133.28</v>
+        <v>218.96</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-157.44</v>
+        <v>-242.55</v>
       </c>
       <c r="K19" t="n">
-        <v>17.48</v>
+        <v>26.93</v>
       </c>
       <c r="L19" t="n">
-        <v>158.41</v>
+        <v>244.04</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-107.38</v>
+        <v>-222.96</v>
       </c>
       <c r="K29" t="n">
-        <v>18.87</v>
+        <v>39.17</v>
       </c>
       <c r="L29" t="n">
-        <v>109.02</v>
+        <v>226.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-51.12</v>
+        <v>-101.03</v>
       </c>
       <c r="K30" t="n">
-        <v>117.71</v>
+        <v>232.63</v>
       </c>
       <c r="L30" t="n">
-        <v>128.33</v>
+        <v>253.63</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.29</v>
+        <v>-27.88</v>
       </c>
       <c r="K31" t="n">
-        <v>89.88</v>
+        <v>175.35</v>
       </c>
       <c r="L31" t="n">
-        <v>91.01000000000001</v>
+        <v>177.55</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>118.44</v>
+        <v>189.54</v>
       </c>
       <c r="K32" t="n">
-        <v>92.84</v>
+        <v>148.58</v>
       </c>
       <c r="L32" t="n">
-        <v>150.49</v>
+        <v>240.83</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-15.61</v>
+        <v>-28.16</v>
       </c>
       <c r="K33" t="n">
-        <v>-158.28</v>
+        <v>-285.52</v>
       </c>
       <c r="L33" t="n">
-        <v>159.05</v>
+        <v>286.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-59.81</v>
+        <v>-101.39</v>
       </c>
       <c r="K34" t="n">
-        <v>114.67</v>
+        <v>194.39</v>
       </c>
       <c r="L34" t="n">
-        <v>129.34</v>
+        <v>219.24</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>76.27</v>
+        <v>170.69</v>
       </c>
       <c r="K44" t="n">
-        <v>-103.51</v>
+        <v>-231.64</v>
       </c>
       <c r="L44" t="n">
-        <v>128.58</v>
+        <v>287.73</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-57.4</v>
+        <v>-121.62</v>
       </c>
       <c r="K45" t="n">
-        <v>118.71</v>
+        <v>251.53</v>
       </c>
       <c r="L45" t="n">
-        <v>131.85</v>
+        <v>279.39</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-115.82</v>
+        <v>-258.8</v>
       </c>
       <c r="K46" t="n">
-        <v>34.08</v>
+        <v>76.16</v>
       </c>
       <c r="L46" t="n">
-        <v>120.73</v>
+        <v>269.77</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>5.46</v>
+        <v>8.85</v>
       </c>
       <c r="K47" t="n">
-        <v>-202.45</v>
+        <v>-328.06</v>
       </c>
       <c r="L47" t="n">
-        <v>202.53</v>
+        <v>328.18</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>44.94</v>
+        <v>87.14</v>
       </c>
       <c r="K48" t="n">
-        <v>194.48</v>
+        <v>377.12</v>
       </c>
       <c r="L48" t="n">
-        <v>199.6</v>
+        <v>387.06</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>119.07</v>
+        <v>237.79</v>
       </c>
       <c r="K49" t="n">
-        <v>-95.53</v>
+        <v>-190.79</v>
       </c>
       <c r="L49" t="n">
-        <v>152.65</v>
+        <v>304.87</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.09</v>
+        <v>-1.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.98</v>
+        <v>-17.41</v>
       </c>
       <c r="L59" t="n">
-        <v>11.04</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>96.86</v>
+        <v>193.93</v>
       </c>
       <c r="K60" t="n">
-        <v>36.52</v>
+        <v>73.11</v>
       </c>
       <c r="L60" t="n">
-        <v>103.52</v>
+        <v>207.25</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-116.96</v>
+        <v>-243.25</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.57</v>
+        <v>-61.51</v>
       </c>
       <c r="L61" t="n">
-        <v>120.64</v>
+        <v>250.9</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>194.86</v>
+        <v>373.18</v>
       </c>
       <c r="K62" t="n">
-        <v>-90.29000000000001</v>
+        <v>-172.92</v>
       </c>
       <c r="L62" t="n">
-        <v>214.76</v>
+        <v>411.3</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>79.42</v>
+        <v>119.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-96.01000000000001</v>
+        <v>-143.94</v>
       </c>
       <c r="L63" t="n">
-        <v>124.61</v>
+        <v>186.81</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-66.84999999999999</v>
+        <v>-113.17</v>
       </c>
       <c r="K64" t="n">
-        <v>-136.03</v>
+        <v>-230.29</v>
       </c>
       <c r="L64" t="n">
-        <v>151.57</v>
+        <v>256.59</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>124.46</v>
+        <v>256.02</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.19</v>
+        <v>-53.87</v>
       </c>
       <c r="L74" t="n">
-        <v>127.19</v>
+        <v>261.62</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-31.67</v>
+        <v>-75.34</v>
       </c>
       <c r="K75" t="n">
-        <v>119.92</v>
+        <v>285.29</v>
       </c>
       <c r="L75" t="n">
-        <v>124.03</v>
+        <v>295.07</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>131.83</v>
+        <v>275.45</v>
       </c>
       <c r="K76" t="n">
-        <v>35.33</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>136.48</v>
+        <v>285.17</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>118.54</v>
+        <v>197.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-71.09999999999999</v>
+        <v>-118.42</v>
       </c>
       <c r="L77" t="n">
-        <v>138.23</v>
+        <v>230.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-48.66</v>
+        <v>-89.72</v>
       </c>
       <c r="K78" t="n">
-        <v>-161.25</v>
+        <v>-297.33</v>
       </c>
       <c r="L78" t="n">
-        <v>168.43</v>
+        <v>310.57</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>2.85</v>
+        <v>6.22</v>
       </c>
       <c r="K79" t="n">
-        <v>22.92</v>
+        <v>50.07</v>
       </c>
       <c r="L79" t="n">
-        <v>23.1</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="80">
